--- a/informes_data/ACB/2025-26/playoffs/aggregate/AGGREGATE_Valencia Basket.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate/AGGREGATE_Valencia Basket.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>152.28</v>
+        <v>239.4</v>
       </c>
       <c r="C2" t="n">
-        <v>153.06</v>
+        <v>240.74</v>
       </c>
       <c r="D2" t="n">
-        <v>111.7208937671501</v>
+        <v>120.0465232200714</v>
       </c>
       <c r="E2" t="n">
-        <v>98.65412256631386</v>
+        <v>111.3234194566753</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5255474452554745</v>
+        <v>0.5547945205479452</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1255134641716111</v>
+        <v>0.1216893342877595</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3066666666666666</v>
+        <v>0.3418803418803419</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1970802919708029</v>
+        <v>0.2100456621004566</v>
       </c>
       <c r="J2" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="K2" t="n">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="L2" t="n">
+        <v>24</v>
+      </c>
+      <c r="M2" t="n">
+        <v>34</v>
+      </c>
+      <c r="N2" t="n">
+        <v>50</v>
+      </c>
+      <c r="O2" t="n">
+        <v>72</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.3287671232876712</v>
+      </c>
+      <c r="Q2" t="n">
         <v>10</v>
       </c>
-      <c r="M2" t="n">
-        <v>22</v>
-      </c>
-      <c r="N2" t="n">
-        <v>31</v>
-      </c>
-      <c r="O2" t="n">
-        <v>46</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.3357664233576642</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>6</v>
-      </c>
       <c r="R2" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1313868613138686</v>
+        <v>0.1278538812785388</v>
       </c>
       <c r="T2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="U2" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1386861313868613</v>
+        <v>0.1050228310502283</v>
       </c>
       <c r="W2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="X2" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.08029197080291971</v>
+        <v>0.1232876712328767</v>
       </c>
       <c r="Z2" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AA2" t="n">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3138686131386861</v>
+        <v>0.3150684931506849</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.6739130434782609</v>
+        <v>0.6944444444444444</v>
       </c>
       <c r="AD2" t="n">
+        <v>0.3571428571428572</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.5217391304347826</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.3703703703703703</v>
+      </c>
+      <c r="AG2" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="AE2" t="n">
-        <v>0.4210526315789473</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0.4545454545454545</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0.3023255813953488</v>
-      </c>
       <c r="AH2" t="n">
-        <v>1.347826086956522</v>
+        <v>1.388888888888889</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.8421052631578947</v>
+        <v>1.043478260869565</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1</v>
+        <v>1.03125</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.068965517241379</v>
+        <v>0.9487179487179487</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.130434782608696</v>
+        <v>1.15</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.666666666666667</v>
+        <v>1.5</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.681818181818182</v>
+        <v>1.941176470588235</v>
       </c>
       <c r="AO2" t="n">
-        <v>6.227272727272728</v>
+        <v>6.441176470588236</v>
       </c>
       <c r="AP2" t="n">
-        <v>7.909090909090909</v>
+        <v>8.382352941176471</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>76.14</v>
+        <v>79.8</v>
       </c>
       <c r="C3" t="n">
-        <v>76.53</v>
+        <v>80.24666666666667</v>
       </c>
       <c r="D3" t="n">
-        <v>111.7208937671501</v>
+        <v>120.0465232200714</v>
       </c>
       <c r="E3" t="n">
-        <v>98.65412256631386</v>
+        <v>111.3234194566752</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5255474452554745</v>
+        <v>0.5547945205479452</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1255134641716111</v>
+        <v>0.1216893342877595</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3066666666666666</v>
+        <v>0.3418803418803419</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1970802919708029</v>
+        <v>0.2100456621004566</v>
       </c>
       <c r="J3" t="n">
-        <v>15.5</v>
+        <v>12.33333333333333</v>
       </c>
       <c r="K3" t="n">
-        <v>13</v>
+        <v>15.33333333333333</v>
       </c>
       <c r="L3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M3" t="n">
-        <v>11</v>
+        <v>11.33333333333333</v>
       </c>
       <c r="N3" t="n">
-        <v>15.5</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="O3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3357664233576642</v>
+        <v>0.3287671232876712</v>
       </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="R3" t="n">
-        <v>9</v>
+        <v>9.333333333333334</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1313868613138686</v>
+        <v>0.1278538812785388</v>
       </c>
       <c r="T3" t="n">
         <v>4</v>
       </c>
       <c r="U3" t="n">
-        <v>9.5</v>
+        <v>7.666666666666667</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1386861313868613</v>
+        <v>0.1050228310502283</v>
       </c>
       <c r="W3" t="n">
-        <v>2.5</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="X3" t="n">
-        <v>5.5</v>
+        <v>9</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.08029197080291971</v>
+        <v>0.1232876712328767</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.5</v>
+        <v>7.666666666666667</v>
       </c>
       <c r="AA3" t="n">
-        <v>21.5</v>
+        <v>23</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3138686131386861</v>
+        <v>0.3150684931506849</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.6739130434782609</v>
+        <v>0.6944444444444445</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.4210526315789473</v>
+        <v>0.5217391304347826</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.3703703703703704</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3023255813953488</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.347826086956522</v>
+        <v>1.388888888888889</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.8421052631578947</v>
+        <v>1.043478260869565</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1</v>
+        <v>1.03125</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.068965517241379</v>
+        <v>0.9487179487179488</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.130434782608696</v>
+        <v>1.15</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.666666666666667</v>
+        <v>1.5</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.681818181818182</v>
+        <v>1.941176470588235</v>
       </c>
       <c r="AO3" t="n">
-        <v>6.227272727272728</v>
+        <v>6.441176470588235</v>
       </c>
       <c r="AP3" t="n">
-        <v>7.909090909090909</v>
+        <v>8.382352941176471</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>153.84</v>
+        <v>242.08</v>
       </c>
       <c r="C4" t="n">
-        <v>153.06</v>
+        <v>240.74</v>
       </c>
       <c r="D4" t="n">
-        <v>98.65412256631386</v>
+        <v>111.3234194566753</v>
       </c>
       <c r="E4" t="n">
-        <v>111.7208937671501</v>
+        <v>120.0465232200714</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4558823529411765</v>
+        <v>0.5185185185185185</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1603627516036275</v>
+        <v>0.1392459297343616</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3214285714285715</v>
+        <v>0.304</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1985294117647059</v>
+        <v>0.2037037037037037</v>
       </c>
       <c r="J4" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="K4" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="L4" t="n">
+        <v>13</v>
+      </c>
+      <c r="M4" t="n">
+        <v>37</v>
+      </c>
+      <c r="N4" t="n">
+        <v>38</v>
+      </c>
+      <c r="O4" t="n">
+        <v>61</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.2824074074074074</v>
+      </c>
+      <c r="Q4" t="n">
         <v>9</v>
       </c>
-      <c r="M4" t="n">
-        <v>27</v>
-      </c>
-      <c r="N4" t="n">
-        <v>21</v>
-      </c>
-      <c r="O4" t="n">
-        <v>35</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.2573529411764706</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3</v>
-      </c>
       <c r="R4" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1470588235294118</v>
+        <v>0.1527777777777778</v>
       </c>
       <c r="T4" t="n">
         <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="V4" t="n">
-        <v>0.05147058823529412</v>
+        <v>0.05092592592592592</v>
       </c>
       <c r="W4" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="X4" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.125</v>
+        <v>0.1296296296296296</v>
       </c>
       <c r="Z4" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="AA4" t="n">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.4191176470588235</v>
+        <v>0.3842592592592592</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.6</v>
+        <v>0.6229508196721312</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.15</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.3529411764705883</v>
+        <v>0.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3157894736842105</v>
+        <v>0.3373493975903614</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.2</v>
+        <v>1.245901639344262</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.972972972972973</v>
+        <v>1.135135135135135</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.6176470588235294</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.9629629629629629</v>
+        <v>1.052631578947368</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.8</v>
+        <v>1.444444444444444</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9655172413793104</v>
+        <v>1.435897435897436</v>
       </c>
       <c r="AO4" t="n">
-        <v>4.689655172413793</v>
+        <v>5.538461538461538</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.655172413793103</v>
+        <v>6.974358974358974</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>76.92</v>
+        <v>80.69333333333333</v>
       </c>
       <c r="C5" t="n">
-        <v>76.53</v>
+        <v>80.24666666666667</v>
       </c>
       <c r="D5" t="n">
-        <v>98.65412256631386</v>
+        <v>111.3234194566752</v>
       </c>
       <c r="E5" t="n">
-        <v>111.7208937671501</v>
+        <v>120.0465232200714</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4558823529411765</v>
+        <v>0.5185185185185185</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1603627516036275</v>
+        <v>0.1392459297343616</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3214285714285715</v>
+        <v>0.304</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1985294117647059</v>
+        <v>0.2037037037037037</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K5" t="n">
-        <v>13</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="L5" t="n">
-        <v>4.5</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="M5" t="n">
-        <v>13.5</v>
+        <v>12.33333333333333</v>
       </c>
       <c r="N5" t="n">
-        <v>10.5</v>
+        <v>12.66666666666667</v>
       </c>
       <c r="O5" t="n">
-        <v>17.5</v>
+        <v>20.33333333333333</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2573529411764706</v>
+        <v>0.2824074074074074</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1470588235294118</v>
+        <v>0.1527777777777778</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="U5" t="n">
-        <v>3.5</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="V5" t="n">
-        <v>0.05147058823529412</v>
+        <v>0.05092592592592592</v>
       </c>
       <c r="W5" t="n">
-        <v>3</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="X5" t="n">
-        <v>8.5</v>
+        <v>9.333333333333334</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.125</v>
+        <v>0.1296296296296297</v>
       </c>
       <c r="Z5" t="n">
-        <v>9</v>
+        <v>9.333333333333334</v>
       </c>
       <c r="AA5" t="n">
-        <v>28.5</v>
+        <v>27.66666666666667</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.4191176470588235</v>
+        <v>0.3842592592592593</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.6</v>
+        <v>0.6229508196721312</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.15</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.3529411764705883</v>
+        <v>0.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3157894736842105</v>
+        <v>0.3373493975903615</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.2</v>
+        <v>1.245901639344262</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.972972972972973</v>
+        <v>1.135135135135135</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.6176470588235293</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.9629629629629629</v>
+        <v>1.052631578947369</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.8</v>
+        <v>1.444444444444444</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9655172413793104</v>
+        <v>1.435897435897436</v>
       </c>
       <c r="AO5" t="n">
-        <v>4.689655172413793</v>
+        <v>5.538461538461538</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.655172413793103</v>
+        <v>6.974358974358974</v>
       </c>
     </row>
     <row r="7">
@@ -1419,10 +1419,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D8" t="n">
         <v>3</v>
@@ -1431,23 +1431,23 @@
         <v>9</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
+        <v>18</v>
+      </c>
+      <c r="H8" t="n">
         <v>8</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
+        <v>11</v>
+      </c>
+      <c r="J8" t="n">
+        <v>10</v>
+      </c>
+      <c r="K8" t="n">
         <v>5</v>
       </c>
-      <c r="I8" t="n">
-        <v>7</v>
-      </c>
-      <c r="J8" t="n">
-        <v>4</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3</v>
-      </c>
       <c r="L8" t="n">
         <v>2</v>
       </c>
@@ -1461,19 +1461,19 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="U8" t="n">
         <v>4</v>
@@ -1482,10 +1482,10 @@
         <v>3</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="n">
         <v>1</v>
@@ -1515,60 +1515,60 @@
         <v>0.4</v>
       </c>
       <c r="AH8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AI8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.5</v>
+        <v>0.429</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL8" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>0.182</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>42:22</t>
+          <t>72:22</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>20.08</v>
+        <v>33.84</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.265</v>
+        <v>0.389</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.349</v>
+        <v>0.455</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.697</v>
+        <v>0.857</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>0.059</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.294</v>
+        <v>0.296</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.216</v>
+        <v>0.209</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.067</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.068</v>
+        <v>0.103</v>
       </c>
     </row>
     <row r="9">
@@ -1578,156 +1578,156 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="D9" t="n">
+        <v>12</v>
+      </c>
+      <c r="E9" t="n">
+        <v>16</v>
+      </c>
+      <c r="F9" t="n">
         <v>5</v>
       </c>
-      <c r="E9" t="n">
+      <c r="G9" t="n">
+        <v>15</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>7</v>
+      </c>
+      <c r="K9" t="n">
+        <v>12</v>
+      </c>
+      <c r="L9" t="n">
+        <v>4</v>
+      </c>
+      <c r="M9" t="n">
+        <v>5</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>4</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="n">
+        <v>54</v>
+      </c>
+      <c r="U9" t="n">
+        <v>6</v>
+      </c>
+      <c r="V9" t="n">
+        <v>5</v>
+      </c>
+      <c r="W9" t="n">
+        <v>3</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF9" t="n">
         <v>8</v>
       </c>
-      <c r="F9" t="n">
-        <v>4</v>
-      </c>
-      <c r="G9" t="n">
-        <v>11</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>3</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3</v>
-      </c>
-      <c r="R9" t="n">
-        <v>3</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3</v>
-      </c>
-      <c r="T9" t="n">
-        <v>23</v>
-      </c>
-      <c r="U9" t="n">
-        <v>4</v>
-      </c>
-      <c r="V9" t="n">
-        <v>3</v>
-      </c>
-      <c r="W9" t="n">
-        <v>3</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF9" t="n">
+      <c r="AG9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
         <v>5</v>
       </c>
-      <c r="AG9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>4</v>
-      </c>
       <c r="AL9" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.444</v>
+        <v>0.417</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>51:23</t>
+          <t>81:44</t>
         </is>
       </c>
       <c r="AO9" t="n">
-        <v>22.88</v>
+        <v>37.76</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.579</v>
+        <v>0.629</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.604</v>
+        <v>0.656</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.049</v>
+        <v>1.139</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.131</v>
+        <v>0.132</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.105</v>
+        <v>0.129</v>
       </c>
       <c r="AU9" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.203</v>
+        <v>0.207</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.021</v>
+        <v>0.052</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.074</v>
+        <v>0.147</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.056</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="10">
@@ -1737,7 +1737,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
         <v>25</v>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>33:41</t>
+          <t>33:56</t>
         </is>
       </c>
       <c r="AO10" t="n">
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.191</v>
+        <v>0.186</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.032</v>
+        <v>0.031</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.17</v>
+        <v>0.177</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.036</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="11">
@@ -1896,156 +1896,156 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="n">
+        <v>14</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" t="n">
+        <v>6</v>
+      </c>
+      <c r="H11" t="n">
+        <v>6</v>
+      </c>
+      <c r="I11" t="n">
         <v>7</v>
       </c>
-      <c r="E11" t="n">
+      <c r="J11" t="n">
+        <v>5</v>
+      </c>
+      <c r="K11" t="n">
+        <v>11</v>
+      </c>
+      <c r="L11" t="n">
+        <v>5</v>
+      </c>
+      <c r="M11" t="n">
+        <v>5</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>3</v>
+      </c>
+      <c r="S11" t="n">
+        <v>6</v>
+      </c>
+      <c r="T11" t="n">
+        <v>57</v>
+      </c>
+      <c r="U11" t="n">
+        <v>7</v>
+      </c>
+      <c r="V11" t="n">
+        <v>6</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
         <v>10</v>
       </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>3</v>
-      </c>
-      <c r="H11" t="n">
-        <v>2</v>
-      </c>
-      <c r="I11" t="n">
-        <v>3</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3</v>
-      </c>
-      <c r="K11" t="n">
+      <c r="Z11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>71:52</t>
+        </is>
+      </c>
+      <c r="AO11" t="n">
+        <v>24.08</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0.758</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.453</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AU11" t="n">
         <v>5</v>
       </c>
-      <c r="L11" t="n">
-        <v>3</v>
-      </c>
-      <c r="M11" t="n">
-        <v>3</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>30</v>
-      </c>
-      <c r="U11" t="n">
-        <v>5</v>
-      </c>
-      <c r="V11" t="n">
-        <v>2</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0.778</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>43:11</t>
-        </is>
-      </c>
-      <c r="AO11" t="n">
-        <v>14.32</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>0.654</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0.663</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>1.327</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0</v>
-      </c>
       <c r="AV11" t="n">
-        <v>0.151</v>
+        <v>0.15</v>
       </c>
       <c r="AW11" t="n">
         <v>0.074</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.11</v>
+        <v>0.153</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.055</v>
+        <v>0.054</v>
       </c>
     </row>
     <row r="12">
@@ -2055,43 +2055,43 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" t="n">
+        <v>11</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
         <v>8</v>
       </c>
-      <c r="D12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" t="n">
-        <v>7</v>
-      </c>
       <c r="F12" t="n">
         <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K12" t="n">
         <v>6</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2103,108 +2103,108 @@
         <v>2</v>
       </c>
       <c r="R12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T12" t="n">
+        <v>10</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL12" t="n">
         <v>7</v>
       </c>
-      <c r="U12" t="n">
-        <v>3</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>5</v>
-      </c>
       <c r="AM12" t="n">
-        <v>0.2</v>
+        <v>0.143</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>31:31</t>
+          <t>44:03</t>
         </is>
       </c>
       <c r="AO12" t="n">
-        <v>15</v>
+        <v>21.76</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.308</v>
+        <v>0.222</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.308</v>
+        <v>0.278</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.533</v>
+        <v>0.506</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.133</v>
+        <v>0.092</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.217</v>
+        <v>0.221</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.034</v>
+        <v>0.073</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.181</v>
+        <v>0.136</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.05</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="13">
@@ -2214,89 +2214,89 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
       </c>
       <c r="G13" t="n">
+        <v>5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" t="n">
+        <v>5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>9</v>
+      </c>
+      <c r="K13" t="n">
+        <v>12</v>
+      </c>
+      <c r="L13" t="n">
         <v>4</v>
       </c>
-      <c r="H13" t="n">
-        <v>2</v>
-      </c>
-      <c r="I13" t="n">
-        <v>3</v>
-      </c>
-      <c r="J13" t="n">
-        <v>6</v>
-      </c>
-      <c r="K13" t="n">
+      <c r="M13" t="n">
+        <v>4</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4</v>
+      </c>
+      <c r="R13" t="n">
         <v>9</v>
       </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>2</v>
-      </c>
-      <c r="N13" t="n">
-        <v>2</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="n">
+        <v>34</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" t="n">
         <v>7</v>
       </c>
-      <c r="S13" t="n">
-        <v>3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>29</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1</v>
-      </c>
-      <c r="V13" t="n">
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
         <v>5</v>
       </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3</v>
-      </c>
       <c r="AD13" t="n">
         <v>0</v>
       </c>
@@ -2313,7 +2313,7 @@
         <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
@@ -2329,41 +2329,41 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>38:11</t>
+          <t>55:07</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>17.32</v>
+        <v>30.2</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.633</v>
+        <v>0.479</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.643</v>
+        <v>0.496</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.212</v>
+        <v>0.861</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.058</v>
+        <v>0.132</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.133</v>
+        <v>0.125</v>
       </c>
       <c r="AU13" t="n">
-        <v>6</v>
+        <v>2.25</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.207</v>
+        <v>0.245</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.028</v>
+        <v>0.078</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.224</v>
+        <v>0.218</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.111</v>
+        <v>0.096</v>
       </c>
     </row>
     <row r="14">
@@ -2373,156 +2373,156 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E14" t="n">
+        <v>18</v>
+      </c>
+      <c r="F14" t="n">
+        <v>5</v>
+      </c>
+      <c r="G14" t="n">
+        <v>15</v>
+      </c>
+      <c r="H14" t="n">
         <v>8</v>
       </c>
-      <c r="F14" t="n">
-        <v>3</v>
-      </c>
-      <c r="G14" t="n">
+      <c r="I14" t="n">
         <v>8</v>
       </c>
-      <c r="H14" t="n">
+      <c r="J14" t="n">
+        <v>18</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>8</v>
+      </c>
+      <c r="R14" t="n">
+        <v>3</v>
+      </c>
+      <c r="S14" t="n">
+        <v>12</v>
+      </c>
+      <c r="T14" t="n">
+        <v>68</v>
+      </c>
+      <c r="U14" t="n">
+        <v>10</v>
+      </c>
+      <c r="V14" t="n">
+        <v>12</v>
+      </c>
+      <c r="W14" t="n">
+        <v>7</v>
+      </c>
+      <c r="X14" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC14" t="n">
         <v>5</v>
       </c>
-      <c r="I14" t="n">
+      <c r="AD14" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
         <v>5</v>
       </c>
-      <c r="J14" t="n">
-        <v>10</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>3</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>6</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>8</v>
-      </c>
-      <c r="T14" t="n">
-        <v>35</v>
-      </c>
-      <c r="U14" t="n">
-        <v>8</v>
-      </c>
-      <c r="V14" t="n">
-        <v>5</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>3</v>
-      </c>
       <c r="AL14" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.375</v>
+        <v>0.333</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>46:52</t>
+          <t>79:08</t>
         </is>
       </c>
       <c r="AO14" t="n">
-        <v>24.2</v>
+        <v>44.52</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.656</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.714</v>
+        <v>0.726</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.074</v>
+        <v>1.19</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.248</v>
+        <v>0.18</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.312</v>
+        <v>0.242</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.667</v>
+        <v>2.25</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.236</v>
+        <v>0.252</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.023</v>
+        <v>0.027</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.02</v>
+        <v>0.025</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.185</v>
+        <v>0.212</v>
       </c>
     </row>
     <row r="15">
@@ -2532,34 +2532,34 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D15" t="n">
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G15" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L15" t="n">
         <v>1</v>
@@ -2568,7 +2568,7 @@
         <v>1</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2583,105 +2583,105 @@
         <v>3</v>
       </c>
       <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="n">
+        <v>20</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>3</v>
+      </c>
+      <c r="W15" t="n">
+        <v>3</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI15" t="n">
         <v>4</v>
       </c>
-      <c r="T15" t="n">
-        <v>12</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>3</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>3</v>
-      </c>
       <c r="AJ15" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="AK15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AL15" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.333</v>
+        <v>0.5</v>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>37:01</t>
+          <t>55:14</t>
         </is>
       </c>
       <c r="AO15" t="n">
-        <v>15.88</v>
+        <v>21.76</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.625</v>
+        <v>0.615</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.676</v>
+        <v>0.644</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.756</v>
+        <v>0.873</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.441</v>
+        <v>0.322</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.25</v>
+        <v>0.231</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.143</v>
+        <v>0.286</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.196</v>
+        <v>0.176</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.029</v>
+        <v>0.019</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.18</v>
+        <v>0.163</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.017</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="16">
@@ -2691,16 +2691,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E16" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2715,37 +2715,37 @@
         <v>8</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L16" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M16" t="n">
         <v>1</v>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T16" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="U16" t="n">
         <v>4</v>
@@ -2754,19 +2754,19 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y16" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Z16" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.556</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
@@ -2806,41 +2806,41 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>34:20</t>
+          <t>56:39</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>16.52</v>
+        <v>21.52</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.417</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.419</v>
+        <v>0.538</v>
       </c>
       <c r="AR16" t="n">
-        <v>0.787</v>
+        <v>0.976</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.061</v>
+        <v>0.093</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.25</v>
+        <v>0.188</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.22</v>
+        <v>0.17</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.217</v>
+        <v>0.189</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.305</v>
+        <v>0.229</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="17">
@@ -3009,80 +3009,80 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
+        <v>12</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>8</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" t="n">
+        <v>5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" t="n">
         <v>7</v>
       </c>
-      <c r="D18" t="n">
-        <v>2</v>
-      </c>
-      <c r="E18" t="n">
-        <v>6</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3</v>
+      </c>
+      <c r="R18" t="n">
         <v>5</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2</v>
-      </c>
-      <c r="R18" t="n">
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>10</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
         <v>4</v>
       </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>5</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3</v>
-      </c>
       <c r="AA18" t="n">
         <v>0</v>
       </c>
@@ -3090,10 +3090,10 @@
         <v>2</v>
       </c>
       <c r="AC18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD18" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -3105,10 +3105,10 @@
         <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ18" t="n">
         <v>1</v>
@@ -3117,73 +3117,73 @@
         <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM18" t="n">
         <v>0</v>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>31:51</t>
+          <t>44:08</t>
         </is>
       </c>
       <c r="AO18" t="n">
-        <v>11</v>
+        <v>16.88</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.389</v>
+        <v>0.385</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.389</v>
+        <v>0.432</v>
       </c>
       <c r="AR18" t="n">
-        <v>0.636</v>
+        <v>0.711</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.182</v>
+        <v>0.178</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="AU18" t="n">
-        <v>2.5</v>
+        <v>2.333</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.158</v>
+        <v>0.171</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.033</v>
+        <v>0.024</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.083</v>
+        <v>0.06900000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>#77 Y. SIMA</t>
+          <t>#24 M. COSTELLO</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -3192,16 +3192,16 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L19" t="n">
         <v>2</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -3216,13 +3216,13 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -3237,66 +3237,66 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z19" t="n">
         <v>2</v>
       </c>
       <c r="AA19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM19" t="n">
         <v>0.5</v>
       </c>
-      <c r="AB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>0</v>
-      </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>22:15</t>
         </is>
       </c>
       <c r="AO19" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.25</v>
+        <v>0.722</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.25</v>
+        <v>0.722</v>
       </c>
       <c r="AR19" t="n">
-        <v>0.5</v>
+        <v>1.444</v>
       </c>
       <c r="AS19" t="n">
         <v>0</v>
@@ -3308,26 +3308,26 @@
         <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.162</v>
+        <v>0.181</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.189</v>
+        <v>0.096</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>#32 I. NOGUÉS</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -3354,10 +3354,10 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -3482,157 +3482,157 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>#77 Y. SIMA</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>171</v>
+        <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>83</v>
+        <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="M21" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="S21" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>209</v>
+        <v>-1</v>
       </c>
       <c r="U21" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="W21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="Z21" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.674</v>
+        <v>0.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.421</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.455</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.302</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>400:00</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AO21" t="n">
-        <v>175.28</v>
+        <v>4</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.526</v>
+        <v>0.25</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="AR21" t="n">
-        <v>0.976</v>
+        <v>0.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>0.126</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>0.197</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.682</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.2</v>
+        <v>0.159</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.061</v>
+        <v>0.189</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.136</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
         <v>0</v>
@@ -3641,157 +3641,157 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Rival</t>
+          <t>Equip</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C22" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="L22" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="M22" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.286</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.353</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.316</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>400:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO22" t="n">
-        <v>180.84</v>
+        <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.456</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.497</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>0.835</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>0.199</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>0.966</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.064</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.139</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
         <v>0</v>
@@ -3800,923 +3800,923 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>--- PER GAME STATS ---</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="inlineStr"/>
-      <c r="AB23" t="inlineStr"/>
-      <c r="AC23" t="inlineStr"/>
-      <c r="AD23" t="inlineStr"/>
-      <c r="AE23" t="inlineStr"/>
-      <c r="AF23" t="inlineStr"/>
-      <c r="AG23" t="inlineStr"/>
-      <c r="AH23" t="inlineStr"/>
-      <c r="AI23" t="inlineStr"/>
-      <c r="AJ23" t="inlineStr"/>
-      <c r="AK23" t="inlineStr"/>
-      <c r="AL23" t="inlineStr"/>
-      <c r="AM23" t="inlineStr"/>
-      <c r="AN23" t="inlineStr"/>
-      <c r="AO23" t="inlineStr"/>
-      <c r="AP23" t="inlineStr"/>
-      <c r="AQ23" t="inlineStr"/>
-      <c r="AR23" t="inlineStr"/>
-      <c r="AS23" t="inlineStr"/>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AU23" t="inlineStr"/>
-      <c r="AV23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr"/>
-      <c r="AX23" t="inlineStr"/>
-      <c r="AY23" t="inlineStr"/>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>3</v>
+      </c>
+      <c r="C23" t="n">
+        <v>289</v>
+      </c>
+      <c r="D23" t="n">
+        <v>72</v>
+      </c>
+      <c r="E23" t="n">
+        <v>123</v>
+      </c>
+      <c r="F23" t="n">
+        <v>33</v>
+      </c>
+      <c r="G23" t="n">
+        <v>96</v>
+      </c>
+      <c r="H23" t="n">
+        <v>46</v>
+      </c>
+      <c r="I23" t="n">
+        <v>60</v>
+      </c>
+      <c r="J23" t="n">
+        <v>66</v>
+      </c>
+      <c r="K23" t="n">
+        <v>87</v>
+      </c>
+      <c r="L23" t="n">
+        <v>40</v>
+      </c>
+      <c r="M23" t="n">
+        <v>23</v>
+      </c>
+      <c r="N23" t="n">
+        <v>17</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>34</v>
+      </c>
+      <c r="R23" t="n">
+        <v>57</v>
+      </c>
+      <c r="S23" t="n">
+        <v>64</v>
+      </c>
+      <c r="T23" t="n">
+        <v>367</v>
+      </c>
+      <c r="U23" t="n">
+        <v>37</v>
+      </c>
+      <c r="V23" t="n">
+        <v>46</v>
+      </c>
+      <c r="W23" t="n">
+        <v>24</v>
+      </c>
+      <c r="X23" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>72</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.694</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>28</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0.522</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>27</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>69</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>625:00</t>
+        </is>
+      </c>
+      <c r="AO23" t="n">
+        <v>279.4</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0.589</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.034</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>1.941</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0.139</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>#0 B. BADIO (Per Game)</t>
+          <t>Rival</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C24" t="n">
-        <v>7</v>
+        <v>268</v>
       </c>
       <c r="D24" t="n">
-        <v>1.5</v>
+        <v>49</v>
       </c>
       <c r="E24" t="n">
-        <v>4.5</v>
+        <v>105</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5</v>
+        <v>42</v>
       </c>
       <c r="G24" t="n">
-        <v>4</v>
+        <v>111</v>
       </c>
       <c r="H24" t="n">
-        <v>2.5</v>
+        <v>44</v>
       </c>
       <c r="I24" t="n">
-        <v>3.5</v>
+        <v>57</v>
       </c>
       <c r="J24" t="n">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="K24" t="n">
-        <v>1.5</v>
+        <v>77</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N24" t="n">
-        <v>0.5</v>
+        <v>17</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="R24" t="n">
-        <v>2.5</v>
+        <v>64</v>
       </c>
       <c r="S24" t="n">
-        <v>2.5</v>
+        <v>57</v>
       </c>
       <c r="T24" t="n">
+        <v>297</v>
+      </c>
+      <c r="U24" t="n">
+        <v>21</v>
+      </c>
+      <c r="V24" t="n">
+        <v>40</v>
+      </c>
+      <c r="W24" t="n">
+        <v>13</v>
+      </c>
+      <c r="X24" t="n">
         <v>9</v>
       </c>
-      <c r="U24" t="n">
-        <v>2</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0</v>
-      </c>
       <c r="Y24" t="n">
-        <v>0.5</v>
+        <v>38</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.5</v>
+        <v>61</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.333</v>
+        <v>0.623</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.5</v>
+        <v>33</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>0.273</v>
       </c>
       <c r="AE24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.5</v>
+        <v>11</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.4</v>
+        <v>0.182</v>
       </c>
       <c r="AH24" t="n">
-        <v>0.5</v>
+        <v>14</v>
       </c>
       <c r="AI24" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="AJ24" t="n">
         <v>0.5</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AL24" t="n">
-        <v>3</v>
+        <v>83</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>0.337</v>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>21:11</t>
+          <t>625:00</t>
         </is>
       </c>
       <c r="AO24" t="n">
-        <v>10.04</v>
+        <v>280.08</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.265</v>
+        <v>0.519</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.349</v>
+        <v>0.556</v>
       </c>
       <c r="AR24" t="n">
-        <v>0.697</v>
+        <v>0.957</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>0.139</v>
       </c>
       <c r="AT24" t="n">
-        <v>0.294</v>
+        <v>0.204</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>1.436</v>
       </c>
       <c r="AV24" t="n">
-        <v>0.216</v>
+        <v>0.2</v>
       </c>
       <c r="AW24" t="n">
-        <v>0.05</v>
+        <v>0.061</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.067</v>
+        <v>0.132</v>
       </c>
       <c r="AY24" t="n">
-        <v>0.068</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>#1 K. TAYLOR (Per Game)</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>2</v>
-      </c>
-      <c r="C25" t="n">
-        <v>12</v>
-      </c>
-      <c r="D25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E25" t="n">
-        <v>4</v>
-      </c>
-      <c r="F25" t="n">
-        <v>2</v>
-      </c>
-      <c r="G25" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K25" t="n">
-        <v>2</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T25" t="n">
-        <v>23</v>
-      </c>
-      <c r="U25" t="n">
-        <v>2</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>0.444</v>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>25:41</t>
-        </is>
-      </c>
-      <c r="AO25" t="n">
-        <v>11.44</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>0.579</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>0.604</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>1.049</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>0.131</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>0.203</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>0.074</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>0.056</v>
-      </c>
+          <t>--- PER GAME STATS ---</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
+      <c r="AP25" t="inlineStr"/>
+      <c r="AQ25" t="inlineStr"/>
+      <c r="AR25" t="inlineStr"/>
+      <c r="AS25" t="inlineStr"/>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AU25" t="inlineStr"/>
+      <c r="AV25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr"/>
+      <c r="AX25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>#3 N. REUVERS (Per Game)</t>
+          <t>#0 B. BADIO (Per Game)</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C26" t="n">
-        <v>12.5</v>
+        <v>9.667</v>
       </c>
       <c r="D26" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="F26" t="n">
-        <v>1.5</v>
+        <v>1.667</v>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H26" t="n">
-        <v>3</v>
+        <v>2.667</v>
       </c>
       <c r="I26" t="n">
-        <v>3.5</v>
+        <v>3.667</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>3.333</v>
       </c>
       <c r="K26" t="n">
-        <v>3</v>
+        <v>1.667</v>
       </c>
       <c r="L26" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="R26" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>3.333</v>
       </c>
       <c r="T26" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>1.333</v>
       </c>
       <c r="V26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W26" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
       </c>
       <c r="X26" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
       </c>
       <c r="Y26" t="n">
-        <v>2</v>
+        <v>0.333</v>
       </c>
       <c r="Z26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA26" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.5</v>
+        <v>1.667</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.333</v>
+        <v>0.4</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI26" t="n">
-        <v>0.5</v>
+        <v>2.333</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>0.429</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.5</v>
+        <v>0.667</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.5</v>
+        <v>3.667</v>
       </c>
       <c r="AM26" t="n">
-        <v>1</v>
+        <v>0.182</v>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>24:07</t>
         </is>
       </c>
       <c r="AO26" t="n">
-        <v>7.04</v>
+        <v>11.28</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.864</v>
+        <v>0.389</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.888</v>
+        <v>0.455</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.776</v>
+        <v>0.857</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>0.059</v>
       </c>
       <c r="AT26" t="n">
-        <v>0.545</v>
+        <v>0.296</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AV26" t="n">
-        <v>0.191</v>
+        <v>0.209</v>
       </c>
       <c r="AW26" t="n">
-        <v>0.032</v>
+        <v>0.03</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.17</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AY26" t="n">
-        <v>0.036</v>
+        <v>0.103</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>#4 J. PRADILLA (Per Game)</t>
+          <t>#1 K. TAYLOR (Per Game)</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C27" t="n">
-        <v>9.5</v>
+        <v>14.333</v>
       </c>
       <c r="D27" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="E27" t="n">
+        <v>5.333</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="G27" t="n">
         <v>5</v>
       </c>
-      <c r="F27" t="n">
+      <c r="H27" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.333</v>
+      </c>
+      <c r="K27" t="n">
+        <v>4</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="T27" t="n">
+        <v>54</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="AD27" t="n">
         <v>0.5</v>
       </c>
-      <c r="G27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H27" t="n">
-        <v>1</v>
-      </c>
-      <c r="I27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="S27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T27" t="n">
-        <v>30</v>
-      </c>
-      <c r="U27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0.778</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.5</v>
+        <v>2.667</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AH27" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.667</v>
       </c>
       <c r="AL27" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>0.417</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>21:35</t>
+          <t>27:14</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>7.16</v>
+        <v>12.587</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.654</v>
+        <v>0.629</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.663</v>
+        <v>0.656</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.327</v>
+        <v>1.139</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>0.132</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.154</v>
+        <v>0.129</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AV27" t="n">
-        <v>0.151</v>
+        <v>0.207</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.074</v>
+        <v>0.052</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.11</v>
+        <v>0.147</v>
       </c>
       <c r="AY27" t="n">
-        <v>0.055</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>#5 S. DE LARREA (Per Game)</t>
+          <t>#3 N. REUVERS (Per Game)</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>8.333</v>
       </c>
       <c r="D28" t="n">
-        <v>0.5</v>
+        <v>1.667</v>
       </c>
       <c r="E28" t="n">
-        <v>3.5</v>
+        <v>2.333</v>
       </c>
       <c r="F28" t="n">
         <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>1.333</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>2.333</v>
       </c>
       <c r="J28" t="n">
-        <v>1.5</v>
+        <v>0.667</v>
       </c>
       <c r="K28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L28" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="N28" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.5</v>
+        <v>2.333</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T28" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="U28" t="n">
-        <v>1.5</v>
+        <v>0.667</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.333</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.5</v>
+        <v>1.333</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
         <v>0.333</v>
       </c>
-      <c r="AE28" t="n">
-        <v>0</v>
-      </c>
       <c r="AF28" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AH28" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AL28" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AO28" t="n">
-        <v>7.5</v>
+        <v>4.693</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.308</v>
+        <v>0.864</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.308</v>
+        <v>0.888</v>
       </c>
       <c r="AR28" t="n">
-        <v>0.533</v>
+        <v>1.776</v>
       </c>
       <c r="AS28" t="n">
-        <v>0.133</v>
+        <v>0</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>0.545</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AV28" t="n">
-        <v>0.217</v>
+        <v>0.186</v>
       </c>
       <c r="AW28" t="n">
-        <v>0.034</v>
+        <v>0.031</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.181</v>
+        <v>0.177</v>
       </c>
       <c r="AY28" t="n">
-        <v>0.05</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>#7 B. KEY (Per Game)</t>
+          <t>#4 J. PRADILLA (Per Game)</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C29" t="n">
-        <v>10.5</v>
+        <v>11.667</v>
       </c>
       <c r="D29" t="n">
-        <v>4</v>
+        <v>3.333</v>
       </c>
       <c r="E29" t="n">
-        <v>5.5</v>
+        <v>4.667</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G29" t="n">
         <v>2</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>2.333</v>
       </c>
       <c r="J29" t="n">
-        <v>3</v>
+        <v>1.667</v>
       </c>
       <c r="K29" t="n">
-        <v>4.5</v>
+        <v>3.667</v>
       </c>
       <c r="L29" t="n">
-        <v>0.5</v>
+        <v>1.667</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>1.667</v>
       </c>
       <c r="N29" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="R29" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="T29" t="n">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="U29" t="n">
-        <v>0.5</v>
+        <v>2.333</v>
       </c>
       <c r="V29" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
@@ -4725,157 +4725,157 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>3.5</v>
+        <v>3.333</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.5</v>
+        <v>4.333</v>
       </c>
       <c r="AA29" t="n">
-        <v>1</v>
+        <v>0.769</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="AG29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="AK29" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="AL29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>23:57</t>
         </is>
       </c>
       <c r="AO29" t="n">
-        <v>8.66</v>
+        <v>8.026999999999999</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.633</v>
+        <v>0.725</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.643</v>
+        <v>0.758</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.212</v>
+        <v>1.453</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.058</v>
+        <v>0.042</v>
       </c>
       <c r="AT29" t="n">
-        <v>0.133</v>
+        <v>0.3</v>
       </c>
       <c r="AU29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV29" t="n">
-        <v>0.207</v>
+        <v>0.15</v>
       </c>
       <c r="AW29" t="n">
-        <v>0.028</v>
+        <v>0.074</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.224</v>
+        <v>0.153</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.111</v>
+        <v>0.054</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>#8 J. MONTERO (Per Game)</t>
+          <t>#5 S. DE LARREA (Per Game)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C30" t="n">
-        <v>13</v>
+        <v>3.667</v>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>0.333</v>
       </c>
       <c r="E30" t="n">
-        <v>4</v>
+        <v>2.667</v>
       </c>
       <c r="F30" t="n">
-        <v>1.5</v>
+        <v>0.667</v>
       </c>
       <c r="G30" t="n">
-        <v>4</v>
+        <v>3.333</v>
       </c>
       <c r="H30" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>2.5</v>
+        <v>1.333</v>
       </c>
       <c r="J30" t="n">
-        <v>5</v>
+        <v>1.333</v>
       </c>
       <c r="K30" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="L30" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>3</v>
+        <v>0.667</v>
       </c>
       <c r="Q30" t="n">
-        <v>3</v>
+        <v>0.667</v>
       </c>
       <c r="R30" t="n">
-        <v>0.5</v>
+        <v>1.667</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T30" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="U30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V30" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
         <v>0</v>
@@ -4884,349 +4884,349 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="AA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.5</v>
+        <v>1.333</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.5</v>
+        <v>0.333</v>
       </c>
       <c r="AL30" t="n">
-        <v>4</v>
+        <v>2.333</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.375</v>
+        <v>0.143</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>12.1</v>
+        <v>7.253</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.656</v>
+        <v>0.222</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.714</v>
+        <v>0.278</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.074</v>
+        <v>0.506</v>
       </c>
       <c r="AS30" t="n">
-        <v>0.248</v>
+        <v>0.092</v>
       </c>
       <c r="AT30" t="n">
-        <v>0.312</v>
+        <v>0.167</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.667</v>
+        <v>2</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.236</v>
+        <v>0.221</v>
       </c>
       <c r="AW30" t="n">
-        <v>0.023</v>
+        <v>0.073</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.02</v>
+        <v>0.136</v>
       </c>
       <c r="AY30" t="n">
-        <v>0.185</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>#10 O. MOORE (Per Game)</t>
+          <t>#7 B. KEY (Per Game)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C31" t="n">
-        <v>6</v>
+        <v>8.667</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>3.333</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>6.333</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>1.667</v>
       </c>
       <c r="H31" t="n">
         <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>1.667</v>
       </c>
       <c r="J31" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="K31" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="L31" t="n">
-        <v>0.5</v>
+        <v>1.333</v>
       </c>
       <c r="M31" t="n">
-        <v>0.5</v>
+        <v>1.333</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>3.5</v>
+        <v>1.333</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.5</v>
+        <v>1.333</v>
       </c>
       <c r="R31" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="S31" t="n">
-        <v>2</v>
+        <v>1.667</v>
       </c>
       <c r="T31" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>2.333</v>
       </c>
       <c r="W31" t="n">
-        <v>1.5</v>
+        <v>0.333</v>
       </c>
       <c r="X31" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.5</v>
+        <v>4.333</v>
       </c>
       <c r="AA31" t="n">
-        <v>1</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.5</v>
+        <v>1.667</v>
       </c>
       <c r="AD31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.5</v>
+        <v>0.333</v>
       </c>
       <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
         <v>0.333</v>
       </c>
-      <c r="AK31" t="n">
-        <v>0.5</v>
-      </c>
       <c r="AL31" t="n">
-        <v>1.5</v>
+        <v>1.333</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>7.94</v>
+        <v>10.067</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.625</v>
+        <v>0.479</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.676</v>
+        <v>0.496</v>
       </c>
       <c r="AR31" t="n">
-        <v>0.756</v>
+        <v>0.861</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.441</v>
+        <v>0.132</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
       <c r="AU31" t="n">
-        <v>0.143</v>
+        <v>2.25</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.196</v>
+        <v>0.245</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.029</v>
+        <v>0.078</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.18</v>
+        <v>0.218</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.017</v>
+        <v>0.096</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>#12 N. SAKO (Per Game)</t>
+          <t>#8 J. MONTERO (Per Game)</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C32" t="n">
-        <v>6.5</v>
+        <v>17.667</v>
       </c>
       <c r="D32" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="E32" t="n">
         <v>6</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>1.667</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H32" t="n">
-        <v>1.5</v>
+        <v>2.667</v>
       </c>
       <c r="I32" t="n">
+        <v>2.667</v>
+      </c>
+      <c r="J32" t="n">
+        <v>6</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.667</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.667</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1</v>
+      </c>
+      <c r="S32" t="n">
         <v>4</v>
       </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2</v>
-      </c>
       <c r="T32" t="n">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="U32" t="n">
-        <v>2</v>
+        <v>3.333</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W32" t="n">
-        <v>1.5</v>
+        <v>2.333</v>
       </c>
       <c r="X32" t="n">
-        <v>1.5</v>
+        <v>1.333</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="Z32" t="n">
-        <v>4.5</v>
+        <v>3.333</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.556</v>
+        <v>0.9</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.333</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.5</v>
+        <v>1.667</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="AH32" t="n">
         <v>0</v>
@@ -5238,145 +5238,145 @@
         <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1.667</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>26:22</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>8.26</v>
+        <v>14.84</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.417</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.419</v>
+        <v>0.726</v>
       </c>
       <c r="AR32" t="n">
-        <v>0.787</v>
+        <v>1.19</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.061</v>
+        <v>0.18</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.25</v>
+        <v>0.242</v>
       </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AV32" t="n">
-        <v>0.22</v>
+        <v>0.252</v>
       </c>
       <c r="AW32" t="n">
-        <v>0.217</v>
+        <v>0.027</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.305</v>
+        <v>0.025</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>0.212</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>#13 D. THOMPSON (Per Game)</t>
+          <t>#10 O. MOORE (Per Game)</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>6.333</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>1.333</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>3.333</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>1.333</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.333</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.333</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>1.667</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -5388,244 +5388,244 @@
         <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>1.333</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>0</v>
+        <v>7.253</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>0.615</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>0.644</v>
       </c>
       <c r="AR33" t="n">
-        <v>0</v>
+        <v>0.873</v>
       </c>
       <c r="AS33" t="n">
-        <v>0</v>
+        <v>0.322</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>0.231</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>0.286</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>0.176</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>0.019</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>0.163</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>#23 A. CÁRDENAS (Per Game)</t>
+          <t>#12 N. SAKO (Per Game)</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C34" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3</v>
+        <v>5.333</v>
       </c>
       <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2.667</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="K34" t="n">
+        <v>4.333</v>
+      </c>
+      <c r="L34" t="n">
+        <v>3.333</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="R34" t="n">
+        <v>2</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="T34" t="n">
+        <v>34</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>4.333</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN34" t="inlineStr">
+        <is>
+          <t>18:53</t>
+        </is>
+      </c>
+      <c r="AO34" t="n">
+        <v>7.173</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>0.976</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="AU34" t="n">
         <v>0.5</v>
       </c>
-      <c r="G34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>1</v>
-      </c>
-      <c r="R34" t="n">
-        <v>2</v>
-      </c>
-      <c r="S34" t="n">
-        <v>1</v>
-      </c>
-      <c r="T34" t="n">
-        <v>5</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AO34" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>0.389</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>0.389</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>0.636</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>0.182</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AV34" t="n">
-        <v>0.158</v>
+        <v>0.17</v>
       </c>
       <c r="AW34" t="n">
-        <v>0.033</v>
+        <v>0.189</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>0.229</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.083</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>#77 Y. SIMA (Per Game)</t>
+          <t>#13 D. THOMPSON (Per Game)</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>2</v>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -5640,7 +5640,7 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -5658,19 +5658,19 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
         <v>0</v>
@@ -5679,19 +5679,19 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
@@ -5718,27 +5718,27 @@
         <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AM35" t="n">
         <v>0</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AR35" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AS35" t="n">
         <v>0</v>
@@ -5750,10 +5750,10 @@
         <v>0</v>
       </c>
       <c r="AV35" t="n">
-        <v>0.162</v>
+        <v>0</v>
       </c>
       <c r="AW35" t="n">
-        <v>0.189</v>
+        <v>0</v>
       </c>
       <c r="AX35" t="n">
         <v>0</v>
@@ -5765,65 +5765,65 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>#23 A. CÁRDENAS (Per Game)</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>2.667</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>1.667</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>2.333</v>
       </c>
       <c r="K36" t="n">
-        <v>2.5</v>
+        <v>0.667</v>
       </c>
       <c r="L36" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.667</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -5832,410 +5832,1046 @@
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="Y36" t="n">
         <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1.333</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK36" t="n">
         <v>0</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM36" t="n">
         <v>0</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>0</v>
+        <v>5.627</v>
       </c>
       <c r="AP36" t="n">
-        <v>0</v>
+        <v>0.385</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0</v>
+        <v>0.432</v>
       </c>
       <c r="AR36" t="n">
-        <v>0</v>
+        <v>0.711</v>
       </c>
       <c r="AS36" t="n">
-        <v>0</v>
+        <v>0.178</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="AU36" t="n">
-        <v>0</v>
+        <v>2.333</v>
       </c>
       <c r="AV36" t="n">
-        <v>0</v>
+        <v>0.171</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="AX36" t="n">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>0.06900000000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>TOTAL (Per Game)</t>
+          <t>#24 M. COSTELLO (Per Game)</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>85.5</v>
+        <v>13</v>
       </c>
       <c r="D37" t="n">
-        <v>22.5</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>41.5</v>
+        <v>2</v>
       </c>
       <c r="F37" t="n">
+        <v>3</v>
+      </c>
+      <c r="G37" t="n">
+        <v>7</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2</v>
+      </c>
+      <c r="L37" t="n">
+        <v>2</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>15</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>2</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AN37" t="inlineStr">
+        <is>
+          <t>22:15</t>
+        </is>
+      </c>
+      <c r="AO37" t="n">
         <v>9</v>
       </c>
-      <c r="G37" t="n">
-        <v>27</v>
-      </c>
-      <c r="H37" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="I37" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="J37" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="K37" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="L37" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="M37" t="n">
-        <v>8</v>
-      </c>
-      <c r="N37" t="n">
-        <v>5</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>11</v>
-      </c>
-      <c r="R37" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="S37" t="n">
-        <v>20</v>
-      </c>
-      <c r="T37" t="n">
-        <v>209</v>
-      </c>
-      <c r="U37" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="V37" t="n">
-        <v>13</v>
-      </c>
-      <c r="W37" t="n">
-        <v>5</v>
-      </c>
-      <c r="X37" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>0.674</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>0.421</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>0.302</v>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>200:00</t>
-        </is>
-      </c>
-      <c r="AO37" t="n">
-        <v>87.64</v>
-      </c>
       <c r="AP37" t="n">
-        <v>0.526</v>
+        <v>0.722</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.722</v>
       </c>
       <c r="AR37" t="n">
-        <v>0.976</v>
+        <v>1.444</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.126</v>
+        <v>0</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.197</v>
+        <v>0</v>
       </c>
       <c r="AU37" t="n">
-        <v>1.682</v>
+        <v>0</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.2</v>
+        <v>0.181</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.061</v>
+        <v>0.096</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.136</v>
+        <v>0.09</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
+          <t>#32 I. NOGUÉS (Per Game)</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN38" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>#77 Y. SIMA (Per Game)</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN39" t="inlineStr">
+        <is>
+          <t>05:38</t>
+        </is>
+      </c>
+      <c r="AO39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>0.189</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>Equip (Per Game)</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>3</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.333</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN40" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL (Per Game)</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>3</v>
+      </c>
+      <c r="C41" t="n">
+        <v>96.333</v>
+      </c>
+      <c r="D41" t="n">
+        <v>24</v>
+      </c>
+      <c r="E41" t="n">
+        <v>41</v>
+      </c>
+      <c r="F41" t="n">
+        <v>11</v>
+      </c>
+      <c r="G41" t="n">
+        <v>32</v>
+      </c>
+      <c r="H41" t="n">
+        <v>15.333</v>
+      </c>
+      <c r="I41" t="n">
+        <v>20</v>
+      </c>
+      <c r="J41" t="n">
+        <v>22</v>
+      </c>
+      <c r="K41" t="n">
+        <v>29</v>
+      </c>
+      <c r="L41" t="n">
+        <v>13.333</v>
+      </c>
+      <c r="M41" t="n">
+        <v>7.667</v>
+      </c>
+      <c r="N41" t="n">
+        <v>5.667</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>11.333</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>11.333</v>
+      </c>
+      <c r="R41" t="n">
+        <v>19</v>
+      </c>
+      <c r="S41" t="n">
+        <v>21.333</v>
+      </c>
+      <c r="T41" t="n">
+        <v>367</v>
+      </c>
+      <c r="U41" t="n">
+        <v>12.333</v>
+      </c>
+      <c r="V41" t="n">
+        <v>15.333</v>
+      </c>
+      <c r="W41" t="n">
+        <v>8</v>
+      </c>
+      <c r="X41" t="n">
+        <v>5.333</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>16.667</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0.694</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>3.333</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>9.333</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>7.667</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0.522</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>3.333</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>7.667</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>23</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AN41" t="inlineStr">
+        <is>
+          <t>208:20</t>
+        </is>
+      </c>
+      <c r="AO41" t="n">
+        <v>93.133</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>0.589</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>1.034</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>1.941</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>0.139</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
           <t>Rival (Per Game)</t>
         </is>
       </c>
-      <c r="B38" t="n">
-        <v>2</v>
-      </c>
-      <c r="C38" t="n">
-        <v>75.5</v>
-      </c>
-      <c r="D38" t="n">
+      <c r="B42" t="n">
+        <v>3</v>
+      </c>
+      <c r="C42" t="n">
+        <v>89.333</v>
+      </c>
+      <c r="D42" t="n">
+        <v>16.333</v>
+      </c>
+      <c r="E42" t="n">
+        <v>35</v>
+      </c>
+      <c r="F42" t="n">
+        <v>14</v>
+      </c>
+      <c r="G42" t="n">
+        <v>37</v>
+      </c>
+      <c r="H42" t="n">
+        <v>14.667</v>
+      </c>
+      <c r="I42" t="n">
+        <v>19</v>
+      </c>
+      <c r="J42" t="n">
+        <v>18.667</v>
+      </c>
+      <c r="K42" t="n">
+        <v>25.667</v>
+      </c>
+      <c r="L42" t="n">
+        <v>12.667</v>
+      </c>
+      <c r="M42" t="n">
+        <v>8.333</v>
+      </c>
+      <c r="N42" t="n">
+        <v>5.667</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
         <v>13</v>
       </c>
-      <c r="E38" t="n">
-        <v>31</v>
-      </c>
-      <c r="F38" t="n">
-        <v>12</v>
-      </c>
-      <c r="G38" t="n">
-        <v>37</v>
-      </c>
-      <c r="H38" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="I38" t="n">
-        <v>18</v>
-      </c>
-      <c r="J38" t="n">
-        <v>14</v>
-      </c>
-      <c r="K38" t="n">
-        <v>26</v>
-      </c>
-      <c r="L38" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="M38" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="N38" t="n">
-        <v>5</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="R38" t="n">
-        <v>20</v>
-      </c>
-      <c r="S38" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="T38" t="n">
-        <v>158</v>
-      </c>
-      <c r="U38" t="n">
-        <v>4</v>
-      </c>
-      <c r="V38" t="n">
-        <v>13</v>
-      </c>
-      <c r="W38" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="X38" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0.353</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>9</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>0.316</v>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>200:00</t>
-        </is>
-      </c>
-      <c r="AO38" t="n">
-        <v>90.42</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>0.456</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>0.497</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>0.199</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>0.966</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>0.206</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>0.124</v>
-      </c>
-      <c r="AY38" t="n">
+      <c r="Q42" t="n">
+        <v>12.333</v>
+      </c>
+      <c r="R42" t="n">
+        <v>21.333</v>
+      </c>
+      <c r="S42" t="n">
+        <v>19</v>
+      </c>
+      <c r="T42" t="n">
+        <v>297</v>
+      </c>
+      <c r="U42" t="n">
+        <v>7</v>
+      </c>
+      <c r="V42" t="n">
+        <v>13.333</v>
+      </c>
+      <c r="W42" t="n">
+        <v>4.333</v>
+      </c>
+      <c r="X42" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>12.667</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>20.333</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0.623</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>3.667</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>4.667</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>9.333</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>9.333</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>27.667</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="AN42" t="inlineStr">
+        <is>
+          <t>208:20</t>
+        </is>
+      </c>
+      <c r="AO42" t="n">
+        <v>93.36</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>0.139</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>0.204</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>1.436</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="AY42" t="n">
         <v>0</v>
       </c>
     </row>

--- a/informes_data/ACB/2025-26/playoffs/aggregate/AGGREGATE_Valencia Basket.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate/AGGREGATE_Valencia Basket.xlsx
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>239.4</v>
+        <v>392</v>
       </c>
       <c r="C2" t="n">
-        <v>240.74</v>
+        <v>393.98</v>
       </c>
       <c r="D2" t="n">
-        <v>120.0465232200714</v>
+        <v>118.2801157419158</v>
       </c>
       <c r="E2" t="n">
-        <v>111.3234194566753</v>
+        <v>106.3505761713793</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5547945205479452</v>
+        <v>0.5341530054644809</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1216893342877595</v>
+        <v>0.1201716738197425</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3418803418803419</v>
+        <v>0.3609756097560975</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2100456621004566</v>
+        <v>0.2049180327868853</v>
       </c>
       <c r="J2" t="n">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="K2" t="n">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="L2" t="n">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="M2" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="N2" t="n">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="O2" t="n">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3287671232876712</v>
+        <v>0.2868852459016393</v>
       </c>
       <c r="Q2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="R2" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1278538812785388</v>
+        <v>0.1120218579234973</v>
       </c>
       <c r="T2" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="U2" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1050228310502283</v>
+        <v>0.1147540983606557</v>
       </c>
       <c r="W2" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="X2" t="n">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1232876712328767</v>
+        <v>0.1420765027322404</v>
       </c>
       <c r="Z2" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="AA2" t="n">
-        <v>69</v>
+        <v>126</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3150684931506849</v>
+        <v>0.3442622950819672</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.6944444444444444</v>
+        <v>0.6952380952380952</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.3902439024390244</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.5217391304347826</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.3703703703703703</v>
+        <v>0.3461538461538461</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3253968253968254</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.388888888888889</v>
+        <v>1.39047619047619</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.043478260869565</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.03125</v>
+        <v>0.9943820224719101</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.9487179487179487</v>
+        <v>1.027777777777778</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.15</v>
+        <v>0.972972972972973</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.5</v>
+        <v>1.708333333333333</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.941176470588235</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="AO2" t="n">
-        <v>6.441176470588236</v>
+        <v>6.535714285714286</v>
       </c>
       <c r="AP2" t="n">
-        <v>8.382352941176471</v>
+        <v>8.392857142857142</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>79.8</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>80.24666666666667</v>
+        <v>78.79599999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>120.0465232200714</v>
+        <v>118.2801157419158</v>
       </c>
       <c r="E3" t="n">
-        <v>111.3234194566752</v>
+        <v>106.3505761713793</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5547945205479452</v>
+        <v>0.5341530054644809</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1216893342877595</v>
+        <v>0.1201716738197425</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3418803418803419</v>
+        <v>0.3609756097560976</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2100456621004566</v>
+        <v>0.2049180327868853</v>
       </c>
       <c r="J3" t="n">
-        <v>12.33333333333333</v>
+        <v>14.8</v>
       </c>
       <c r="K3" t="n">
-        <v>15.33333333333333</v>
+        <v>14.4</v>
       </c>
       <c r="L3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>11.33333333333333</v>
+        <v>11</v>
       </c>
       <c r="N3" t="n">
-        <v>16.66666666666667</v>
+        <v>14.6</v>
       </c>
       <c r="O3" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3287671232876712</v>
+        <v>0.2868852459016393</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.333333333333333</v>
+        <v>3.2</v>
       </c>
       <c r="R3" t="n">
-        <v>9.333333333333334</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1278538812785388</v>
+        <v>0.1120218579234973</v>
       </c>
       <c r="T3" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="U3" t="n">
-        <v>7.666666666666667</v>
+        <v>8.4</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1050228310502283</v>
+        <v>0.1147540983606557</v>
       </c>
       <c r="W3" t="n">
-        <v>3.333333333333333</v>
+        <v>3.6</v>
       </c>
       <c r="X3" t="n">
-        <v>9</v>
+        <v>10.4</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1232876712328767</v>
+        <v>0.1420765027322404</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.666666666666667</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA3" t="n">
-        <v>23</v>
+        <v>25.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3150684931506849</v>
+        <v>0.3442622950819672</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.6944444444444445</v>
+        <v>0.6952380952380952</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.3902439024390245</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.5217391304347826</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.3703703703703704</v>
+        <v>0.3461538461538461</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3333333333333334</v>
+        <v>0.3253968253968254</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.388888888888889</v>
+        <v>1.39047619047619</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.043478260869565</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.03125</v>
+        <v>0.99438202247191</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.9487179487179488</v>
+        <v>1.027777777777778</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.15</v>
+        <v>0.9729729729729729</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.5</v>
+        <v>1.708333333333333</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.941176470588235</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="AO3" t="n">
-        <v>6.441176470588235</v>
+        <v>6.535714285714286</v>
       </c>
       <c r="AP3" t="n">
-        <v>8.382352941176471</v>
+        <v>8.392857142857144</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>242.08</v>
+        <v>395.96</v>
       </c>
       <c r="C4" t="n">
-        <v>240.74</v>
+        <v>393.98</v>
       </c>
       <c r="D4" t="n">
-        <v>111.3234194566753</v>
+        <v>106.3505761713793</v>
       </c>
       <c r="E4" t="n">
-        <v>120.0465232200714</v>
+        <v>118.2801157419158</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5185185185185185</v>
+        <v>0.5101156069364162</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1392459297343616</v>
+        <v>0.1582556708282047</v>
       </c>
       <c r="H4" t="n">
-        <v>0.304</v>
+        <v>0.3010204081632653</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2037037037037037</v>
+        <v>0.1907514450867052</v>
       </c>
       <c r="J4" t="n">
+        <v>41</v>
+      </c>
+      <c r="K4" t="n">
+        <v>66</v>
+      </c>
+      <c r="L4" t="n">
+        <v>23</v>
+      </c>
+      <c r="M4" t="n">
+        <v>66</v>
+      </c>
+      <c r="N4" t="n">
+        <v>64</v>
+      </c>
+      <c r="O4" t="n">
+        <v>96</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.2774566473988439</v>
+      </c>
+      <c r="Q4" t="n">
         <v>21</v>
       </c>
-      <c r="K4" t="n">
-        <v>40</v>
-      </c>
-      <c r="L4" t="n">
-        <v>13</v>
-      </c>
-      <c r="M4" t="n">
-        <v>37</v>
-      </c>
-      <c r="N4" t="n">
-        <v>38</v>
-      </c>
-      <c r="O4" t="n">
-        <v>61</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.2824074074074074</v>
-      </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
+        <v>58</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.1676300578034682</v>
+      </c>
+      <c r="T4" t="n">
         <v>9</v>
       </c>
-      <c r="R4" t="n">
-        <v>33</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.1527777777777778</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2</v>
-      </c>
       <c r="U4" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="V4" t="n">
-        <v>0.05092592592592592</v>
+        <v>0.08092485549132948</v>
       </c>
       <c r="W4" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="X4" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1296296296296296</v>
+        <v>0.1329479768786127</v>
       </c>
       <c r="Z4" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AA4" t="n">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3842592592592592</v>
+        <v>0.3410404624277457</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.6229508196721312</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.3620689655172414</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.3214285714285715</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.5</v>
+        <v>0.4130434782608696</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3373493975903614</v>
+        <v>0.3050847457627119</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.245901639344262</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.135135135135135</v>
+        <v>1.00609756097561</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.6176470588235294</v>
+        <v>0.7321428571428571</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.052631578947368</v>
+        <v>1.11864406779661</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.444444444444444</v>
+        <v>1.4375</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.435897435897436</v>
+        <v>1.222222222222222</v>
       </c>
       <c r="AO4" t="n">
-        <v>5.538461538461538</v>
+        <v>4.805555555555555</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.974358974358974</v>
+        <v>6.027777777777778</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>80.69333333333333</v>
+        <v>79.19200000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>80.24666666666667</v>
+        <v>78.79599999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>111.3234194566752</v>
+        <v>106.3505761713793</v>
       </c>
       <c r="E5" t="n">
-        <v>120.0465232200714</v>
+        <v>118.2801157419158</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5185185185185185</v>
+        <v>0.5101156069364162</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1392459297343616</v>
+        <v>0.1582556708282047</v>
       </c>
       <c r="H5" t="n">
-        <v>0.304</v>
+        <v>0.3010204081632653</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2037037037037037</v>
+        <v>0.1907514450867052</v>
       </c>
       <c r="J5" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>13.33333333333333</v>
+        <v>13.2</v>
       </c>
       <c r="L5" t="n">
-        <v>4.333333333333333</v>
+        <v>4.6</v>
       </c>
       <c r="M5" t="n">
-        <v>12.33333333333333</v>
+        <v>13.2</v>
       </c>
       <c r="N5" t="n">
-        <v>12.66666666666667</v>
+        <v>12.8</v>
       </c>
       <c r="O5" t="n">
-        <v>20.33333333333333</v>
+        <v>19.2</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2824074074074074</v>
+        <v>0.277456647398844</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="R5" t="n">
-        <v>11</v>
+        <v>11.6</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1527777777777778</v>
+        <v>0.1676300578034682</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6666666666666666</v>
+        <v>1.8</v>
       </c>
       <c r="U5" t="n">
-        <v>3.666666666666667</v>
+        <v>5.6</v>
       </c>
       <c r="V5" t="n">
-        <v>0.05092592592592592</v>
+        <v>0.08092485549132949</v>
       </c>
       <c r="W5" t="n">
-        <v>4.666666666666667</v>
+        <v>3.8</v>
       </c>
       <c r="X5" t="n">
-        <v>9.333333333333334</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1296296296296297</v>
+        <v>0.1329479768786127</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.333333333333334</v>
+        <v>7.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>27.66666666666667</v>
+        <v>23.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3842592592592593</v>
+        <v>0.3410404624277457</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.6229508196721312</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.3620689655172414</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.3214285714285715</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.5</v>
+        <v>0.4130434782608696</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3373493975903615</v>
+        <v>0.3050847457627118</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.245901639344262</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.135135135135135</v>
+        <v>1.00609756097561</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.6176470588235293</v>
+        <v>0.7321428571428571</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.052631578947369</v>
+        <v>1.11864406779661</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.444444444444444</v>
+        <v>1.4375</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.435897435897436</v>
+        <v>1.222222222222222</v>
       </c>
       <c r="AO5" t="n">
-        <v>5.538461538461538</v>
+        <v>4.805555555555554</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.974358974358974</v>
+        <v>6.027777777777777</v>
       </c>
     </row>
     <row r="7">
@@ -1419,64 +1419,64 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" t="n">
+        <v>56</v>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="n">
+        <v>17</v>
+      </c>
+      <c r="F8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G8" t="n">
+        <v>30</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="n">
+        <v>15</v>
+      </c>
+      <c r="J8" t="n">
+        <v>14</v>
+      </c>
+      <c r="K8" t="n">
+        <v>7</v>
+      </c>
+      <c r="L8" t="n">
         <v>3</v>
       </c>
-      <c r="C8" t="n">
-        <v>29</v>
-      </c>
-      <c r="D8" t="n">
+      <c r="M8" t="n">
+        <v>2</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
         <v>3</v>
       </c>
-      <c r="E8" t="n">
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
+        <v>12</v>
+      </c>
+      <c r="S8" t="n">
+        <v>12</v>
+      </c>
+      <c r="T8" t="n">
+        <v>49</v>
+      </c>
+      <c r="U8" t="n">
         <v>9</v>
-      </c>
-      <c r="F8" t="n">
-        <v>5</v>
-      </c>
-      <c r="G8" t="n">
-        <v>18</v>
-      </c>
-      <c r="H8" t="n">
-        <v>8</v>
-      </c>
-      <c r="I8" t="n">
-        <v>11</v>
-      </c>
-      <c r="J8" t="n">
-        <v>10</v>
-      </c>
-      <c r="K8" t="n">
-        <v>5</v>
-      </c>
-      <c r="L8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2</v>
-      </c>
-      <c r="R8" t="n">
-        <v>9</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="n">
-        <v>24</v>
-      </c>
-      <c r="U8" t="n">
-        <v>4</v>
       </c>
       <c r="V8" t="n">
         <v>3</v>
@@ -1488,87 +1488,87 @@
         <v>2</v>
       </c>
       <c r="Y8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC8" t="n">
         <v>3</v>
       </c>
-      <c r="AA8" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1</v>
-      </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="AE8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AF8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AH8" t="n">
         <v>5</v>
       </c>
-      <c r="AG8" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AH8" t="n">
+      <c r="AI8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK8" t="n">
         <v>3</v>
       </c>
-      <c r="AI8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>2</v>
-      </c>
       <c r="AL8" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.182</v>
+        <v>0.15</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>72:22</t>
+          <t>116:20</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>33.84</v>
+        <v>56.6</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.389</v>
+        <v>0.468</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.455</v>
+        <v>0.522</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.857</v>
+        <v>0.989</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.059</v>
+        <v>0.053</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.296</v>
+        <v>0.255</v>
       </c>
       <c r="AU8" t="n">
-        <v>5</v>
+        <v>4.667</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.209</v>
+        <v>0.214</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.03</v>
+        <v>0.026</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.063</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.103</v>
+        <v>0.095</v>
       </c>
     </row>
     <row r="9">
@@ -1578,67 +1578,67 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E9" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" t="n">
+        <v>26</v>
+      </c>
+      <c r="H9" t="n">
+        <v>6</v>
+      </c>
+      <c r="I9" t="n">
+        <v>7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>8</v>
+      </c>
+      <c r="K9" t="n">
+        <v>15</v>
+      </c>
+      <c r="L9" t="n">
         <v>5</v>
       </c>
-      <c r="G9" t="n">
-        <v>15</v>
-      </c>
-      <c r="H9" t="n">
-        <v>4</v>
-      </c>
-      <c r="I9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J9" t="n">
+      <c r="M9" t="n">
+        <v>9</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>6</v>
+      </c>
+      <c r="R9" t="n">
+        <v>9</v>
+      </c>
+      <c r="S9" t="n">
+        <v>9</v>
+      </c>
+      <c r="T9" t="n">
+        <v>74</v>
+      </c>
+      <c r="U9" t="n">
         <v>7</v>
       </c>
-      <c r="K9" t="n">
-        <v>12</v>
-      </c>
-      <c r="L9" t="n">
-        <v>4</v>
-      </c>
-      <c r="M9" t="n">
-        <v>5</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>5</v>
-      </c>
-      <c r="R9" t="n">
-        <v>4</v>
-      </c>
-      <c r="S9" t="n">
-        <v>5</v>
-      </c>
-      <c r="T9" t="n">
-        <v>54</v>
-      </c>
-      <c r="U9" t="n">
-        <v>6</v>
-      </c>
       <c r="V9" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="W9" t="n">
         <v>3</v>
@@ -1647,87 +1647,87 @@
         <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA9" t="n">
         <v>1</v>
       </c>
       <c r="AB9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AD9" t="n">
         <v>0.5</v>
       </c>
       <c r="AE9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI9" t="n">
         <v>6</v>
       </c>
-      <c r="AF9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>3</v>
-      </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AK9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AL9" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.417</v>
+        <v>0.45</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>81:44</t>
+          <t>126:28</t>
         </is>
       </c>
       <c r="AO9" t="n">
-        <v>37.76</v>
+        <v>58.08</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.629</v>
+        <v>0.612</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.656</v>
+        <v>0.634</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.139</v>
+        <v>1.136</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.132</v>
+        <v>0.103</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.129</v>
+        <v>0.122</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.4</v>
+        <v>1.333</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.207</v>
+        <v>0.202</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.052</v>
+        <v>0.04</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.147</v>
+        <v>0.124</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.08</v>
+        <v>0.057</v>
       </c>
     </row>
     <row r="10">
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.186</v>
+        <v>0.183</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.031</v>
+        <v>0.029</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.177</v>
+        <v>0.185</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.021</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="11">
@@ -1896,82 +1896,82 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" t="n">
+        <v>50</v>
+      </c>
+      <c r="D11" t="n">
+        <v>13</v>
+      </c>
+      <c r="E11" t="n">
+        <v>20</v>
+      </c>
+      <c r="F11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G11" t="n">
+        <v>15</v>
+      </c>
+      <c r="H11" t="n">
+        <v>9</v>
+      </c>
+      <c r="I11" t="n">
+        <v>10</v>
+      </c>
+      <c r="J11" t="n">
+        <v>7</v>
+      </c>
+      <c r="K11" t="n">
+        <v>13</v>
+      </c>
+      <c r="L11" t="n">
+        <v>7</v>
+      </c>
+      <c r="M11" t="n">
+        <v>6</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
         <v>3</v>
       </c>
-      <c r="C11" t="n">
-        <v>35</v>
-      </c>
-      <c r="D11" t="n">
-        <v>10</v>
-      </c>
-      <c r="E11" t="n">
-        <v>14</v>
-      </c>
-      <c r="F11" t="n">
+      <c r="Q11" t="n">
         <v>3</v>
       </c>
-      <c r="G11" t="n">
+      <c r="R11" t="n">
         <v>6</v>
       </c>
-      <c r="H11" t="n">
-        <v>6</v>
-      </c>
-      <c r="I11" t="n">
-        <v>7</v>
-      </c>
-      <c r="J11" t="n">
-        <v>5</v>
-      </c>
-      <c r="K11" t="n">
-        <v>11</v>
-      </c>
-      <c r="L11" t="n">
-        <v>5</v>
-      </c>
-      <c r="M11" t="n">
-        <v>5</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>3</v>
-      </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T11" t="n">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="U11" t="n">
         <v>7</v>
       </c>
       <c r="V11" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z11" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.769</v>
+        <v>0.722</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -1986,7 +1986,7 @@
         <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -1995,57 +1995,57 @@
         <v>2</v>
       </c>
       <c r="AI11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AK11" t="n">
         <v>3</v>
       </c>
-      <c r="AJ11" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1</v>
-      </c>
       <c r="AL11" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>71:52</t>
+          <t>108:18</t>
         </is>
       </c>
       <c r="AO11" t="n">
-        <v>24.08</v>
+        <v>42.4</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.725</v>
+        <v>0.586</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.758</v>
+        <v>0.635</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.453</v>
+        <v>1.179</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.042</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.3</v>
+        <v>0.257</v>
       </c>
       <c r="AU11" t="n">
-        <v>5</v>
+        <v>2.333</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.15</v>
+        <v>0.172</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.074</v>
+        <v>0.065</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.153</v>
+        <v>0.126</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.054</v>
+        <v>0.047</v>
       </c>
     </row>
     <row r="12">
@@ -2055,156 +2055,156 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" t="n">
+        <v>23</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>14</v>
+      </c>
+      <c r="F12" t="n">
         <v>3</v>
       </c>
-      <c r="C12" t="n">
+      <c r="G12" t="n">
+        <v>18</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" t="n">
+        <v>7</v>
+      </c>
+      <c r="J12" t="n">
+        <v>8</v>
+      </c>
+      <c r="K12" t="n">
+        <v>13</v>
+      </c>
+      <c r="L12" t="n">
+        <v>4</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N12" t="n">
+        <v>5</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>8</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7</v>
+      </c>
+      <c r="S12" t="n">
         <v>11</v>
       </c>
-      <c r="D12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" t="n">
-        <v>8</v>
-      </c>
-      <c r="F12" t="n">
+      <c r="T12" t="n">
+        <v>24</v>
+      </c>
+      <c r="U12" t="n">
+        <v>5</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" t="n">
         <v>2</v>
       </c>
-      <c r="G12" t="n">
-        <v>10</v>
-      </c>
-      <c r="H12" t="n">
+      <c r="X12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" t="n">
         <v>3</v>
       </c>
-      <c r="I12" t="n">
-        <v>4</v>
-      </c>
-      <c r="J12" t="n">
-        <v>4</v>
-      </c>
-      <c r="K12" t="n">
+      <c r="Z12" t="n">
         <v>6</v>
       </c>
-      <c r="L12" t="n">
+      <c r="AA12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
         <v>3</v>
       </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>3</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="AK12" t="n">
         <v>2</v>
       </c>
-      <c r="Q12" t="n">
-        <v>2</v>
-      </c>
-      <c r="R12" t="n">
-        <v>5</v>
-      </c>
-      <c r="S12" t="n">
-        <v>6</v>
-      </c>
-      <c r="T12" t="n">
-        <v>10</v>
-      </c>
-      <c r="U12" t="n">
-        <v>3</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1</v>
-      </c>
       <c r="AL12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.143</v>
+        <v>0.182</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>44:03</t>
+          <t>86:54</t>
         </is>
       </c>
       <c r="AO12" t="n">
-        <v>21.76</v>
+        <v>43.08</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.222</v>
+        <v>0.297</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.278</v>
+        <v>0.328</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.506</v>
+        <v>0.534</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.092</v>
+        <v>0.186</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.167</v>
+        <v>0.125</v>
       </c>
       <c r="AU12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.221</v>
+        <v>0.218</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.073</v>
+        <v>0.046</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.136</v>
+        <v>0.156</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.039</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="13">
@@ -2214,88 +2214,88 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" t="n">
+        <v>38</v>
+      </c>
+      <c r="D13" t="n">
+        <v>11</v>
+      </c>
+      <c r="E13" t="n">
+        <v>25</v>
+      </c>
+      <c r="F13" t="n">
         <v>3</v>
       </c>
-      <c r="C13" t="n">
-        <v>26</v>
-      </c>
-      <c r="D13" t="n">
+      <c r="G13" t="n">
+        <v>9</v>
+      </c>
+      <c r="H13" t="n">
+        <v>7</v>
+      </c>
+      <c r="I13" t="n">
+        <v>11</v>
+      </c>
+      <c r="J13" t="n">
+        <v>17</v>
+      </c>
+      <c r="K13" t="n">
+        <v>19</v>
+      </c>
+      <c r="L13" t="n">
         <v>10</v>
-      </c>
-      <c r="E13" t="n">
-        <v>19</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="n">
-        <v>5</v>
-      </c>
-      <c r="H13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I13" t="n">
-        <v>5</v>
-      </c>
-      <c r="J13" t="n">
-        <v>9</v>
-      </c>
-      <c r="K13" t="n">
-        <v>12</v>
-      </c>
-      <c r="L13" t="n">
-        <v>4</v>
       </c>
       <c r="M13" t="n">
         <v>4</v>
       </c>
       <c r="N13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="R13" t="n">
+        <v>11</v>
+      </c>
+      <c r="S13" t="n">
         <v>9</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
+        <v>57</v>
+      </c>
+      <c r="U13" t="n">
         <v>5</v>
-      </c>
-      <c r="T13" t="n">
-        <v>34</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1</v>
       </c>
       <c r="V13" t="n">
         <v>7</v>
       </c>
       <c r="W13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z13" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.667</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2304,66 +2304,66 @@
         <v>1</v>
       </c>
       <c r="AF13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG13" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AK13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>55:07</t>
+          <t>98:49</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>30.2</v>
+        <v>47.84</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.479</v>
+        <v>0.456</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.496</v>
+        <v>0.489</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.861</v>
+        <v>0.794</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.132</v>
+        <v>0.188</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.125</v>
+        <v>0.206</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.25</v>
+        <v>1.889</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.245</v>
+        <v>0.213</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.078</v>
+        <v>0.101</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.218</v>
+        <v>0.201</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.096</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="14">
@@ -2373,156 +2373,156 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
+        <v>17</v>
+      </c>
+      <c r="E14" t="n">
+        <v>27</v>
+      </c>
+      <c r="F14" t="n">
+        <v>13</v>
+      </c>
+      <c r="G14" t="n">
+        <v>31</v>
+      </c>
+      <c r="H14" t="n">
         <v>15</v>
       </c>
-      <c r="E14" t="n">
-        <v>18</v>
-      </c>
-      <c r="F14" t="n">
+      <c r="I14" t="n">
+        <v>16</v>
+      </c>
+      <c r="J14" t="n">
+        <v>29</v>
+      </c>
+      <c r="K14" t="n">
+        <v>10</v>
+      </c>
+      <c r="L14" t="n">
         <v>5</v>
       </c>
-      <c r="G14" t="n">
+      <c r="M14" t="n">
+        <v>7</v>
+      </c>
+      <c r="N14" t="n">
+        <v>5</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>11</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7</v>
+      </c>
+      <c r="S14" t="n">
+        <v>24</v>
+      </c>
+      <c r="T14" t="n">
+        <v>121</v>
+      </c>
+      <c r="U14" t="n">
+        <v>20</v>
+      </c>
+      <c r="V14" t="n">
         <v>15</v>
       </c>
-      <c r="H14" t="n">
-        <v>8</v>
-      </c>
-      <c r="I14" t="n">
-        <v>8</v>
-      </c>
-      <c r="J14" t="n">
-        <v>18</v>
-      </c>
-      <c r="K14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L14" t="n">
-        <v>2</v>
-      </c>
-      <c r="M14" t="n">
-        <v>3</v>
-      </c>
-      <c r="N14" t="n">
-        <v>2</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>8</v>
-      </c>
-      <c r="R14" t="n">
-        <v>3</v>
-      </c>
-      <c r="S14" t="n">
-        <v>12</v>
-      </c>
-      <c r="T14" t="n">
-        <v>68</v>
-      </c>
-      <c r="U14" t="n">
-        <v>10</v>
-      </c>
-      <c r="V14" t="n">
-        <v>12</v>
-      </c>
       <c r="W14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.9</v>
+        <v>0.733</v>
       </c>
       <c r="AB14" t="n">
         <v>4</v>
       </c>
       <c r="AC14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="AE14" t="n">
         <v>2</v>
       </c>
       <c r="AF14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI14" t="n">
         <v>3</v>
       </c>
-      <c r="AG14" t="n">
+      <c r="AJ14" t="n">
         <v>0.667</v>
       </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
       <c r="AK14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AL14" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.333</v>
+        <v>0.393</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>79:08</t>
+          <t>129:40</t>
         </is>
       </c>
       <c r="AO14" t="n">
-        <v>44.52</v>
+        <v>76.04000000000001</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.629</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.726</v>
+        <v>0.677</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.19</v>
+        <v>1.157</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.18</v>
+        <v>0.145</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.242</v>
+        <v>0.259</v>
       </c>
       <c r="AU14" t="n">
-        <v>2.25</v>
+        <v>2.636</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.252</v>
+        <v>0.258</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.027</v>
+        <v>0.039</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.025</v>
+        <v>0.081</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.212</v>
+        <v>0.213</v>
       </c>
     </row>
     <row r="15">
@@ -2532,67 +2532,67 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C15" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F15" t="n">
         <v>4</v>
       </c>
       <c r="G15" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="H15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I15" t="n">
+        <v>6</v>
+      </c>
+      <c r="J15" t="n">
         <v>4</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
+        <v>11</v>
+      </c>
+      <c r="L15" t="n">
+        <v>5</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
         <v>2</v>
       </c>
-      <c r="K15" t="n">
-        <v>9</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1</v>
-      </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S15" t="n">
+        <v>6</v>
+      </c>
+      <c r="T15" t="n">
+        <v>21</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" t="n">
         <v>5</v>
-      </c>
-      <c r="T15" t="n">
-        <v>20</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>3</v>
       </c>
       <c r="W15" t="n">
         <v>3</v>
@@ -2601,87 +2601,87 @@
         <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA15" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="AB15" t="n">
         <v>1</v>
       </c>
       <c r="AC15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AH15" t="n">
         <v>1</v>
       </c>
       <c r="AI15" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="AK15" t="n">
         <v>3</v>
       </c>
       <c r="AL15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AM15" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>85:34</t>
+        </is>
+      </c>
+      <c r="AO15" t="n">
+        <v>36.64</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0.419</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0.218</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="AU15" t="n">
         <v>0.5</v>
       </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>55:14</t>
-        </is>
-      </c>
-      <c r="AO15" t="n">
-        <v>21.76</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>0.644</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>0.873</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>0.322</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>0.231</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>0.286</v>
-      </c>
       <c r="AV15" t="n">
-        <v>0.176</v>
+        <v>0.188</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.019</v>
+        <v>0.058</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.163</v>
+        <v>0.134</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.02</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="16">
@@ -2691,16 +2691,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E16" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2709,25 +2709,25 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I16" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L16" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2739,19 +2739,19 @@
         <v>2</v>
       </c>
       <c r="R16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="n">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="U16" t="n">
+        <v>9</v>
+      </c>
+      <c r="V16" t="n">
         <v>4</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>5</v>
@@ -2760,22 +2760,22 @@
         <v>4</v>
       </c>
       <c r="Y16" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="Z16" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.789</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2806,41 +2806,41 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>56:39</t>
+          <t>91:38</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>21.52</v>
+        <v>30.72</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.696</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.538</v>
+        <v>0.627</v>
       </c>
       <c r="AR16" t="n">
-        <v>0.976</v>
+        <v>1.172</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.093</v>
+        <v>0.065</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.188</v>
+        <v>0.174</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.17</v>
+        <v>0.147</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.189</v>
+        <v>0.153</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.229</v>
+        <v>0.194</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.01</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="17">
@@ -2850,7 +2850,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -3009,22 +3009,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C18" t="n">
+        <v>28</v>
+      </c>
+      <c r="D18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E18" t="n">
+        <v>11</v>
+      </c>
+      <c r="F18" t="n">
+        <v>6</v>
+      </c>
+      <c r="G18" t="n">
         <v>12</v>
-      </c>
-      <c r="D18" t="n">
-        <v>2</v>
-      </c>
-      <c r="E18" t="n">
-        <v>8</v>
-      </c>
-      <c r="F18" t="n">
-        <v>2</v>
-      </c>
-      <c r="G18" t="n">
-        <v>5</v>
       </c>
       <c r="H18" t="n">
         <v>2</v>
@@ -3033,132 +3033,132 @@
         <v>2</v>
       </c>
       <c r="J18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K18" t="n">
+        <v>3</v>
+      </c>
+      <c r="L18" t="n">
+        <v>3</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>4</v>
+      </c>
+      <c r="R18" t="n">
+        <v>14</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="n">
+        <v>18</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
+      </c>
+      <c r="V18" t="n">
+        <v>5</v>
+      </c>
+      <c r="W18" t="n">
+        <v>5</v>
+      </c>
+      <c r="X18" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK18" t="n">
         <v>2</v>
       </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3</v>
-      </c>
-      <c r="R18" t="n">
-        <v>5</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>10</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
+      <c r="AL18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>72:07</t>
+        </is>
+      </c>
+      <c r="AO18" t="n">
+        <v>27.88</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.004</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="AU18" t="n">
         <v>2</v>
       </c>
-      <c r="X18" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>44:08</t>
-        </is>
-      </c>
-      <c r="AO18" t="n">
-        <v>16.88</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>0.432</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>0.711</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0.178</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>2.333</v>
-      </c>
       <c r="AV18" t="n">
-        <v>0.171</v>
+        <v>0.17</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.024</v>
+        <v>0.042</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.045</v>
+        <v>0.044</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="19">
@@ -3168,82 +3168,82 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E19" t="n">
+        <v>6</v>
+      </c>
+      <c r="F19" t="n">
+        <v>4</v>
+      </c>
+      <c r="G19" t="n">
+        <v>15</v>
+      </c>
+      <c r="H19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4</v>
+      </c>
+      <c r="J19" t="n">
+        <v>5</v>
+      </c>
+      <c r="K19" t="n">
+        <v>9</v>
+      </c>
+      <c r="L19" t="n">
+        <v>6</v>
+      </c>
+      <c r="M19" t="n">
+        <v>5</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>5</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4</v>
+      </c>
+      <c r="T19" t="n">
+        <v>34</v>
+      </c>
+      <c r="U19" t="n">
         <v>2</v>
-      </c>
-      <c r="E19" t="n">
-        <v>2</v>
-      </c>
-      <c r="F19" t="n">
-        <v>3</v>
-      </c>
-      <c r="G19" t="n">
-        <v>7</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>2</v>
-      </c>
-      <c r="L19" t="n">
-        <v>2</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1</v>
-      </c>
-      <c r="T19" t="n">
-        <v>15</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
       </c>
       <c r="V19" t="n">
         <v>2</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AA19" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -3273,51 +3273,51 @@
         <v>0.333</v>
       </c>
       <c r="AK19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL19" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>22:15</t>
+          <t>58:31</t>
         </is>
       </c>
       <c r="AO19" t="n">
-        <v>9</v>
+        <v>23.76</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.722</v>
+        <v>0.476</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.722</v>
+        <v>0.527</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.444</v>
+        <v>1.01</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>0.042</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.181</v>
+        <v>0.179</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.096</v>
+        <v>0.103</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.09</v>
+        <v>0.161</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.01</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="20">
@@ -3486,40 +3486,40 @@
         </is>
       </c>
       <c r="B21" t="n">
+        <v>4</v>
+      </c>
+      <c r="C21" t="n">
+        <v>8</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>6</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
         <v>2</v>
       </c>
-      <c r="C21" t="n">
+      <c r="I21" t="n">
         <v>2</v>
       </c>
-      <c r="D21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" t="n">
-        <v>3</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L21" t="n">
         <v>2</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -3534,16 +3534,16 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V21" t="n">
         <v>2</v>
@@ -3555,13 +3555,13 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -3601,38 +3601,38 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="AO21" t="n">
-        <v>4</v>
+        <v>7.88</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.25</v>
+        <v>0.429</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.25</v>
+        <v>0.508</v>
       </c>
       <c r="AR21" t="n">
-        <v>0.5</v>
+        <v>1.015</v>
       </c>
       <c r="AS21" t="n">
         <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>0.286</v>
       </c>
       <c r="AU21" t="n">
         <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.159</v>
+        <v>0.172</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.189</v>
+        <v>0.099</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>0.104</v>
       </c>
       <c r="AY21" t="n">
         <v>0</v>
@@ -3645,7 +3645,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -3672,10 +3672,10 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="L22" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -3687,7 +3687,7 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3804,153 +3804,153 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C23" t="n">
-        <v>289</v>
+        <v>466</v>
       </c>
       <c r="D23" t="n">
+        <v>107</v>
+      </c>
+      <c r="E23" t="n">
+        <v>188</v>
+      </c>
+      <c r="F23" t="n">
+        <v>59</v>
+      </c>
+      <c r="G23" t="n">
+        <v>178</v>
+      </c>
+      <c r="H23" t="n">
+        <v>75</v>
+      </c>
+      <c r="I23" t="n">
+        <v>100</v>
+      </c>
+      <c r="J23" t="n">
+        <v>104</v>
+      </c>
+      <c r="K23" t="n">
+        <v>137</v>
+      </c>
+      <c r="L23" t="n">
+        <v>74</v>
+      </c>
+      <c r="M23" t="n">
+        <v>42</v>
+      </c>
+      <c r="N23" t="n">
+        <v>30</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>55</v>
+      </c>
+      <c r="R23" t="n">
+        <v>94</v>
+      </c>
+      <c r="S23" t="n">
+        <v>106</v>
+      </c>
+      <c r="T23" t="n">
+        <v>584</v>
+      </c>
+      <c r="U23" t="n">
+        <v>74</v>
+      </c>
+      <c r="V23" t="n">
         <v>72</v>
       </c>
-      <c r="E23" t="n">
-        <v>123</v>
-      </c>
-      <c r="F23" t="n">
-        <v>33</v>
-      </c>
-      <c r="G23" t="n">
-        <v>96</v>
-      </c>
-      <c r="H23" t="n">
-        <v>46</v>
-      </c>
-      <c r="I23" t="n">
-        <v>60</v>
-      </c>
-      <c r="J23" t="n">
-        <v>66</v>
-      </c>
-      <c r="K23" t="n">
-        <v>87</v>
-      </c>
-      <c r="L23" t="n">
-        <v>40</v>
-      </c>
-      <c r="M23" t="n">
-        <v>23</v>
-      </c>
-      <c r="N23" t="n">
-        <v>17</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>34</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>34</v>
-      </c>
-      <c r="R23" t="n">
-        <v>57</v>
-      </c>
-      <c r="S23" t="n">
-        <v>64</v>
-      </c>
-      <c r="T23" t="n">
-        <v>367</v>
-      </c>
-      <c r="U23" t="n">
-        <v>37</v>
-      </c>
-      <c r="V23" t="n">
-        <v>46</v>
-      </c>
       <c r="W23" t="n">
+        <v>41</v>
+      </c>
+      <c r="X23" t="n">
         <v>24</v>
       </c>
-      <c r="X23" t="n">
+      <c r="Y23" t="n">
+        <v>73</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>105</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="AB23" t="n">
         <v>16</v>
       </c>
-      <c r="Y23" t="n">
-        <v>50</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>72</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0.694</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>10</v>
-      </c>
       <c r="AC23" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.357</v>
+        <v>0.39</v>
       </c>
       <c r="AE23" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AF23" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.522</v>
+        <v>0.429</v>
       </c>
       <c r="AH23" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AI23" t="n">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.37</v>
+        <v>0.346</v>
       </c>
       <c r="AK23" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="AL23" t="n">
-        <v>69</v>
+        <v>126</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.333</v>
+        <v>0.325</v>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>625:00</t>
+          <t>1025:00</t>
         </is>
       </c>
       <c r="AO23" t="n">
-        <v>279.4</v>
+        <v>466</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.555</v>
+        <v>0.534</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.589</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.034</v>
+        <v>1</v>
       </c>
       <c r="AS23" t="n">
-        <v>0.122</v>
+        <v>0.12</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.21</v>
+        <v>0.205</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.941</v>
+        <v>1.857</v>
       </c>
       <c r="AV23" t="n">
         <v>0.2</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.068</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.139</v>
+        <v>0.14</v>
       </c>
       <c r="AY23" t="n">
         <v>0</v>
@@ -3963,153 +3963,153 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C24" t="n">
-        <v>268</v>
+        <v>419</v>
       </c>
       <c r="D24" t="n">
-        <v>49</v>
+        <v>94</v>
       </c>
       <c r="E24" t="n">
-        <v>105</v>
+        <v>182</v>
       </c>
       <c r="F24" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G24" t="n">
-        <v>111</v>
+        <v>164</v>
       </c>
       <c r="H24" t="n">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="I24" t="n">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="J24" t="n">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="K24" t="n">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="L24" t="n">
+        <v>59</v>
+      </c>
+      <c r="M24" t="n">
         <v>38</v>
       </c>
-      <c r="M24" t="n">
-        <v>25</v>
-      </c>
       <c r="N24" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="Q24" t="n">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="R24" t="n">
+        <v>107</v>
+      </c>
+      <c r="S24" t="n">
+        <v>93</v>
+      </c>
+      <c r="T24" t="n">
+        <v>463</v>
+      </c>
+      <c r="U24" t="n">
+        <v>41</v>
+      </c>
+      <c r="V24" t="n">
+        <v>66</v>
+      </c>
+      <c r="W24" t="n">
+        <v>23</v>
+      </c>
+      <c r="X24" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y24" t="n">
         <v>64</v>
       </c>
-      <c r="S24" t="n">
-        <v>57</v>
-      </c>
-      <c r="T24" t="n">
-        <v>297</v>
-      </c>
-      <c r="U24" t="n">
+      <c r="Z24" t="n">
+        <v>96</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AB24" t="n">
         <v>21</v>
       </c>
-      <c r="V24" t="n">
-        <v>40</v>
-      </c>
-      <c r="W24" t="n">
-        <v>13</v>
-      </c>
-      <c r="X24" t="n">
+      <c r="AC24" t="n">
+        <v>58</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="AE24" t="n">
         <v>9</v>
       </c>
-      <c r="Y24" t="n">
-        <v>38</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>61</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0.623</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>33</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0.273</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>2</v>
-      </c>
       <c r="AF24" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.182</v>
+        <v>0.321</v>
       </c>
       <c r="AH24" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AI24" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.5</v>
+        <v>0.413</v>
       </c>
       <c r="AK24" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AL24" t="n">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.337</v>
+        <v>0.305</v>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>625:00</t>
+          <t>1025:00</t>
         </is>
       </c>
       <c r="AO24" t="n">
-        <v>280.08</v>
+        <v>454.96</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.519</v>
+        <v>0.51</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.556</v>
+        <v>0.547</v>
       </c>
       <c r="AR24" t="n">
-        <v>0.957</v>
+        <v>0.921</v>
       </c>
       <c r="AS24" t="n">
-        <v>0.139</v>
+        <v>0.158</v>
       </c>
       <c r="AT24" t="n">
-        <v>0.204</v>
+        <v>0.191</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.436</v>
+        <v>1.222</v>
       </c>
       <c r="AV24" t="n">
         <v>0.2</v>
       </c>
       <c r="AW24" t="n">
-        <v>0.061</v>
+        <v>0.06</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.132</v>
+        <v>0.128</v>
       </c>
       <c r="AY24" t="n">
         <v>0</v>
@@ -4179,156 +4179,156 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>9.667</v>
+        <v>11.2</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="F26" t="n">
-        <v>1.667</v>
+        <v>1.6</v>
       </c>
       <c r="G26" t="n">
         <v>6</v>
       </c>
       <c r="H26" t="n">
-        <v>2.667</v>
+        <v>2.4</v>
       </c>
       <c r="I26" t="n">
-        <v>3.667</v>
+        <v>3</v>
       </c>
       <c r="J26" t="n">
-        <v>3.333</v>
+        <v>2.8</v>
       </c>
       <c r="K26" t="n">
-        <v>1.667</v>
+        <v>1.4</v>
       </c>
       <c r="L26" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T26" t="n">
+        <v>49</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AD26" t="n">
         <v>0.667</v>
       </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="R26" t="n">
-        <v>3</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3.333</v>
-      </c>
-      <c r="T26" t="n">
-        <v>24</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0</v>
-      </c>
       <c r="AE26" t="n">
-        <v>0.667</v>
+        <v>1.2</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.667</v>
+        <v>2</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="AH26" t="n">
         <v>1</v>
       </c>
       <c r="AI26" t="n">
-        <v>2.333</v>
+        <v>2</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.429</v>
+        <v>0.5</v>
       </c>
       <c r="AK26" t="n">
-        <v>0.667</v>
+        <v>0.6</v>
       </c>
       <c r="AL26" t="n">
-        <v>3.667</v>
+        <v>4</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.182</v>
+        <v>0.15</v>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>24:07</t>
+          <t>23:16</t>
         </is>
       </c>
       <c r="AO26" t="n">
-        <v>11.28</v>
+        <v>11.32</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.389</v>
+        <v>0.468</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.455</v>
+        <v>0.522</v>
       </c>
       <c r="AR26" t="n">
-        <v>0.857</v>
+        <v>0.989</v>
       </c>
       <c r="AS26" t="n">
-        <v>0.059</v>
+        <v>0.053</v>
       </c>
       <c r="AT26" t="n">
-        <v>0.296</v>
+        <v>0.255</v>
       </c>
       <c r="AU26" t="n">
-        <v>5</v>
+        <v>4.667</v>
       </c>
       <c r="AV26" t="n">
-        <v>0.209</v>
+        <v>0.214</v>
       </c>
       <c r="AW26" t="n">
-        <v>0.03</v>
+        <v>0.026</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.063</v>
       </c>
       <c r="AY26" t="n">
-        <v>0.103</v>
+        <v>0.095</v>
       </c>
     </row>
     <row r="27">
@@ -4338,156 +4338,156 @@
         </is>
       </c>
       <c r="B27" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="D27" t="n">
         <v>3</v>
       </c>
-      <c r="C27" t="n">
-        <v>14.333</v>
-      </c>
-      <c r="D27" t="n">
-        <v>4</v>
-      </c>
       <c r="E27" t="n">
-        <v>5.333</v>
+        <v>4.6</v>
       </c>
       <c r="F27" t="n">
-        <v>1.667</v>
+        <v>2</v>
       </c>
       <c r="G27" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="H27" t="n">
-        <v>1.333</v>
+        <v>1.2</v>
       </c>
       <c r="I27" t="n">
-        <v>1.333</v>
+        <v>1.4</v>
       </c>
       <c r="J27" t="n">
-        <v>2.333</v>
+        <v>1.6</v>
       </c>
       <c r="K27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L27" t="n">
-        <v>1.333</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>1.667</v>
+        <v>1.8</v>
       </c>
       <c r="N27" t="n">
-        <v>0.333</v>
+        <v>0.4</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.667</v>
+        <v>1.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.667</v>
+        <v>1.2</v>
       </c>
       <c r="R27" t="n">
-        <v>1.333</v>
+        <v>1.8</v>
       </c>
       <c r="S27" t="n">
-        <v>1.667</v>
+        <v>1.8</v>
       </c>
       <c r="T27" t="n">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="U27" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="V27" t="n">
-        <v>1.667</v>
+        <v>2.2</v>
       </c>
       <c r="W27" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="X27" t="n">
-        <v>0.333</v>
+        <v>0.2</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.333</v>
+        <v>1</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.333</v>
+        <v>1</v>
       </c>
       <c r="AA27" t="n">
         <v>1</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.667</v>
+        <v>0.6</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.333</v>
+        <v>1.2</v>
       </c>
       <c r="AD27" t="n">
         <v>0.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.667</v>
+        <v>2.4</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.75</v>
+        <v>0.583</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AI27" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.667</v>
+        <v>1.8</v>
       </c>
       <c r="AL27" t="n">
         <v>4</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.417</v>
+        <v>0.45</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>27:14</t>
+          <t>25:17</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>12.587</v>
+        <v>11.616</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.629</v>
+        <v>0.612</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.656</v>
+        <v>0.634</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.139</v>
+        <v>1.136</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.132</v>
+        <v>0.103</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.129</v>
+        <v>0.122</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.4</v>
+        <v>1.333</v>
       </c>
       <c r="AV27" t="n">
-        <v>0.207</v>
+        <v>0.202</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.052</v>
+        <v>0.04</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.147</v>
+        <v>0.124</v>
       </c>
       <c r="AY27" t="n">
-        <v>0.08</v>
+        <v>0.057</v>
       </c>
     </row>
     <row r="28">
@@ -4637,16 +4637,16 @@
         <v>0</v>
       </c>
       <c r="AV28" t="n">
-        <v>0.186</v>
+        <v>0.183</v>
       </c>
       <c r="AW28" t="n">
-        <v>0.031</v>
+        <v>0.029</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.177</v>
+        <v>0.185</v>
       </c>
       <c r="AY28" t="n">
-        <v>0.021</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="29">
@@ -4656,156 +4656,156 @@
         </is>
       </c>
       <c r="B29" t="n">
+        <v>5</v>
+      </c>
+      <c r="C29" t="n">
+        <v>10</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E29" t="n">
+        <v>4</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="n">
         <v>3</v>
       </c>
-      <c r="C29" t="n">
-        <v>11.667</v>
-      </c>
-      <c r="D29" t="n">
-        <v>3.333</v>
-      </c>
-      <c r="E29" t="n">
-        <v>4.667</v>
-      </c>
-      <c r="F29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I29" t="n">
         <v>2</v>
       </c>
-      <c r="H29" t="n">
+      <c r="J29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T29" t="n">
+        <v>69</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AL29" t="n">
         <v>2</v>
       </c>
-      <c r="I29" t="n">
+      <c r="AM29" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AN29" t="inlineStr">
+        <is>
+          <t>21:39</t>
+        </is>
+      </c>
+      <c r="AO29" t="n">
+        <v>8.48</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1.179</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0.257</v>
+      </c>
+      <c r="AU29" t="n">
         <v>2.333</v>
       </c>
-      <c r="J29" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="K29" t="n">
-        <v>3.667</v>
-      </c>
-      <c r="L29" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T29" t="n">
-        <v>57</v>
-      </c>
-      <c r="U29" t="n">
-        <v>2.333</v>
-      </c>
-      <c r="V29" t="n">
-        <v>2</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>3.333</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0.769</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>23:57</t>
-        </is>
-      </c>
-      <c r="AO29" t="n">
-        <v>8.026999999999999</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>0.758</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>1.453</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>5</v>
-      </c>
       <c r="AV29" t="n">
-        <v>0.15</v>
+        <v>0.172</v>
       </c>
       <c r="AW29" t="n">
-        <v>0.074</v>
+        <v>0.065</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.153</v>
+        <v>0.126</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.054</v>
+        <v>0.047</v>
       </c>
     </row>
     <row r="30">
@@ -4815,40 +4815,40 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>3.667</v>
+        <v>4.6</v>
       </c>
       <c r="D30" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>2.667</v>
+        <v>2.8</v>
       </c>
       <c r="F30" t="n">
-        <v>0.667</v>
+        <v>0.6</v>
       </c>
       <c r="G30" t="n">
-        <v>3.333</v>
+        <v>3.6</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="I30" t="n">
-        <v>1.333</v>
+        <v>1.4</v>
       </c>
       <c r="J30" t="n">
-        <v>1.333</v>
+        <v>1.6</v>
       </c>
       <c r="K30" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="N30" t="n">
         <v>1</v>
@@ -4857,114 +4857,114 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>0.667</v>
+        <v>1.6</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.667</v>
+        <v>1.6</v>
       </c>
       <c r="R30" t="n">
-        <v>1.667</v>
+        <v>1.4</v>
       </c>
       <c r="S30" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="T30" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="U30" t="n">
         <v>1</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="Z30" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.333</v>
+        <v>0.4</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.333</v>
+        <v>1</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.333</v>
+        <v>0.6</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.333</v>
+        <v>0.2</v>
       </c>
       <c r="AI30" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.333</v>
+        <v>0.143</v>
       </c>
       <c r="AK30" t="n">
-        <v>0.333</v>
+        <v>0.4</v>
       </c>
       <c r="AL30" t="n">
-        <v>2.333</v>
+        <v>2.2</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.143</v>
+        <v>0.182</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>7.253</v>
+        <v>8.616</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.222</v>
+        <v>0.297</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.278</v>
+        <v>0.328</v>
       </c>
       <c r="AR30" t="n">
-        <v>0.506</v>
+        <v>0.534</v>
       </c>
       <c r="AS30" t="n">
-        <v>0.092</v>
+        <v>0.186</v>
       </c>
       <c r="AT30" t="n">
-        <v>0.167</v>
+        <v>0.125</v>
       </c>
       <c r="AU30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.221</v>
+        <v>0.218</v>
       </c>
       <c r="AW30" t="n">
-        <v>0.073</v>
+        <v>0.046</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.136</v>
+        <v>0.156</v>
       </c>
       <c r="AY30" t="n">
-        <v>0.039</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="31">
@@ -4974,156 +4974,156 @@
         </is>
       </c>
       <c r="B31" t="n">
+        <v>5</v>
+      </c>
+      <c r="C31" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E31" t="n">
+        <v>5</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L31" t="n">
+        <v>2</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T31" t="n">
+        <v>57</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z31" t="n">
         <v>3</v>
       </c>
-      <c r="C31" t="n">
-        <v>8.667</v>
-      </c>
-      <c r="D31" t="n">
-        <v>3.333</v>
-      </c>
-      <c r="E31" t="n">
-        <v>6.333</v>
-      </c>
-      <c r="F31" t="n">
+      <c r="AA31" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AJ31" t="n">
         <v>0.333</v>
       </c>
-      <c r="G31" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="H31" t="n">
-        <v>1</v>
-      </c>
-      <c r="I31" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="J31" t="n">
-        <v>3</v>
-      </c>
-      <c r="K31" t="n">
-        <v>4</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="M31" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="R31" t="n">
-        <v>3</v>
-      </c>
-      <c r="S31" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="T31" t="n">
-        <v>34</v>
-      </c>
-      <c r="U31" t="n">
+      <c r="AK31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AM31" t="n">
         <v>0.333</v>
       </c>
-      <c r="V31" t="n">
-        <v>2.333</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0.6919999999999999</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>0.25</v>
-      </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>10.067</v>
+        <v>9.568</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.479</v>
+        <v>0.456</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.496</v>
+        <v>0.489</v>
       </c>
       <c r="AR31" t="n">
-        <v>0.861</v>
+        <v>0.794</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.132</v>
+        <v>0.188</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.125</v>
+        <v>0.206</v>
       </c>
       <c r="AU31" t="n">
-        <v>2.25</v>
+        <v>1.889</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.245</v>
+        <v>0.213</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.078</v>
+        <v>0.101</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.218</v>
+        <v>0.201</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.096</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="32">
@@ -5133,156 +5133,156 @@
         </is>
       </c>
       <c r="B32" t="n">
+        <v>5</v>
+      </c>
+      <c r="C32" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="D32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G32" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H32" t="n">
         <v>3</v>
       </c>
-      <c r="C32" t="n">
-        <v>17.667</v>
-      </c>
-      <c r="D32" t="n">
-        <v>5</v>
-      </c>
-      <c r="E32" t="n">
-        <v>6</v>
-      </c>
-      <c r="F32" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="G32" t="n">
-        <v>5</v>
-      </c>
-      <c r="H32" t="n">
-        <v>2.667</v>
-      </c>
       <c r="I32" t="n">
-        <v>2.667</v>
+        <v>3.2</v>
       </c>
       <c r="J32" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="K32" t="n">
+        <v>2</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T32" t="n">
+        <v>121</v>
+      </c>
+      <c r="U32" t="n">
+        <v>4</v>
+      </c>
+      <c r="V32" t="n">
+        <v>3</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD32" t="n">
         <v>0.667</v>
       </c>
-      <c r="L32" t="n">
+      <c r="AE32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AJ32" t="n">
         <v>0.667</v>
       </c>
-      <c r="M32" t="n">
-        <v>1</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>2.667</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>2.667</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1</v>
-      </c>
-      <c r="S32" t="n">
-        <v>4</v>
-      </c>
-      <c r="T32" t="n">
-        <v>68</v>
-      </c>
-      <c r="U32" t="n">
-        <v>3.333</v>
-      </c>
-      <c r="V32" t="n">
-        <v>4</v>
-      </c>
-      <c r="W32" t="n">
-        <v>2.333</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>3.333</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>0</v>
-      </c>
       <c r="AK32" t="n">
-        <v>1.667</v>
+        <v>2.2</v>
       </c>
       <c r="AL32" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.333</v>
+        <v>0.393</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>26:22</t>
+          <t>25:56</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>14.84</v>
+        <v>15.208</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.629</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.726</v>
+        <v>0.677</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.19</v>
+        <v>1.157</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.18</v>
+        <v>0.145</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.242</v>
+        <v>0.259</v>
       </c>
       <c r="AU32" t="n">
-        <v>2.25</v>
+        <v>2.636</v>
       </c>
       <c r="AV32" t="n">
-        <v>0.252</v>
+        <v>0.258</v>
       </c>
       <c r="AW32" t="n">
-        <v>0.027</v>
+        <v>0.039</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.025</v>
+        <v>0.081</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.212</v>
+        <v>0.213</v>
       </c>
     </row>
     <row r="33">
@@ -5292,156 +5292,156 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C33" t="n">
-        <v>6.333</v>
+        <v>4.8</v>
       </c>
       <c r="D33" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T33" t="n">
+        <v>21</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA33" t="n">
         <v>0.667</v>
       </c>
-      <c r="E33" t="n">
-        <v>1</v>
-      </c>
-      <c r="F33" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="G33" t="n">
-        <v>3.333</v>
-      </c>
-      <c r="H33" t="n">
-        <v>1</v>
-      </c>
-      <c r="I33" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="K33" t="n">
-        <v>3</v>
-      </c>
-      <c r="L33" t="n">
+      <c r="AB33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AD33" t="n">
         <v>0.333</v>
       </c>
-      <c r="M33" t="n">
+      <c r="AE33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AG33" t="n">
         <v>0.333</v>
       </c>
-      <c r="N33" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2.333</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>2.333</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1</v>
-      </c>
-      <c r="S33" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="T33" t="n">
-        <v>20</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AD33" t="n">
+      <c r="AH33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="AN33" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AO33" t="n">
+        <v>7.328</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0.419</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0.218</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="AU33" t="n">
         <v>0.5</v>
       </c>
-      <c r="AE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>18:24</t>
-        </is>
-      </c>
-      <c r="AO33" t="n">
-        <v>7.253</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>0.644</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>0.873</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>0.322</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>0.231</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>0.286</v>
-      </c>
       <c r="AV33" t="n">
-        <v>0.176</v>
+        <v>0.188</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.019</v>
+        <v>0.058</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.163</v>
+        <v>0.134</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.02</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="34">
@@ -5451,16 +5451,16 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C34" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="E34" t="n">
-        <v>5.333</v>
+        <v>4.6</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -5469,73 +5469,73 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="I34" t="n">
-        <v>2.667</v>
+        <v>2.6</v>
       </c>
       <c r="J34" t="n">
-        <v>0.333</v>
+        <v>0.4</v>
       </c>
       <c r="K34" t="n">
-        <v>4.333</v>
+        <v>3.4</v>
       </c>
       <c r="L34" t="n">
-        <v>3.333</v>
+        <v>2.8</v>
       </c>
       <c r="M34" t="n">
-        <v>0.333</v>
+        <v>0.4</v>
       </c>
       <c r="N34" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0.667</v>
+        <v>0.4</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.667</v>
+        <v>0.4</v>
       </c>
       <c r="R34" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S34" t="n">
         <v>2</v>
       </c>
-      <c r="S34" t="n">
-        <v>1.667</v>
-      </c>
       <c r="T34" t="n">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="U34" t="n">
-        <v>1.333</v>
+        <v>1.8</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="W34" t="n">
-        <v>1.667</v>
+        <v>1</v>
       </c>
       <c r="X34" t="n">
-        <v>1.333</v>
+        <v>0.8</v>
       </c>
       <c r="Y34" t="n">
         <v>3</v>
       </c>
       <c r="Z34" t="n">
-        <v>4.333</v>
+        <v>3.8</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.789</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AC34" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -5566,41 +5566,41 @@
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>7.173</v>
+        <v>6.144</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.696</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.538</v>
+        <v>0.627</v>
       </c>
       <c r="AR34" t="n">
-        <v>0.976</v>
+        <v>1.172</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.093</v>
+        <v>0.065</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.188</v>
+        <v>0.174</v>
       </c>
       <c r="AU34" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AV34" t="n">
-        <v>0.17</v>
+        <v>0.147</v>
       </c>
       <c r="AW34" t="n">
-        <v>0.189</v>
+        <v>0.153</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.229</v>
+        <v>0.194</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.01</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="35">
@@ -5610,7 +5610,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -5769,156 +5769,156 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C36" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="D36" t="n">
-        <v>0.667</v>
+        <v>0.8</v>
       </c>
       <c r="E36" t="n">
-        <v>2.667</v>
+        <v>2.2</v>
       </c>
       <c r="F36" t="n">
-        <v>0.667</v>
+        <v>1.2</v>
       </c>
       <c r="G36" t="n">
-        <v>1.667</v>
+        <v>2.4</v>
       </c>
       <c r="H36" t="n">
-        <v>0.667</v>
+        <v>0.4</v>
       </c>
       <c r="I36" t="n">
-        <v>0.667</v>
+        <v>0.4</v>
       </c>
       <c r="J36" t="n">
-        <v>2.333</v>
+        <v>1.6</v>
       </c>
       <c r="K36" t="n">
-        <v>0.667</v>
+        <v>0.6</v>
       </c>
       <c r="L36" t="n">
-        <v>0.333</v>
+        <v>0.6</v>
       </c>
       <c r="M36" t="n">
-        <v>0.333</v>
+        <v>0.2</v>
       </c>
       <c r="N36" t="n">
-        <v>0.333</v>
+        <v>0.2</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="R36" t="n">
-        <v>1.667</v>
+        <v>2.8</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
       </c>
       <c r="T36" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W36" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="X36" t="n">
-        <v>0.667</v>
+        <v>0.6</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.333</v>
+        <v>1</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.667</v>
+        <v>0.6</v>
       </c>
       <c r="AC36" t="n">
         <v>1</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.667</v>
+        <v>0.6</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.333</v>
+        <v>0.2</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.667</v>
+        <v>0.8</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.667</v>
+        <v>0.8</v>
       </c>
       <c r="AJ36" t="n">
         <v>1</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AL36" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>5.627</v>
+        <v>5.576</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.385</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.432</v>
+        <v>0.586</v>
       </c>
       <c r="AR36" t="n">
-        <v>0.711</v>
+        <v>1.004</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.178</v>
+        <v>0.143</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.154</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AU36" t="n">
-        <v>2.333</v>
+        <v>2</v>
       </c>
       <c r="AV36" t="n">
-        <v>0.171</v>
+        <v>0.17</v>
       </c>
       <c r="AW36" t="n">
-        <v>0.024</v>
+        <v>0.042</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.045</v>
+        <v>0.044</v>
       </c>
       <c r="AY36" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="37">
@@ -5928,40 +5928,40 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C37" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>1.333</v>
       </c>
       <c r="E37" t="n">
         <v>2</v>
       </c>
       <c r="F37" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="G37" t="n">
+        <v>5</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="K37" t="n">
         <v>3</v>
-      </c>
-      <c r="G37" t="n">
-        <v>7</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="n">
-        <v>1</v>
-      </c>
-      <c r="K37" t="n">
-        <v>2</v>
       </c>
       <c r="L37" t="n">
         <v>2</v>
       </c>
       <c r="M37" t="n">
-        <v>1</v>
+        <v>1.667</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -5970,40 +5970,40 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="R37" t="n">
-        <v>1</v>
+        <v>1.667</v>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>1.333</v>
       </c>
       <c r="T37" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="V37" t="n">
-        <v>2</v>
+        <v>0.667</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="Y37" t="n">
-        <v>2</v>
+        <v>1.333</v>
       </c>
       <c r="Z37" t="n">
         <v>2</v>
       </c>
       <c r="AA37" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="AB37" t="n">
         <v>0</v>
@@ -6024,60 +6024,60 @@
         <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
       <c r="AI37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AJ37" t="n">
         <v>0.333</v>
       </c>
       <c r="AK37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL37" t="n">
         <v>4</v>
       </c>
       <c r="AM37" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>22:15</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>9</v>
+        <v>7.92</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.722</v>
+        <v>0.476</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.722</v>
+        <v>0.527</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.444</v>
+        <v>1.01</v>
       </c>
       <c r="AS37" t="n">
-        <v>0</v>
+        <v>0.042</v>
       </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="AU37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.181</v>
+        <v>0.179</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.096</v>
+        <v>0.103</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.09</v>
+        <v>0.161</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.033</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="38">
@@ -6246,13 +6246,13 @@
         </is>
       </c>
       <c r="B39" t="n">
+        <v>4</v>
+      </c>
+      <c r="C39" t="n">
         <v>2</v>
       </c>
-      <c r="C39" t="n">
-        <v>1</v>
-      </c>
       <c r="D39" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E39" t="n">
         <v>1.5</v>
@@ -6261,25 +6261,25 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H39" t="n">
         <v>0.5</v>
       </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L39" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -6297,16 +6297,16 @@
         <v>1</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="T39" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V39" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="W39" t="n">
         <v>0</v>
@@ -6315,19 +6315,19 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="Z39" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AB39" t="n">
         <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>
@@ -6354,45 +6354,45 @@
         <v>0</v>
       </c>
       <c r="AL39" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AM39" t="n">
         <v>0</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>05:02</t>
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.25</v>
+        <v>0.429</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.25</v>
+        <v>0.508</v>
       </c>
       <c r="AR39" t="n">
-        <v>0.5</v>
+        <v>1.015</v>
       </c>
       <c r="AS39" t="n">
         <v>0</v>
       </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>0.286</v>
       </c>
       <c r="AU39" t="n">
         <v>0</v>
       </c>
       <c r="AV39" t="n">
-        <v>0.159</v>
+        <v>0.172</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.189</v>
+        <v>0.099</v>
       </c>
       <c r="AX39" t="n">
-        <v>0</v>
+        <v>0.104</v>
       </c>
       <c r="AY39" t="n">
         <v>0</v>
@@ -6405,7 +6405,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
@@ -6432,10 +6432,10 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>2.333</v>
+        <v>2.4</v>
       </c>
       <c r="L40" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -6447,7 +6447,7 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6564,153 +6564,153 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C41" t="n">
-        <v>96.333</v>
+        <v>93.2</v>
       </c>
       <c r="D41" t="n">
-        <v>24</v>
+        <v>21.4</v>
       </c>
       <c r="E41" t="n">
-        <v>41</v>
+        <v>37.6</v>
       </c>
       <c r="F41" t="n">
-        <v>11</v>
+        <v>11.8</v>
       </c>
       <c r="G41" t="n">
-        <v>32</v>
+        <v>35.6</v>
       </c>
       <c r="H41" t="n">
-        <v>15.333</v>
+        <v>15</v>
       </c>
       <c r="I41" t="n">
         <v>20</v>
       </c>
       <c r="J41" t="n">
-        <v>22</v>
+        <v>20.8</v>
       </c>
       <c r="K41" t="n">
-        <v>29</v>
+        <v>27.4</v>
       </c>
       <c r="L41" t="n">
-        <v>13.333</v>
+        <v>14.8</v>
       </c>
       <c r="M41" t="n">
-        <v>7.667</v>
+        <v>8.4</v>
       </c>
       <c r="N41" t="n">
-        <v>5.667</v>
+        <v>6</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>11.333</v>
+        <v>11.2</v>
       </c>
       <c r="Q41" t="n">
-        <v>11.333</v>
+        <v>11</v>
       </c>
       <c r="R41" t="n">
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="S41" t="n">
-        <v>21.333</v>
+        <v>21.2</v>
       </c>
       <c r="T41" t="n">
-        <v>367</v>
+        <v>584</v>
       </c>
       <c r="U41" t="n">
-        <v>12.333</v>
+        <v>14.8</v>
       </c>
       <c r="V41" t="n">
-        <v>15.333</v>
+        <v>14.4</v>
       </c>
       <c r="W41" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X41" t="n">
-        <v>5.333</v>
+        <v>4.8</v>
       </c>
       <c r="Y41" t="n">
-        <v>16.667</v>
+        <v>14.6</v>
       </c>
       <c r="Z41" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.694</v>
+        <v>0.695</v>
       </c>
       <c r="AB41" t="n">
-        <v>3.333</v>
+        <v>3.2</v>
       </c>
       <c r="AC41" t="n">
-        <v>9.333</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.357</v>
+        <v>0.39</v>
       </c>
       <c r="AE41" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="AF41" t="n">
-        <v>7.667</v>
+        <v>8.4</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.522</v>
+        <v>0.429</v>
       </c>
       <c r="AH41" t="n">
-        <v>3.333</v>
+        <v>3.6</v>
       </c>
       <c r="AI41" t="n">
-        <v>9</v>
+        <v>10.4</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.37</v>
+        <v>0.346</v>
       </c>
       <c r="AK41" t="n">
-        <v>7.667</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AL41" t="n">
-        <v>23</v>
+        <v>25.2</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.333</v>
+        <v>0.325</v>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>208:20</t>
+          <t>205:00</t>
         </is>
       </c>
       <c r="AO41" t="n">
-        <v>93.133</v>
+        <v>93.2</v>
       </c>
       <c r="AP41" t="n">
-        <v>0.555</v>
+        <v>0.534</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.589</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.034</v>
+        <v>1</v>
       </c>
       <c r="AS41" t="n">
-        <v>0.122</v>
+        <v>0.12</v>
       </c>
       <c r="AT41" t="n">
-        <v>0.21</v>
+        <v>0.205</v>
       </c>
       <c r="AU41" t="n">
-        <v>1.941</v>
+        <v>1.857</v>
       </c>
       <c r="AV41" t="n">
         <v>0.2</v>
       </c>
       <c r="AW41" t="n">
-        <v>0.068</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AX41" t="n">
-        <v>0.139</v>
+        <v>0.14</v>
       </c>
       <c r="AY41" t="n">
         <v>0</v>
@@ -6723,153 +6723,153 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C42" t="n">
-        <v>89.333</v>
+        <v>83.8</v>
       </c>
       <c r="D42" t="n">
-        <v>16.333</v>
+        <v>18.8</v>
       </c>
       <c r="E42" t="n">
-        <v>35</v>
+        <v>36.4</v>
       </c>
       <c r="F42" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G42" t="n">
-        <v>37</v>
+        <v>32.8</v>
       </c>
       <c r="H42" t="n">
-        <v>14.667</v>
+        <v>13.2</v>
       </c>
       <c r="I42" t="n">
-        <v>19</v>
+        <v>16.8</v>
       </c>
       <c r="J42" t="n">
-        <v>18.667</v>
+        <v>17.6</v>
       </c>
       <c r="K42" t="n">
-        <v>25.667</v>
+        <v>26.2</v>
       </c>
       <c r="L42" t="n">
-        <v>12.667</v>
+        <v>11.8</v>
       </c>
       <c r="M42" t="n">
-        <v>8.333</v>
+        <v>7.6</v>
       </c>
       <c r="N42" t="n">
-        <v>5.667</v>
+        <v>5.8</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>13</v>
+        <v>14.4</v>
       </c>
       <c r="Q42" t="n">
-        <v>12.333</v>
+        <v>13.2</v>
       </c>
       <c r="R42" t="n">
-        <v>21.333</v>
+        <v>21.4</v>
       </c>
       <c r="S42" t="n">
-        <v>19</v>
+        <v>18.6</v>
       </c>
       <c r="T42" t="n">
-        <v>297</v>
+        <v>463</v>
       </c>
       <c r="U42" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="V42" t="n">
-        <v>13.333</v>
+        <v>13.2</v>
       </c>
       <c r="W42" t="n">
-        <v>4.333</v>
+        <v>4.6</v>
       </c>
       <c r="X42" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="Y42" t="n">
-        <v>12.667</v>
+        <v>12.8</v>
       </c>
       <c r="Z42" t="n">
-        <v>20.333</v>
+        <v>19.2</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.623</v>
+        <v>0.667</v>
       </c>
       <c r="AB42" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="AC42" t="n">
-        <v>11</v>
+        <v>11.6</v>
       </c>
       <c r="AD42" t="n">
-        <v>0.273</v>
+        <v>0.362</v>
       </c>
       <c r="AE42" t="n">
-        <v>0.667</v>
+        <v>1.8</v>
       </c>
       <c r="AF42" t="n">
-        <v>3.667</v>
+        <v>5.6</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.182</v>
+        <v>0.321</v>
       </c>
       <c r="AH42" t="n">
-        <v>4.667</v>
+        <v>3.8</v>
       </c>
       <c r="AI42" t="n">
-        <v>9.333</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.5</v>
+        <v>0.413</v>
       </c>
       <c r="AK42" t="n">
-        <v>9.333</v>
+        <v>7.2</v>
       </c>
       <c r="AL42" t="n">
-        <v>27.667</v>
+        <v>23.6</v>
       </c>
       <c r="AM42" t="n">
-        <v>0.337</v>
+        <v>0.305</v>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>208:20</t>
+          <t>205:00</t>
         </is>
       </c>
       <c r="AO42" t="n">
-        <v>93.36</v>
+        <v>90.992</v>
       </c>
       <c r="AP42" t="n">
-        <v>0.519</v>
+        <v>0.51</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.556</v>
+        <v>0.547</v>
       </c>
       <c r="AR42" t="n">
-        <v>0.957</v>
+        <v>0.921</v>
       </c>
       <c r="AS42" t="n">
-        <v>0.139</v>
+        <v>0.158</v>
       </c>
       <c r="AT42" t="n">
-        <v>0.204</v>
+        <v>0.191</v>
       </c>
       <c r="AU42" t="n">
-        <v>1.436</v>
+        <v>1.222</v>
       </c>
       <c r="AV42" t="n">
-        <v>0.2</v>
+        <v>0.195</v>
       </c>
       <c r="AW42" t="n">
-        <v>0.065</v>
+        <v>0.058</v>
       </c>
       <c r="AX42" t="n">
-        <v>0.123</v>
+        <v>0.134</v>
       </c>
       <c r="AY42" t="n">
         <v>0</v>

--- a/informes_data/ACB/2025-26/playoffs/aggregate/AGGREGATE_Valencia Basket.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate/AGGREGATE_Valencia Basket.xlsx
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>392</v>
+        <v>478.56</v>
       </c>
       <c r="C2" t="n">
-        <v>393.98</v>
+        <v>480.88</v>
       </c>
       <c r="D2" t="n">
-        <v>118.2801157419158</v>
+        <v>120.19630677092</v>
       </c>
       <c r="E2" t="n">
-        <v>106.3505761713793</v>
+        <v>110.6305107303277</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5341530054644809</v>
+        <v>0.5401785714285714</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1201716738197425</v>
+        <v>0.1082404712896586</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3609756097560975</v>
+        <v>0.3541666666666667</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2049180327868853</v>
+        <v>0.2098214285714286</v>
       </c>
       <c r="J2" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K2" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="L2" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="M2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="N2" t="n">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="O2" t="n">
-        <v>105</v>
+        <v>137</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2868852459016393</v>
+        <v>0.3058035714285715</v>
       </c>
       <c r="Q2" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="R2" t="n">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1120218579234973</v>
+        <v>0.1272321428571428</v>
       </c>
       <c r="T2" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="U2" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1147540983606557</v>
+        <v>0.1116071428571429</v>
       </c>
       <c r="W2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="X2" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1420765027322404</v>
+        <v>0.125</v>
       </c>
       <c r="Z2" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="AA2" t="n">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3442622950819672</v>
+        <v>0.3303571428571428</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.6952380952380952</v>
+        <v>0.708029197080292</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.3902439024390244</v>
+        <v>0.4210526315789473</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.44</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.3461538461538461</v>
+        <v>0.3392857142857143</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3253968253968254</v>
+        <v>0.3175675675675675</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.39047619047619</v>
+        <v>1.416058394160584</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.88</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.9943820224719101</v>
+        <v>0.9705882352941176</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.027777777777778</v>
+        <v>0.9879518072289156</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.972972972972973</v>
+        <v>0.9882352941176471</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.708333333333333</v>
+        <v>1.7</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.857142857142857</v>
+        <v>2.016393442622951</v>
       </c>
       <c r="AO2" t="n">
-        <v>6.535714285714286</v>
+        <v>7.344262295081967</v>
       </c>
       <c r="AP2" t="n">
-        <v>8.392857142857142</v>
+        <v>9.360655737704919</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>78.40000000000001</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>78.79599999999999</v>
+        <v>80.14666666666666</v>
       </c>
       <c r="D3" t="n">
-        <v>118.2801157419158</v>
+        <v>120.19630677092</v>
       </c>
       <c r="E3" t="n">
-        <v>106.3505761713793</v>
+        <v>110.6305107303278</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5341530054644809</v>
+        <v>0.5401785714285714</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1201716738197425</v>
+        <v>0.1082404712896586</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3609756097560976</v>
+        <v>0.3541666666666666</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2049180327868853</v>
+        <v>0.2098214285714286</v>
       </c>
       <c r="J3" t="n">
-        <v>14.8</v>
+        <v>13.66666666666667</v>
       </c>
       <c r="K3" t="n">
-        <v>14.4</v>
+        <v>14</v>
       </c>
       <c r="L3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="M3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N3" t="n">
-        <v>14.6</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="O3" t="n">
-        <v>21</v>
+        <v>22.83333333333333</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2868852459016393</v>
+        <v>0.3058035714285715</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>8.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1120218579234973</v>
+        <v>0.1272321428571429</v>
       </c>
       <c r="T3" t="n">
-        <v>3.6</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="U3" t="n">
-        <v>8.4</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1147540983606557</v>
+        <v>0.1116071428571429</v>
       </c>
       <c r="W3" t="n">
-        <v>3.6</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="X3" t="n">
-        <v>10.4</v>
+        <v>9.333333333333334</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1420765027322404</v>
+        <v>0.125</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.199999999999999</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="AA3" t="n">
-        <v>25.2</v>
+        <v>24.66666666666667</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3442622950819672</v>
+        <v>0.3303571428571429</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.6952380952380952</v>
+        <v>0.7080291970802921</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.3902439024390245</v>
+        <v>0.4210526315789473</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.3461538461538461</v>
+        <v>0.3392857142857142</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3253968253968254</v>
+        <v>0.3175675675675675</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.39047619047619</v>
+        <v>1.416058394160584</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8799999999999999</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.99438202247191</v>
+        <v>0.9705882352941176</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.027777777777778</v>
+        <v>0.9879518072289156</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.9729729729729729</v>
+        <v>0.9882352941176471</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.708333333333333</v>
+        <v>1.7</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.857142857142857</v>
+        <v>2.016393442622951</v>
       </c>
       <c r="AO3" t="n">
-        <v>6.535714285714286</v>
+        <v>7.344262295081966</v>
       </c>
       <c r="AP3" t="n">
-        <v>8.392857142857144</v>
+        <v>9.360655737704917</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>395.96</v>
+        <v>483.2</v>
       </c>
       <c r="C4" t="n">
-        <v>393.98</v>
+        <v>480.88</v>
       </c>
       <c r="D4" t="n">
-        <v>106.3505761713793</v>
+        <v>110.6305107303277</v>
       </c>
       <c r="E4" t="n">
-        <v>118.2801157419158</v>
+        <v>120.19630677092</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5101156069364162</v>
+        <v>0.5368171021377672</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1582556708282047</v>
+        <v>0.1508542348237005</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3010204081632653</v>
+        <v>0.2875536480686695</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1907514450867052</v>
+        <v>0.1900237529691211</v>
       </c>
       <c r="J4" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="K4" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="L4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M4" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="N4" t="n">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="O4" t="n">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2774566473988439</v>
+        <v>0.2707838479809976</v>
       </c>
       <c r="Q4" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="R4" t="n">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1676300578034682</v>
+        <v>0.171021377672209</v>
       </c>
       <c r="T4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="U4" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="V4" t="n">
-        <v>0.08092485549132948</v>
+        <v>0.07838479809976247</v>
       </c>
       <c r="W4" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X4" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1329479768786127</v>
+        <v>0.1235154394299287</v>
       </c>
       <c r="Z4" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="AA4" t="n">
-        <v>118</v>
+        <v>150</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3410404624277457</v>
+        <v>0.3562945368171022</v>
       </c>
       <c r="AC4" t="n">
+        <v>0.6842105263157895</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.3611111111111111</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.4230769230769231</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.3466666666666667</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.368421052631579</v>
+      </c>
+      <c r="AI4" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="AD4" t="n">
-        <v>0.3620689655172414</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0.3214285714285715</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0.4130434782608696</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0.3050847457627119</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0.6428571428571429</v>
-      </c>
       <c r="AJ4" t="n">
-        <v>1.00609756097561</v>
+        <v>1.099009900990099</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.7321428571428571</v>
+        <v>0.819672131147541</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.11864406779661</v>
+        <v>1.059701492537313</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.4375</v>
+        <v>1.470588235294118</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.222222222222222</v>
+        <v>1.325301204819277</v>
       </c>
       <c r="AO4" t="n">
-        <v>4.805555555555555</v>
+        <v>5.072289156626506</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.027777777777778</v>
+        <v>6.397590361445783</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>79.19200000000001</v>
+        <v>80.53333333333335</v>
       </c>
       <c r="C5" t="n">
-        <v>78.79599999999999</v>
+        <v>80.14666666666666</v>
       </c>
       <c r="D5" t="n">
-        <v>106.3505761713793</v>
+        <v>110.6305107303278</v>
       </c>
       <c r="E5" t="n">
-        <v>118.2801157419158</v>
+        <v>120.19630677092</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5101156069364162</v>
+        <v>0.5368171021377673</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1582556708282047</v>
+        <v>0.1508542348237005</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3010204081632653</v>
+        <v>0.2875536480686695</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1907514450867052</v>
+        <v>0.1900237529691212</v>
       </c>
       <c r="J5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="K5" t="n">
-        <v>13.2</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="L5" t="n">
-        <v>4.6</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="M5" t="n">
-        <v>13.2</v>
+        <v>12.66666666666667</v>
       </c>
       <c r="N5" t="n">
-        <v>12.8</v>
+        <v>13</v>
       </c>
       <c r="O5" t="n">
-        <v>19.2</v>
+        <v>19</v>
       </c>
       <c r="P5" t="n">
-        <v>0.277456647398844</v>
+        <v>0.2707838479809976</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.2</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="R5" t="n">
-        <v>11.6</v>
+        <v>12</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1676300578034682</v>
+        <v>0.171021377672209</v>
       </c>
       <c r="T5" t="n">
-        <v>1.8</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="U5" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="V5" t="n">
-        <v>0.08092485549132949</v>
+        <v>0.07838479809976248</v>
       </c>
       <c r="W5" t="n">
-        <v>3.8</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="X5" t="n">
-        <v>9.199999999999999</v>
+        <v>8.666666666666666</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1329479768786127</v>
+        <v>0.1235154394299288</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.2</v>
+        <v>8.666666666666666</v>
       </c>
       <c r="AA5" t="n">
-        <v>23.6</v>
+        <v>25</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3410404624277457</v>
+        <v>0.3562945368171022</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.6842105263157895</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.3620689655172414</v>
+        <v>0.3611111111111111</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.3214285714285715</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.4130434782608696</v>
+        <v>0.4230769230769231</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3050847457627118</v>
+        <v>0.3466666666666666</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.333333333333333</v>
+        <v>1.368421052631579</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.00609756097561</v>
+        <v>1.099009900990099</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.7321428571428571</v>
+        <v>0.8196721311475411</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.11864406779661</v>
+        <v>1.059701492537314</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.4375</v>
+        <v>1.470588235294118</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.222222222222222</v>
+        <v>1.325301204819277</v>
       </c>
       <c r="AO5" t="n">
-        <v>4.805555555555554</v>
+        <v>5.072289156626505</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.027777777777777</v>
+        <v>6.397590361445782</v>
       </c>
     </row>
     <row r="7">
@@ -1419,22 +1419,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="D8" t="n">
+        <v>17</v>
+      </c>
+      <c r="E8" t="n">
+        <v>26</v>
+      </c>
+      <c r="F8" t="n">
         <v>10</v>
       </c>
-      <c r="E8" t="n">
-        <v>17</v>
-      </c>
-      <c r="F8" t="n">
-        <v>8</v>
-      </c>
       <c r="G8" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H8" t="n">
         <v>12</v>
@@ -1443,7 +1443,7 @@
         <v>15</v>
       </c>
       <c r="J8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K8" t="n">
         <v>7</v>
@@ -1452,10 +1452,10 @@
         <v>3</v>
       </c>
       <c r="M8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1467,52 +1467,52 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="S8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T8" t="n">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="U8" t="n">
         <v>9</v>
       </c>
       <c r="V8" t="n">
+        <v>5</v>
+      </c>
+      <c r="W8" t="n">
+        <v>4</v>
+      </c>
+      <c r="X8" t="n">
         <v>3</v>
       </c>
-      <c r="W8" t="n">
-        <v>2</v>
-      </c>
-      <c r="X8" t="n">
-        <v>2</v>
-      </c>
       <c r="Y8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Z8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AB8" t="n">
         <v>4</v>
       </c>
-      <c r="AA8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2</v>
-      </c>
       <c r="AC8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AD8" t="n">
         <v>0.667</v>
       </c>
       <c r="AE8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.6</v>
+        <v>0.583</v>
       </c>
       <c r="AH8" t="n">
         <v>5</v>
@@ -1524,51 +1524,51 @@
         <v>0.5</v>
       </c>
       <c r="AK8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AL8" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.15</v>
+        <v>0.208</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>116:20</t>
+          <t>157:35</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>56.6</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.468</v>
+        <v>0.533</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.522</v>
+        <v>0.571</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.989</v>
+        <v>1.092</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.053</v>
+        <v>0.043</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.255</v>
+        <v>0.2</v>
       </c>
       <c r="AU8" t="n">
-        <v>4.667</v>
+        <v>5.333</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.214</v>
+        <v>0.196</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.026</v>
+        <v>0.02</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.063</v>
+        <v>0.048</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.095</v>
+        <v>0.08799999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -1578,82 +1578,82 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="D9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E9" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F9" t="n">
         <v>10</v>
       </c>
       <c r="G9" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I9" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J9" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K9" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="L9" t="n">
         <v>5</v>
       </c>
       <c r="M9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T9" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="U9" t="n">
         <v>7</v>
       </c>
       <c r="V9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="W9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Z9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AA9" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AB9" t="n">
         <v>3</v>
@@ -1665,69 +1665,69 @@
         <v>0.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF9" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.583</v>
+        <v>0.533</v>
       </c>
       <c r="AH9" t="n">
         <v>1</v>
       </c>
       <c r="AI9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.167</v>
+        <v>0.143</v>
       </c>
       <c r="AK9" t="n">
         <v>9</v>
       </c>
       <c r="AL9" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.45</v>
+        <v>0.346</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>126:28</t>
+          <t>159:34</t>
         </is>
       </c>
       <c r="AO9" t="n">
-        <v>58.08</v>
+        <v>75.84</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.612</v>
+        <v>0.547</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.634</v>
+        <v>0.574</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.136</v>
+        <v>1.042</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.103</v>
+        <v>0.092</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.122</v>
+        <v>0.141</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.333</v>
+        <v>1.571</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.202</v>
+        <v>0.211</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.04</v>
+        <v>0.033</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.124</v>
+        <v>0.141</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.057</v>
+        <v>0.061</v>
       </c>
     </row>
     <row r="10">
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.183</v>
+        <v>0.184</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.029</v>
+        <v>0.031</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.185</v>
+        <v>0.19</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="11">
@@ -1896,67 +1896,67 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D11" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E11" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F11" t="n">
         <v>5</v>
       </c>
       <c r="G11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H11" t="n">
+        <v>11</v>
+      </c>
+      <c r="I11" t="n">
+        <v>12</v>
+      </c>
+      <c r="J11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K11" t="n">
+        <v>16</v>
+      </c>
+      <c r="L11" t="n">
+        <v>11</v>
+      </c>
+      <c r="M11" t="n">
+        <v>7</v>
+      </c>
+      <c r="N11" t="n">
+        <v>5</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7</v>
+      </c>
+      <c r="S11" t="n">
+        <v>13</v>
+      </c>
+      <c r="T11" t="n">
+        <v>87</v>
+      </c>
+      <c r="U11" t="n">
         <v>9</v>
       </c>
-      <c r="I11" t="n">
-        <v>10</v>
-      </c>
-      <c r="J11" t="n">
-        <v>7</v>
-      </c>
-      <c r="K11" t="n">
+      <c r="V11" t="n">
         <v>13</v>
-      </c>
-      <c r="L11" t="n">
-        <v>7</v>
-      </c>
-      <c r="M11" t="n">
-        <v>6</v>
-      </c>
-      <c r="N11" t="n">
-        <v>4</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>6</v>
-      </c>
-      <c r="S11" t="n">
-        <v>9</v>
-      </c>
-      <c r="T11" t="n">
-        <v>69</v>
-      </c>
-      <c r="U11" t="n">
-        <v>7</v>
-      </c>
-      <c r="V11" t="n">
-        <v>11</v>
       </c>
       <c r="W11" t="n">
         <v>5</v>
@@ -1965,19 +1965,19 @@
         <v>2</v>
       </c>
       <c r="Y11" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Z11" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.722</v>
+        <v>0.739</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -1986,7 +1986,7 @@
         <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -1995,10 +1995,10 @@
         <v>2</v>
       </c>
       <c r="AI11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="AK11" t="n">
         <v>3</v>
@@ -2011,41 +2011,41 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>108:18</t>
+          <t>130:56</t>
         </is>
       </c>
       <c r="AO11" t="n">
-        <v>42.4</v>
+        <v>52.28</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.586</v>
+        <v>0.57</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.635</v>
+        <v>0.621</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.179</v>
+        <v>1.148</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.077</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.257</v>
+        <v>0.256</v>
       </c>
       <c r="AU11" t="n">
-        <v>2.333</v>
+        <v>2</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.172</v>
+        <v>0.177</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.065</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.126</v>
+        <v>0.131</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.047</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="12">
@@ -2055,40 +2055,40 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L12" t="n">
         <v>4</v>
       </c>
       <c r="M12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N12" t="n">
         <v>5</v>
@@ -2097,40 +2097,40 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T12" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="U12" t="n">
         <v>5</v>
       </c>
       <c r="V12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W12" t="n">
+        <v>5</v>
+      </c>
+      <c r="X12" t="n">
         <v>2</v>
       </c>
-      <c r="X12" t="n">
-        <v>1</v>
-      </c>
       <c r="Y12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.5</v>
+        <v>0.571</v>
       </c>
       <c r="AB12" t="n">
         <v>2</v>
@@ -2151,13 +2151,13 @@
         <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.143</v>
+        <v>0.25</v>
       </c>
       <c r="AK12" t="n">
         <v>2</v>
@@ -2170,41 +2170,41 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>86:54</t>
+          <t>101:38</t>
         </is>
       </c>
       <c r="AO12" t="n">
-        <v>43.08</v>
+        <v>48.84</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.297</v>
+        <v>0.353</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.328</v>
+        <v>0.412</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.534</v>
+        <v>0.655</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.186</v>
+        <v>0.205</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.125</v>
+        <v>0.235</v>
       </c>
       <c r="AU12" t="n">
         <v>1</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.218</v>
+        <v>0.213</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.046</v>
+        <v>0.041</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.156</v>
+        <v>0.169</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.051</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="13">
@@ -2214,43 +2214,43 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E13" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F13" t="n">
         <v>3</v>
       </c>
       <c r="G13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I13" t="n">
+        <v>12</v>
+      </c>
+      <c r="J13" t="n">
+        <v>18</v>
+      </c>
+      <c r="K13" t="n">
+        <v>23</v>
+      </c>
+      <c r="L13" t="n">
         <v>11</v>
       </c>
-      <c r="J13" t="n">
-        <v>17</v>
-      </c>
-      <c r="K13" t="n">
-        <v>19</v>
-      </c>
-      <c r="L13" t="n">
-        <v>10</v>
-      </c>
       <c r="M13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2262,43 +2262,43 @@
         <v>9</v>
       </c>
       <c r="R13" t="n">
+        <v>14</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="n">
+        <v>76</v>
+      </c>
+      <c r="U13" t="n">
         <v>11</v>
-      </c>
-      <c r="S13" t="n">
-        <v>9</v>
-      </c>
-      <c r="T13" t="n">
-        <v>57</v>
-      </c>
-      <c r="U13" t="n">
-        <v>5</v>
       </c>
       <c r="V13" t="n">
         <v>7</v>
       </c>
       <c r="W13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Z13" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.667</v>
+        <v>0.714</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2322,48 +2322,48 @@
         <v>2</v>
       </c>
       <c r="AL13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.333</v>
+        <v>0.286</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>98:49</t>
+          <t>133:54</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>47.84</v>
+        <v>56.28</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.456</v>
+        <v>0.512</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.489</v>
+        <v>0.539</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.794</v>
+        <v>0.906</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.188</v>
+        <v>0.16</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.206</v>
+        <v>0.19</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.889</v>
+        <v>2</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.213</v>
+        <v>0.186</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.101</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.201</v>
+        <v>0.184</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.112</v>
+        <v>0.095</v>
       </c>
     </row>
     <row r="14">
@@ -2373,43 +2373,43 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E14" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="F14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G14" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H14" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I14" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="K14" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M14" t="n">
         <v>7</v>
       </c>
       <c r="N14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2421,13 +2421,13 @@
         <v>11</v>
       </c>
       <c r="R14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S14" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="T14" t="n">
-        <v>121</v>
+        <v>152</v>
       </c>
       <c r="U14" t="n">
         <v>20</v>
@@ -2442,31 +2442,31 @@
         <v>6</v>
       </c>
       <c r="Y14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z14" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.733</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="AB14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AC14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.333</v>
+        <v>0.429</v>
       </c>
       <c r="AH14" t="n">
         <v>2</v>
@@ -2478,51 +2478,51 @@
         <v>0.667</v>
       </c>
       <c r="AK14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AL14" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.393</v>
+        <v>0.382</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>129:40</t>
+          <t>172:54</t>
         </is>
       </c>
       <c r="AO14" t="n">
-        <v>76.04000000000001</v>
+        <v>97</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.629</v>
+        <v>0.593</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.677</v>
+        <v>0.651</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.157</v>
+        <v>1.155</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.145</v>
+        <v>0.113</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.259</v>
+        <v>0.307</v>
       </c>
       <c r="AU14" t="n">
-        <v>2.636</v>
+        <v>3.273</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.258</v>
+        <v>0.249</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.039</v>
+        <v>0.036</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.081</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.213</v>
+        <v>0.209</v>
       </c>
     </row>
     <row r="15">
@@ -2532,16 +2532,16 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>6</v>
+      </c>
+      <c r="C15" t="n">
+        <v>26</v>
+      </c>
+      <c r="D15" t="n">
         <v>5</v>
       </c>
-      <c r="C15" t="n">
-        <v>24</v>
-      </c>
-      <c r="D15" t="n">
-        <v>4</v>
-      </c>
       <c r="E15" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F15" t="n">
         <v>4</v>
@@ -2574,19 +2574,19 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S15" t="n">
         <v>6</v>
       </c>
       <c r="T15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="U15" t="n">
         <v>1</v>
@@ -2601,13 +2601,13 @@
         <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.667</v>
+        <v>0.6</v>
       </c>
       <c r="AB15" t="n">
         <v>1</v>
@@ -2647,41 +2647,41 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>85:34</t>
+          <t>105:57</t>
         </is>
       </c>
       <c r="AO15" t="n">
-        <v>36.64</v>
+        <v>39.64</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.385</v>
+        <v>0.393</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.419</v>
+        <v>0.424</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.655</v>
+        <v>0.656</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.218</v>
+        <v>0.227</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.154</v>
+        <v>0.143</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.5</v>
+        <v>0.444</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.188</v>
+        <v>0.166</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.058</v>
+        <v>0.049</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.134</v>
+        <v>0.111</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="16">
@@ -2691,37 +2691,37 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>6</v>
+      </c>
+      <c r="C16" t="n">
+        <v>41</v>
+      </c>
+      <c r="D16" t="n">
+        <v>18</v>
+      </c>
+      <c r="E16" t="n">
+        <v>25</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
         <v>5</v>
       </c>
-      <c r="C16" t="n">
-        <v>36</v>
-      </c>
-      <c r="D16" t="n">
-        <v>16</v>
-      </c>
-      <c r="E16" t="n">
-        <v>23</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>4</v>
-      </c>
       <c r="I16" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K16" t="n">
         <v>17</v>
       </c>
       <c r="L16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M16" t="n">
         <v>2</v>
@@ -2739,19 +2739,19 @@
         <v>2</v>
       </c>
       <c r="R16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T16" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="U16" t="n">
         <v>9</v>
       </c>
       <c r="V16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="W16" t="n">
         <v>5</v>
@@ -2760,22 +2760,22 @@
         <v>4</v>
       </c>
       <c r="Y16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.789</v>
+        <v>0.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2806,41 +2806,41 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>91:38</t>
+          <t>107:31</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>30.72</v>
+        <v>33.6</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.696</v>
+        <v>0.72</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.627</v>
+        <v>0.649</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.172</v>
+        <v>1.22</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.174</v>
+        <v>0.2</v>
       </c>
       <c r="AU16" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.147</v>
+        <v>0.139</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.153</v>
+        <v>0.145</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.194</v>
+        <v>0.17</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.013</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="17">
@@ -2850,7 +2850,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -3009,22 +3009,22 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>6</v>
+      </c>
+      <c r="C18" t="n">
+        <v>33</v>
+      </c>
+      <c r="D18" t="n">
         <v>5</v>
       </c>
-      <c r="C18" t="n">
-        <v>28</v>
-      </c>
-      <c r="D18" t="n">
-        <v>4</v>
-      </c>
       <c r="E18" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G18" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H18" t="n">
         <v>2</v>
@@ -3033,7 +3033,7 @@
         <v>2</v>
       </c>
       <c r="J18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K18" t="n">
         <v>3</v>
@@ -3042,10 +3042,10 @@
         <v>3</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -3057,13 +3057,13 @@
         <v>4</v>
       </c>
       <c r="R18" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
       </c>
       <c r="T18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U18" t="n">
         <v>3</v>
@@ -3081,19 +3081,19 @@
         <v>1</v>
       </c>
       <c r="Z18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AB18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.6</v>
+        <v>0.571</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -3108,57 +3108,57 @@
         <v>4</v>
       </c>
       <c r="AI18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AK18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>72:07</t>
+          <t>85:02</t>
         </is>
       </c>
       <c r="AO18" t="n">
-        <v>27.88</v>
+        <v>32.88</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.554</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.586</v>
+        <v>0.571</v>
       </c>
       <c r="AR18" t="n">
         <v>1.004</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.143</v>
+        <v>0.122</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AU18" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.17</v>
+        <v>0.172</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.042</v>
+        <v>0.037</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.044</v>
+        <v>0.038</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.051</v>
+        <v>0.046</v>
       </c>
     </row>
     <row r="19">
@@ -3168,34 +3168,34 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E19" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G19" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H19" t="n">
         <v>4</v>
       </c>
       <c r="I19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K19" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L19" t="n">
         <v>6</v>
@@ -3216,13 +3216,13 @@
         <v>1</v>
       </c>
       <c r="R19" t="n">
+        <v>8</v>
+      </c>
+      <c r="S19" t="n">
         <v>5</v>
       </c>
-      <c r="S19" t="n">
-        <v>4</v>
-      </c>
       <c r="T19" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="U19" t="n">
         <v>2</v>
@@ -3237,31 +3237,31 @@
         <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z19" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.667</v>
+        <v>0.625</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH19" t="n">
         <v>1</v>
@@ -3273,51 +3273,51 @@
         <v>0.333</v>
       </c>
       <c r="AK19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL19" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AM19" t="n">
         <v>0.25</v>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>58:31</t>
+          <t>81:16</t>
         </is>
       </c>
       <c r="AO19" t="n">
-        <v>23.76</v>
+        <v>32.64</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.476</v>
+        <v>0.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.527</v>
+        <v>0.521</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.01</v>
+        <v>1.011</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.042</v>
+        <v>0.031</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.19</v>
+        <v>0.138</v>
       </c>
       <c r="AU19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.179</v>
+        <v>0.178</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.103</v>
+        <v>0.077</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.161</v>
+        <v>0.172</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.032</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="20">
@@ -3486,16 +3486,16 @@
         </is>
       </c>
       <c r="B21" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" t="n">
+        <v>10</v>
+      </c>
+      <c r="D21" t="n">
         <v>4</v>
       </c>
-      <c r="C21" t="n">
+      <c r="E21" t="n">
         <v>8</v>
-      </c>
-      <c r="D21" t="n">
-        <v>3</v>
-      </c>
-      <c r="E21" t="n">
-        <v>6</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -3513,16 +3513,16 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M21" t="n">
         <v>1</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3534,40 +3534,40 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U21" t="n">
         <v>4</v>
       </c>
       <c r="V21" t="n">
+        <v>4</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
         <v>2</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3601,38 +3601,38 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>34:02</t>
         </is>
       </c>
       <c r="AO21" t="n">
-        <v>7.88</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.429</v>
+        <v>0.444</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.508</v>
+        <v>0.506</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.015</v>
+        <v>1.012</v>
       </c>
       <c r="AS21" t="n">
         <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>0.286</v>
+        <v>0.222</v>
       </c>
       <c r="AU21" t="n">
         <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.172</v>
+        <v>0.129</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.099</v>
+        <v>0.092</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.104</v>
+        <v>0.095</v>
       </c>
       <c r="AY21" t="n">
         <v>0</v>
@@ -3645,7 +3645,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -3672,10 +3672,10 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
+        <v>16</v>
+      </c>
+      <c r="L22" t="n">
         <v>12</v>
-      </c>
-      <c r="L22" t="n">
-        <v>9</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -3804,153 +3804,153 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C23" t="n">
-        <v>466</v>
+        <v>578</v>
       </c>
       <c r="D23" t="n">
-        <v>107</v>
+        <v>143</v>
       </c>
       <c r="E23" t="n">
-        <v>188</v>
+        <v>244</v>
       </c>
       <c r="F23" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="G23" t="n">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="H23" t="n">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="I23" t="n">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="J23" t="n">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="K23" t="n">
+        <v>166</v>
+      </c>
+      <c r="L23" t="n">
+        <v>85</v>
+      </c>
+      <c r="M23" t="n">
+        <v>52</v>
+      </c>
+      <c r="N23" t="n">
+        <v>39</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>61</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>60</v>
+      </c>
+      <c r="R23" t="n">
+        <v>116</v>
+      </c>
+      <c r="S23" t="n">
+        <v>129</v>
+      </c>
+      <c r="T23" t="n">
+        <v>726</v>
+      </c>
+      <c r="U23" t="n">
+        <v>82</v>
+      </c>
+      <c r="V23" t="n">
+        <v>84</v>
+      </c>
+      <c r="W23" t="n">
+        <v>51</v>
+      </c>
+      <c r="X23" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>97</v>
+      </c>
+      <c r="Z23" t="n">
         <v>137</v>
       </c>
-      <c r="L23" t="n">
-        <v>74</v>
-      </c>
-      <c r="M23" t="n">
-        <v>42</v>
-      </c>
-      <c r="N23" t="n">
-        <v>30</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
+      <c r="AA23" t="n">
+        <v>0.708</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>57</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.421</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI23" t="n">
         <v>56</v>
       </c>
-      <c r="Q23" t="n">
-        <v>55</v>
-      </c>
-      <c r="R23" t="n">
-        <v>94</v>
-      </c>
-      <c r="S23" t="n">
-        <v>106</v>
-      </c>
-      <c r="T23" t="n">
-        <v>584</v>
-      </c>
-      <c r="U23" t="n">
-        <v>74</v>
-      </c>
-      <c r="V23" t="n">
-        <v>72</v>
-      </c>
-      <c r="W23" t="n">
-        <v>41</v>
-      </c>
-      <c r="X23" t="n">
-        <v>24</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>73</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>105</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0.695</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>41</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>18</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>42</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>52</v>
-      </c>
       <c r="AJ23" t="n">
-        <v>0.346</v>
+        <v>0.339</v>
       </c>
       <c r="AK23" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="AL23" t="n">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.325</v>
+        <v>0.318</v>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>1025:00</t>
+          <t>1250:00</t>
         </is>
       </c>
       <c r="AO23" t="n">
-        <v>466</v>
+        <v>563.5599999999999</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.534</v>
+        <v>0.54</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.575</v>
       </c>
       <c r="AR23" t="n">
-        <v>1</v>
+        <v>1.026</v>
       </c>
       <c r="AS23" t="n">
-        <v>0.12</v>
+        <v>0.108</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.205</v>
+        <v>0.21</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.857</v>
+        <v>2.016</v>
       </c>
       <c r="AV23" t="n">
         <v>0.2</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.14</v>
+        <v>0.142</v>
       </c>
       <c r="AY23" t="n">
         <v>0</v>
@@ -3963,153 +3963,153 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C24" t="n">
-        <v>419</v>
+        <v>532</v>
       </c>
       <c r="D24" t="n">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="E24" t="n">
-        <v>182</v>
+        <v>219</v>
       </c>
       <c r="F24" t="n">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="G24" t="n">
-        <v>164</v>
+        <v>202</v>
       </c>
       <c r="H24" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="I24" t="n">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="J24" t="n">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="K24" t="n">
-        <v>131</v>
+        <v>155</v>
       </c>
       <c r="L24" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="M24" t="n">
+        <v>42</v>
+      </c>
+      <c r="N24" t="n">
         <v>38</v>
       </c>
-      <c r="N24" t="n">
-        <v>29</v>
-      </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
+        <v>83</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>76</v>
+      </c>
+      <c r="R24" t="n">
+        <v>130</v>
+      </c>
+      <c r="S24" t="n">
+        <v>115</v>
+      </c>
+      <c r="T24" t="n">
+        <v>589</v>
+      </c>
+      <c r="U24" t="n">
+        <v>50</v>
+      </c>
+      <c r="V24" t="n">
+        <v>71</v>
+      </c>
+      <c r="W24" t="n">
+        <v>25</v>
+      </c>
+      <c r="X24" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>78</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>114</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC24" t="n">
         <v>72</v>
       </c>
-      <c r="Q24" t="n">
-        <v>66</v>
-      </c>
-      <c r="R24" t="n">
-        <v>107</v>
-      </c>
-      <c r="S24" t="n">
-        <v>93</v>
-      </c>
-      <c r="T24" t="n">
-        <v>463</v>
-      </c>
-      <c r="U24" t="n">
-        <v>41</v>
-      </c>
-      <c r="V24" t="n">
-        <v>66</v>
-      </c>
-      <c r="W24" t="n">
-        <v>23</v>
-      </c>
-      <c r="X24" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>64</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>96</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>21</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>58</v>
-      </c>
       <c r="AD24" t="n">
-        <v>0.362</v>
+        <v>0.361</v>
       </c>
       <c r="AE24" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AF24" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.321</v>
+        <v>0.333</v>
       </c>
       <c r="AH24" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AI24" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.413</v>
+        <v>0.423</v>
       </c>
       <c r="AK24" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="AL24" t="n">
-        <v>118</v>
+        <v>150</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.305</v>
+        <v>0.347</v>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>1025:00</t>
+          <t>1250:00</t>
         </is>
       </c>
       <c r="AO24" t="n">
-        <v>454.96</v>
+        <v>550.2</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.51</v>
+        <v>0.537</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.547</v>
+        <v>0.569</v>
       </c>
       <c r="AR24" t="n">
-        <v>0.921</v>
+        <v>0.967</v>
       </c>
       <c r="AS24" t="n">
-        <v>0.158</v>
+        <v>0.151</v>
       </c>
       <c r="AT24" t="n">
-        <v>0.191</v>
+        <v>0.19</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.222</v>
+        <v>1.325</v>
       </c>
       <c r="AV24" t="n">
         <v>0.2</v>
       </c>
       <c r="AW24" t="n">
-        <v>0.06</v>
+        <v>0.058</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.128</v>
+        <v>0.129</v>
       </c>
       <c r="AY24" t="n">
         <v>0</v>
@@ -4179,156 +4179,156 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C26" t="n">
-        <v>11.2</v>
+        <v>12.667</v>
       </c>
       <c r="D26" t="n">
+        <v>2.833</v>
+      </c>
+      <c r="E26" t="n">
+        <v>4.333</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="G26" t="n">
+        <v>5.667</v>
+      </c>
+      <c r="H26" t="n">
         <v>2</v>
       </c>
-      <c r="E26" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="F26" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="G26" t="n">
-        <v>6</v>
-      </c>
-      <c r="H26" t="n">
-        <v>2.4</v>
-      </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="J26" t="n">
-        <v>2.8</v>
+        <v>2.667</v>
       </c>
       <c r="K26" t="n">
-        <v>1.4</v>
+        <v>1.167</v>
       </c>
       <c r="L26" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="M26" t="n">
-        <v>0.4</v>
+        <v>0.667</v>
       </c>
       <c r="N26" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="R26" t="n">
-        <v>2.4</v>
+        <v>2.333</v>
       </c>
       <c r="S26" t="n">
-        <v>2.4</v>
+        <v>2.167</v>
       </c>
       <c r="T26" t="n">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="U26" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="V26" t="n">
-        <v>0.6</v>
+        <v>0.833</v>
       </c>
       <c r="W26" t="n">
-        <v>0.4</v>
+        <v>0.667</v>
       </c>
       <c r="X26" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.8</v>
+        <v>1.333</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.4</v>
+        <v>0.667</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AD26" t="n">
         <v>0.667</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.2</v>
+        <v>1.167</v>
       </c>
       <c r="AF26" t="n">
         <v>2</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.6</v>
+        <v>0.583</v>
       </c>
       <c r="AH26" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="AI26" t="n">
-        <v>2</v>
+        <v>1.667</v>
       </c>
       <c r="AJ26" t="n">
         <v>0.5</v>
       </c>
       <c r="AK26" t="n">
-        <v>0.6</v>
+        <v>0.833</v>
       </c>
       <c r="AL26" t="n">
         <v>4</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.15</v>
+        <v>0.208</v>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>23:16</t>
+          <t>26:15</t>
         </is>
       </c>
       <c r="AO26" t="n">
-        <v>11.32</v>
+        <v>11.6</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.468</v>
+        <v>0.533</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.522</v>
+        <v>0.571</v>
       </c>
       <c r="AR26" t="n">
-        <v>0.989</v>
+        <v>1.092</v>
       </c>
       <c r="AS26" t="n">
-        <v>0.053</v>
+        <v>0.043</v>
       </c>
       <c r="AT26" t="n">
-        <v>0.255</v>
+        <v>0.2</v>
       </c>
       <c r="AU26" t="n">
-        <v>4.667</v>
+        <v>5.333</v>
       </c>
       <c r="AV26" t="n">
-        <v>0.214</v>
+        <v>0.196</v>
       </c>
       <c r="AW26" t="n">
-        <v>0.026</v>
+        <v>0.02</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.063</v>
+        <v>0.048</v>
       </c>
       <c r="AY26" t="n">
-        <v>0.095</v>
+        <v>0.08799999999999999</v>
       </c>
     </row>
     <row r="27">
@@ -4338,156 +4338,156 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C27" t="n">
-        <v>13.2</v>
+        <v>13.167</v>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>3.333</v>
       </c>
       <c r="E27" t="n">
-        <v>4.6</v>
+        <v>5.167</v>
       </c>
       <c r="F27" t="n">
-        <v>2</v>
+        <v>1.667</v>
       </c>
       <c r="G27" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="H27" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="I27" t="n">
-        <v>1.4</v>
+        <v>1.833</v>
       </c>
       <c r="J27" t="n">
-        <v>1.6</v>
+        <v>1.833</v>
       </c>
       <c r="K27" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="L27" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.167</v>
+      </c>
+      <c r="T27" t="n">
+        <v>88</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="V27" t="n">
+        <v>2.167</v>
+      </c>
+      <c r="W27" t="n">
         <v>1</v>
       </c>
-      <c r="M27" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S27" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="T27" t="n">
-        <v>74</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V27" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0.6</v>
-      </c>
       <c r="X27" t="n">
-        <v>0.2</v>
+        <v>0.667</v>
       </c>
       <c r="Y27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC27" t="n">
         <v>1</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.2</v>
       </c>
       <c r="AD27" t="n">
         <v>0.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.4</v>
+        <v>1.333</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.583</v>
+        <v>0.533</v>
       </c>
       <c r="AH27" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.2</v>
+        <v>1.167</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.167</v>
+        <v>0.143</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AL27" t="n">
-        <v>4</v>
+        <v>4.333</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.45</v>
+        <v>0.346</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>25:17</t>
+          <t>26:35</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>11.616</v>
+        <v>12.64</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.612</v>
+        <v>0.547</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.634</v>
+        <v>0.574</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.136</v>
+        <v>1.042</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.103</v>
+        <v>0.092</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.122</v>
+        <v>0.141</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.333</v>
+        <v>1.571</v>
       </c>
       <c r="AV27" t="n">
-        <v>0.202</v>
+        <v>0.211</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.04</v>
+        <v>0.033</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.124</v>
+        <v>0.141</v>
       </c>
       <c r="AY27" t="n">
-        <v>0.057</v>
+        <v>0.061</v>
       </c>
     </row>
     <row r="28">
@@ -4637,16 +4637,16 @@
         <v>0</v>
       </c>
       <c r="AV28" t="n">
-        <v>0.183</v>
+        <v>0.184</v>
       </c>
       <c r="AW28" t="n">
-        <v>0.029</v>
+        <v>0.031</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.185</v>
+        <v>0.19</v>
       </c>
       <c r="AY28" t="n">
-        <v>0.022</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="29">
@@ -4656,88 +4656,88 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C29" t="n">
         <v>10</v>
       </c>
       <c r="D29" t="n">
-        <v>2.6</v>
+        <v>2.833</v>
       </c>
       <c r="E29" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="G29" t="n">
-        <v>3</v>
+        <v>2.667</v>
       </c>
       <c r="H29" t="n">
-        <v>1.8</v>
+        <v>1.833</v>
       </c>
       <c r="I29" t="n">
         <v>2</v>
       </c>
       <c r="J29" t="n">
-        <v>1.4</v>
+        <v>1.333</v>
       </c>
       <c r="K29" t="n">
-        <v>2.6</v>
+        <v>2.667</v>
       </c>
       <c r="L29" t="n">
-        <v>1.4</v>
+        <v>1.833</v>
       </c>
       <c r="M29" t="n">
-        <v>1.2</v>
+        <v>1.167</v>
       </c>
       <c r="N29" t="n">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="R29" t="n">
-        <v>1.2</v>
+        <v>1.167</v>
       </c>
       <c r="S29" t="n">
-        <v>1.8</v>
+        <v>2.167</v>
       </c>
       <c r="T29" t="n">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="U29" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V29" t="n">
-        <v>2.2</v>
+        <v>2.167</v>
       </c>
       <c r="W29" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="X29" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.6</v>
+        <v>2.833</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.6</v>
+        <v>3.833</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.722</v>
+        <v>0.739</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AD29" t="n">
         <v>0</v>
@@ -4746,66 +4746,66 @@
         <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="AI29" t="n">
         <v>1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="AK29" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AL29" t="n">
-        <v>2</v>
+        <v>1.667</v>
       </c>
       <c r="AM29" t="n">
         <v>0.3</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>21:39</t>
+          <t>21:49</t>
         </is>
       </c>
       <c r="AO29" t="n">
-        <v>8.48</v>
+        <v>8.712999999999999</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.586</v>
+        <v>0.57</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.635</v>
+        <v>0.621</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.179</v>
+        <v>1.148</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.077</v>
       </c>
       <c r="AT29" t="n">
-        <v>0.257</v>
+        <v>0.256</v>
       </c>
       <c r="AU29" t="n">
-        <v>2.333</v>
+        <v>2</v>
       </c>
       <c r="AV29" t="n">
-        <v>0.172</v>
+        <v>0.177</v>
       </c>
       <c r="AW29" t="n">
-        <v>0.065</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.126</v>
+        <v>0.131</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.047</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="30">
@@ -4815,88 +4815,88 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C30" t="n">
-        <v>4.6</v>
+        <v>5.333</v>
       </c>
       <c r="D30" t="n">
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="G30" t="n">
-        <v>3.6</v>
+        <v>3.167</v>
       </c>
       <c r="H30" t="n">
-        <v>0.8</v>
+        <v>1.333</v>
       </c>
       <c r="I30" t="n">
-        <v>1.4</v>
+        <v>1.833</v>
       </c>
       <c r="J30" t="n">
-        <v>1.6</v>
+        <v>1.667</v>
       </c>
       <c r="K30" t="n">
-        <v>2.6</v>
+        <v>2.667</v>
       </c>
       <c r="L30" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="M30" t="n">
-        <v>0.4</v>
+        <v>0.833</v>
       </c>
       <c r="N30" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.6</v>
+        <v>1.667</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.6</v>
+        <v>1.667</v>
       </c>
       <c r="R30" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="S30" t="n">
-        <v>2.2</v>
+        <v>2.333</v>
       </c>
       <c r="T30" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="U30" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="V30" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W30" t="n">
-        <v>0.4</v>
+        <v>0.833</v>
       </c>
       <c r="X30" t="n">
-        <v>0.2</v>
+        <v>0.333</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.2</v>
+        <v>1.167</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.5</v>
+        <v>0.571</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="AC30" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="AD30" t="n">
         <v>0.4</v>
@@ -4905,66 +4905,66 @@
         <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.2</v>
+        <v>0.333</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.4</v>
+        <v>1.333</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.143</v>
+        <v>0.25</v>
       </c>
       <c r="AK30" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="AL30" t="n">
-        <v>2.2</v>
+        <v>1.833</v>
       </c>
       <c r="AM30" t="n">
         <v>0.182</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>8.616</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.297</v>
+        <v>0.353</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.328</v>
+        <v>0.412</v>
       </c>
       <c r="AR30" t="n">
-        <v>0.534</v>
+        <v>0.655</v>
       </c>
       <c r="AS30" t="n">
-        <v>0.186</v>
+        <v>0.205</v>
       </c>
       <c r="AT30" t="n">
-        <v>0.125</v>
+        <v>0.235</v>
       </c>
       <c r="AU30" t="n">
         <v>1</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.218</v>
+        <v>0.213</v>
       </c>
       <c r="AW30" t="n">
-        <v>0.046</v>
+        <v>0.041</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.156</v>
+        <v>0.169</v>
       </c>
       <c r="AY30" t="n">
-        <v>0.051</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="31">
@@ -4974,156 +4974,156 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C31" t="n">
-        <v>7.6</v>
+        <v>8.5</v>
       </c>
       <c r="D31" t="n">
-        <v>2.2</v>
+        <v>2.833</v>
       </c>
       <c r="E31" t="n">
-        <v>5</v>
+        <v>5.333</v>
       </c>
       <c r="F31" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="G31" t="n">
-        <v>1.8</v>
+        <v>1.667</v>
       </c>
       <c r="H31" t="n">
-        <v>1.4</v>
+        <v>1.333</v>
       </c>
       <c r="I31" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="K31" t="n">
-        <v>3.8</v>
+        <v>3.833</v>
       </c>
       <c r="L31" t="n">
-        <v>2</v>
+        <v>1.833</v>
       </c>
       <c r="M31" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="N31" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="R31" t="n">
-        <v>2.2</v>
+        <v>2.333</v>
       </c>
       <c r="S31" t="n">
-        <v>1.8</v>
+        <v>1.667</v>
       </c>
       <c r="T31" t="n">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="U31" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="W31" t="n">
         <v>1</v>
       </c>
-      <c r="V31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0.8</v>
-      </c>
       <c r="X31" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.667</v>
+        <v>0.714</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="AG31" t="n">
         <v>0.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AJ31" t="n">
         <v>0.333</v>
       </c>
       <c r="AK31" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.2</v>
+        <v>1.167</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.333</v>
+        <v>0.286</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>22:19</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>9.568</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.456</v>
+        <v>0.512</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.489</v>
+        <v>0.539</v>
       </c>
       <c r="AR31" t="n">
-        <v>0.794</v>
+        <v>0.906</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.188</v>
+        <v>0.16</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.206</v>
+        <v>0.19</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.889</v>
+        <v>2</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.213</v>
+        <v>0.186</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.101</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.201</v>
+        <v>0.184</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.112</v>
+        <v>0.095</v>
       </c>
     </row>
     <row r="32">
@@ -5133,40 +5133,40 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C32" t="n">
-        <v>17.6</v>
+        <v>18.667</v>
       </c>
       <c r="D32" t="n">
-        <v>3.4</v>
+        <v>3.667</v>
       </c>
       <c r="E32" t="n">
-        <v>5.4</v>
+        <v>6.333</v>
       </c>
       <c r="F32" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="G32" t="n">
-        <v>6.2</v>
+        <v>6.167</v>
       </c>
       <c r="H32" t="n">
-        <v>3</v>
+        <v>3.833</v>
       </c>
       <c r="I32" t="n">
-        <v>3.2</v>
+        <v>4.167</v>
       </c>
       <c r="J32" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="K32" t="n">
-        <v>2</v>
+        <v>2.333</v>
       </c>
       <c r="L32" t="n">
         <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>1.4</v>
+        <v>1.167</v>
       </c>
       <c r="N32" t="n">
         <v>1</v>
@@ -5175,114 +5175,114 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.2</v>
+        <v>1.833</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.2</v>
+        <v>1.833</v>
       </c>
       <c r="R32" t="n">
-        <v>1.4</v>
+        <v>1.333</v>
       </c>
       <c r="S32" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="T32" t="n">
-        <v>121</v>
+        <v>152</v>
       </c>
       <c r="U32" t="n">
-        <v>4</v>
+        <v>3.333</v>
       </c>
       <c r="V32" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="W32" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="X32" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.2</v>
+        <v>2.167</v>
       </c>
       <c r="Z32" t="n">
-        <v>3</v>
+        <v>3.167</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.733</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.2</v>
+        <v>1.167</v>
       </c>
       <c r="AG32" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="AH32" t="n">
         <v>0.333</v>
       </c>
-      <c r="AH32" t="n">
-        <v>0.4</v>
-      </c>
       <c r="AI32" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AJ32" t="n">
         <v>0.667</v>
       </c>
       <c r="AK32" t="n">
-        <v>2.2</v>
+        <v>2.167</v>
       </c>
       <c r="AL32" t="n">
-        <v>5.6</v>
+        <v>5.667</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.393</v>
+        <v>0.382</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>25:56</t>
+          <t>28:49</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>15.208</v>
+        <v>16.167</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.629</v>
+        <v>0.593</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.677</v>
+        <v>0.651</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.157</v>
+        <v>1.155</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.145</v>
+        <v>0.113</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.259</v>
+        <v>0.307</v>
       </c>
       <c r="AU32" t="n">
-        <v>2.636</v>
+        <v>3.273</v>
       </c>
       <c r="AV32" t="n">
-        <v>0.258</v>
+        <v>0.249</v>
       </c>
       <c r="AW32" t="n">
-        <v>0.039</v>
+        <v>0.036</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.081</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.213</v>
+        <v>0.209</v>
       </c>
     </row>
     <row r="33">
@@ -5292,156 +5292,156 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C33" t="n">
-        <v>4.8</v>
+        <v>4.333</v>
       </c>
       <c r="D33" t="n">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="E33" t="n">
-        <v>1.8</v>
+        <v>1.833</v>
       </c>
       <c r="F33" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="G33" t="n">
-        <v>3.4</v>
+        <v>2.833</v>
       </c>
       <c r="H33" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="I33" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="K33" t="n">
-        <v>2.2</v>
+        <v>1.833</v>
       </c>
       <c r="L33" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="S33" t="n">
         <v>1</v>
       </c>
-      <c r="M33" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="S33" t="n">
-        <v>1.2</v>
-      </c>
       <c r="T33" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="U33" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="V33" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="W33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AA33" t="n">
         <v>0.6</v>
       </c>
-      <c r="X33" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0.667</v>
-      </c>
       <c r="AB33" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AD33" t="n">
         <v>0.333</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AG33" t="n">
         <v>0.333</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AI33" t="n">
-        <v>2</v>
+        <v>1.667</v>
       </c>
       <c r="AJ33" t="n">
         <v>0.1</v>
       </c>
       <c r="AK33" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.4</v>
+        <v>1.167</v>
       </c>
       <c r="AM33" t="n">
         <v>0.429</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>7.328</v>
+        <v>6.607</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.385</v>
+        <v>0.393</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.419</v>
+        <v>0.424</v>
       </c>
       <c r="AR33" t="n">
-        <v>0.655</v>
+        <v>0.656</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.218</v>
+        <v>0.227</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.154</v>
+        <v>0.143</v>
       </c>
       <c r="AU33" t="n">
-        <v>0.5</v>
+        <v>0.444</v>
       </c>
       <c r="AV33" t="n">
-        <v>0.188</v>
+        <v>0.166</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.058</v>
+        <v>0.049</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.134</v>
+        <v>0.111</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="34">
@@ -5451,16 +5451,16 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C34" t="n">
-        <v>7.2</v>
+        <v>6.833</v>
       </c>
       <c r="D34" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>4.6</v>
+        <v>4.167</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -5469,138 +5469,138 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.833</v>
+      </c>
+      <c r="L34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.167</v>
+      </c>
+      <c r="T34" t="n">
+        <v>66</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>2.667</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>3.333</v>
+      </c>
+      <c r="AA34" t="n">
         <v>0.8</v>
       </c>
-      <c r="I34" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J34" t="n">
+      <c r="AB34" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AD34" t="n">
         <v>0.4</v>
       </c>
-      <c r="K34" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L34" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2</v>
-      </c>
-      <c r="T34" t="n">
-        <v>59</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0.789</v>
-      </c>
-      <c r="AB34" t="n">
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN34" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AO34" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0.649</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AT34" t="n">
         <v>0.2</v>
       </c>
-      <c r="AC34" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>18:19</t>
-        </is>
-      </c>
-      <c r="AO34" t="n">
-        <v>6.144</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>0.696</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>0.627</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>1.172</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>0.174</v>
-      </c>
       <c r="AU34" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AV34" t="n">
-        <v>0.147</v>
+        <v>0.139</v>
       </c>
       <c r="AW34" t="n">
-        <v>0.153</v>
+        <v>0.145</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.194</v>
+        <v>0.17</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.013</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="35">
@@ -5610,7 +5610,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -5769,156 +5769,156 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C36" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="D36" t="n">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="E36" t="n">
-        <v>2.2</v>
+        <v>2.333</v>
       </c>
       <c r="F36" t="n">
-        <v>1.2</v>
+        <v>1.167</v>
       </c>
       <c r="G36" t="n">
-        <v>2.4</v>
+        <v>2.333</v>
       </c>
       <c r="H36" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="I36" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="J36" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="K36" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="L36" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="M36" t="n">
-        <v>0.2</v>
+        <v>0.333</v>
       </c>
       <c r="N36" t="n">
-        <v>0.2</v>
+        <v>0.333</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="R36" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="T36" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U36" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="V36" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="W36" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="X36" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="Z36" t="n">
         <v>1</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="AC36" t="n">
-        <v>1</v>
+        <v>1.167</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.6</v>
+        <v>0.571</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
       </c>
       <c r="AH36" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AJ36" t="n">
         <v>0.8</v>
       </c>
-      <c r="AI36" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>1</v>
-      </c>
       <c r="AK36" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>5.576</v>
+        <v>5.48</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.554</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.586</v>
+        <v>0.571</v>
       </c>
       <c r="AR36" t="n">
         <v>1.004</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.143</v>
+        <v>0.122</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AU36" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AV36" t="n">
-        <v>0.17</v>
+        <v>0.172</v>
       </c>
       <c r="AW36" t="n">
-        <v>0.042</v>
+        <v>0.037</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.044</v>
+        <v>0.038</v>
       </c>
       <c r="AY36" t="n">
-        <v>0.051</v>
+        <v>0.046</v>
       </c>
     </row>
     <row r="37">
@@ -5928,106 +5928,106 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C37" t="n">
-        <v>8</v>
+        <v>8.25</v>
       </c>
       <c r="D37" t="n">
-        <v>1.333</v>
+        <v>1.75</v>
       </c>
       <c r="E37" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G37" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R37" t="n">
         <v>2</v>
       </c>
-      <c r="F37" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="G37" t="n">
-        <v>5</v>
-      </c>
-      <c r="H37" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="I37" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="J37" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="K37" t="n">
-        <v>3</v>
-      </c>
-      <c r="L37" t="n">
-        <v>2</v>
-      </c>
-      <c r="M37" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.667</v>
-      </c>
       <c r="S37" t="n">
-        <v>1.333</v>
+        <v>1.25</v>
       </c>
       <c r="T37" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="U37" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="V37" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="W37" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="X37" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.333</v>
+        <v>1.25</v>
       </c>
       <c r="Z37" t="n">
         <v>2</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.667</v>
+        <v>0.625</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH37" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="AI37" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AJ37" t="n">
         <v>0.333</v>
@@ -6043,41 +6043,41 @@
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>7.92</v>
+        <v>8.16</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.476</v>
+        <v>0.5</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.527</v>
+        <v>0.521</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.01</v>
+        <v>1.011</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.042</v>
+        <v>0.031</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.19</v>
+        <v>0.138</v>
       </c>
       <c r="AU37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.179</v>
+        <v>0.178</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.103</v>
+        <v>0.077</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.161</v>
+        <v>0.172</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.055</v>
+        <v>0.047</v>
       </c>
     </row>
     <row r="38">
@@ -6246,43 +6246,43 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C39" t="n">
         <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="E39" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="H39" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="I39" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="L39" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="M39" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -6297,16 +6297,16 @@
         <v>1</v>
       </c>
       <c r="S39" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="T39" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U39" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="V39" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="W39" t="n">
         <v>0</v>
@@ -6315,19 +6315,19 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="AB39" t="n">
         <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>
@@ -6354,45 +6354,45 @@
         <v>0</v>
       </c>
       <c r="AL39" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AM39" t="n">
         <v>0</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>05:02</t>
+          <t>06:48</t>
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>1.97</v>
+        <v>1.976</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.429</v>
+        <v>0.444</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.508</v>
+        <v>0.506</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.015</v>
+        <v>1.012</v>
       </c>
       <c r="AS39" t="n">
         <v>0</v>
       </c>
       <c r="AT39" t="n">
-        <v>0.286</v>
+        <v>0.222</v>
       </c>
       <c r="AU39" t="n">
         <v>0</v>
       </c>
       <c r="AV39" t="n">
-        <v>0.172</v>
+        <v>0.129</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.099</v>
+        <v>0.092</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.104</v>
+        <v>0.095</v>
       </c>
       <c r="AY39" t="n">
         <v>0</v>
@@ -6405,7 +6405,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
@@ -6432,10 +6432,10 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>2.4</v>
+        <v>2.667</v>
       </c>
       <c r="L40" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -6447,7 +6447,7 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6564,153 +6564,153 @@
         </is>
       </c>
       <c r="B41" t="n">
+        <v>6</v>
+      </c>
+      <c r="C41" t="n">
+        <v>96.333</v>
+      </c>
+      <c r="D41" t="n">
+        <v>23.833</v>
+      </c>
+      <c r="E41" t="n">
+        <v>40.667</v>
+      </c>
+      <c r="F41" t="n">
+        <v>11</v>
+      </c>
+      <c r="G41" t="n">
+        <v>34</v>
+      </c>
+      <c r="H41" t="n">
+        <v>15.667</v>
+      </c>
+      <c r="I41" t="n">
+        <v>20.667</v>
+      </c>
+      <c r="J41" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="K41" t="n">
+        <v>27.667</v>
+      </c>
+      <c r="L41" t="n">
+        <v>14.167</v>
+      </c>
+      <c r="M41" t="n">
+        <v>8.667</v>
+      </c>
+      <c r="N41" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>10.167</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>10</v>
+      </c>
+      <c r="R41" t="n">
+        <v>19.333</v>
+      </c>
+      <c r="S41" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="T41" t="n">
+        <v>726</v>
+      </c>
+      <c r="U41" t="n">
+        <v>13.667</v>
+      </c>
+      <c r="V41" t="n">
+        <v>14</v>
+      </c>
+      <c r="W41" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="X41" t="n">
         <v>5</v>
       </c>
-      <c r="C41" t="n">
-        <v>93.2</v>
-      </c>
-      <c r="D41" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="E41" t="n">
-        <v>37.6</v>
-      </c>
-      <c r="F41" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="G41" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="H41" t="n">
-        <v>15</v>
-      </c>
-      <c r="I41" t="n">
-        <v>20</v>
-      </c>
-      <c r="J41" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="K41" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="L41" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="M41" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="N41" t="n">
-        <v>6</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>11</v>
-      </c>
-      <c r="R41" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="S41" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="T41" t="n">
-        <v>584</v>
-      </c>
-      <c r="U41" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="V41" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="W41" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="X41" t="n">
-        <v>4.8</v>
-      </c>
       <c r="Y41" t="n">
-        <v>14.6</v>
+        <v>16.167</v>
       </c>
       <c r="Z41" t="n">
-        <v>21</v>
+        <v>22.833</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.695</v>
+        <v>0.708</v>
       </c>
       <c r="AB41" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="AC41" t="n">
-        <v>8.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.39</v>
+        <v>0.421</v>
       </c>
       <c r="AE41" t="n">
-        <v>3.6</v>
+        <v>3.667</v>
       </c>
       <c r="AF41" t="n">
-        <v>8.4</v>
+        <v>8.333</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.429</v>
+        <v>0.44</v>
       </c>
       <c r="AH41" t="n">
-        <v>3.6</v>
+        <v>3.167</v>
       </c>
       <c r="AI41" t="n">
-        <v>10.4</v>
+        <v>9.333</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.346</v>
+        <v>0.339</v>
       </c>
       <c r="AK41" t="n">
-        <v>8.199999999999999</v>
+        <v>7.833</v>
       </c>
       <c r="AL41" t="n">
-        <v>25.2</v>
+        <v>24.667</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.325</v>
+        <v>0.318</v>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>205:00</t>
+          <t>208:20</t>
         </is>
       </c>
       <c r="AO41" t="n">
-        <v>93.2</v>
+        <v>93.92700000000001</v>
       </c>
       <c r="AP41" t="n">
-        <v>0.534</v>
+        <v>0.54</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.575</v>
       </c>
       <c r="AR41" t="n">
-        <v>1</v>
+        <v>1.026</v>
       </c>
       <c r="AS41" t="n">
-        <v>0.12</v>
+        <v>0.108</v>
       </c>
       <c r="AT41" t="n">
-        <v>0.205</v>
+        <v>0.21</v>
       </c>
       <c r="AU41" t="n">
-        <v>1.857</v>
+        <v>2.016</v>
       </c>
       <c r="AV41" t="n">
         <v>0.2</v>
       </c>
       <c r="AW41" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AX41" t="n">
-        <v>0.14</v>
+        <v>0.142</v>
       </c>
       <c r="AY41" t="n">
         <v>0</v>
@@ -6723,153 +6723,153 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C42" t="n">
-        <v>83.8</v>
+        <v>88.667</v>
       </c>
       <c r="D42" t="n">
-        <v>18.8</v>
+        <v>19.167</v>
       </c>
       <c r="E42" t="n">
-        <v>36.4</v>
+        <v>36.5</v>
       </c>
       <c r="F42" t="n">
-        <v>11</v>
+        <v>12.333</v>
       </c>
       <c r="G42" t="n">
-        <v>32.8</v>
+        <v>33.667</v>
       </c>
       <c r="H42" t="n">
-        <v>13.2</v>
+        <v>13.333</v>
       </c>
       <c r="I42" t="n">
-        <v>16.8</v>
+        <v>17.5</v>
       </c>
       <c r="J42" t="n">
-        <v>17.6</v>
+        <v>18.333</v>
       </c>
       <c r="K42" t="n">
-        <v>26.2</v>
+        <v>25.833</v>
       </c>
       <c r="L42" t="n">
-        <v>11.8</v>
+        <v>11.167</v>
       </c>
       <c r="M42" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="N42" t="n">
-        <v>5.8</v>
+        <v>6.333</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>14.4</v>
+        <v>13.833</v>
       </c>
       <c r="Q42" t="n">
-        <v>13.2</v>
+        <v>12.667</v>
       </c>
       <c r="R42" t="n">
-        <v>21.4</v>
+        <v>21.667</v>
       </c>
       <c r="S42" t="n">
-        <v>18.6</v>
+        <v>19.167</v>
       </c>
       <c r="T42" t="n">
-        <v>463</v>
+        <v>589</v>
       </c>
       <c r="U42" t="n">
-        <v>8.199999999999999</v>
+        <v>8.333</v>
       </c>
       <c r="V42" t="n">
-        <v>13.2</v>
+        <v>11.833</v>
       </c>
       <c r="W42" t="n">
-        <v>4.6</v>
+        <v>4.167</v>
       </c>
       <c r="X42" t="n">
-        <v>3.2</v>
+        <v>2.833</v>
       </c>
       <c r="Y42" t="n">
-        <v>12.8</v>
+        <v>13</v>
       </c>
       <c r="Z42" t="n">
-        <v>19.2</v>
+        <v>19</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.667</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="AB42" t="n">
-        <v>4.2</v>
+        <v>4.333</v>
       </c>
       <c r="AC42" t="n">
-        <v>11.6</v>
+        <v>12</v>
       </c>
       <c r="AD42" t="n">
-        <v>0.362</v>
+        <v>0.361</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.8</v>
+        <v>1.833</v>
       </c>
       <c r="AF42" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.321</v>
+        <v>0.333</v>
       </c>
       <c r="AH42" t="n">
-        <v>3.8</v>
+        <v>3.667</v>
       </c>
       <c r="AI42" t="n">
-        <v>9.199999999999999</v>
+        <v>8.667</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.413</v>
+        <v>0.423</v>
       </c>
       <c r="AK42" t="n">
-        <v>7.2</v>
+        <v>8.667</v>
       </c>
       <c r="AL42" t="n">
-        <v>23.6</v>
+        <v>25</v>
       </c>
       <c r="AM42" t="n">
-        <v>0.305</v>
+        <v>0.347</v>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>205:00</t>
+          <t>208:20</t>
         </is>
       </c>
       <c r="AO42" t="n">
-        <v>90.992</v>
+        <v>91.7</v>
       </c>
       <c r="AP42" t="n">
-        <v>0.51</v>
+        <v>0.537</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.547</v>
+        <v>0.569</v>
       </c>
       <c r="AR42" t="n">
-        <v>0.921</v>
+        <v>0.967</v>
       </c>
       <c r="AS42" t="n">
-        <v>0.158</v>
+        <v>0.151</v>
       </c>
       <c r="AT42" t="n">
-        <v>0.191</v>
+        <v>0.19</v>
       </c>
       <c r="AU42" t="n">
-        <v>1.222</v>
+        <v>1.325</v>
       </c>
       <c r="AV42" t="n">
         <v>0.195</v>
       </c>
       <c r="AW42" t="n">
-        <v>0.058</v>
+        <v>0.056</v>
       </c>
       <c r="AX42" t="n">
-        <v>0.134</v>
+        <v>0.133</v>
       </c>
       <c r="AY42" t="n">
         <v>0</v>

--- a/informes_data/ACB/2025-26/playoffs/aggregate/AGGREGATE_Valencia Basket.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate/AGGREGATE_Valencia Basket.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>478.56</v>
+        <v>552.24</v>
       </c>
       <c r="C2" t="n">
-        <v>480.88</v>
+        <v>555.46</v>
       </c>
       <c r="D2" t="n">
-        <v>120.19630677092</v>
+        <v>122.4210564217045</v>
       </c>
       <c r="E2" t="n">
-        <v>110.6305107303277</v>
+        <v>109.2787959529039</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5401785714285714</v>
+        <v>0.5537109375</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1082404712896586</v>
+        <v>0.1110699740836727</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3541666666666667</v>
+        <v>0.3542435424354243</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2098214285714286</v>
+        <v>0.220703125</v>
       </c>
       <c r="J2" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K2" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="L2" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="M2" t="n">
+        <v>71</v>
+      </c>
+      <c r="N2" t="n">
+        <v>113</v>
+      </c>
+      <c r="O2" t="n">
+        <v>159</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.310546875</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>28</v>
+      </c>
+      <c r="R2" t="n">
+        <v>68</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.1328125</v>
+      </c>
+      <c r="T2" t="n">
+        <v>27</v>
+      </c>
+      <c r="U2" t="n">
         <v>60</v>
       </c>
-      <c r="N2" t="n">
-        <v>97</v>
-      </c>
-      <c r="O2" t="n">
-        <v>137</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.3058035714285715</v>
-      </c>
-      <c r="Q2" t="n">
+      <c r="V2" t="n">
+        <v>0.1171875</v>
+      </c>
+      <c r="W2" t="n">
         <v>24</v>
       </c>
-      <c r="R2" t="n">
-        <v>57</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.1272321428571428</v>
-      </c>
-      <c r="T2" t="n">
-        <v>22</v>
-      </c>
-      <c r="U2" t="n">
-        <v>50</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.1116071428571429</v>
-      </c>
-      <c r="W2" t="n">
-        <v>19</v>
-      </c>
       <c r="X2" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.125</v>
+        <v>0.126953125</v>
       </c>
       <c r="Z2" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="AA2" t="n">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3303571428571428</v>
+        <v>0.3125</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.708029197080292</v>
+        <v>0.710691823899371</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.4210526315789473</v>
+        <v>0.4117647058823529</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.3392857142857143</v>
+        <v>0.3692307692307693</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3175675675675675</v>
+        <v>0.33125</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.416058394160584</v>
+        <v>1.421383647798742</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.9705882352941176</v>
+        <v>1.026666666666667</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.9879518072289156</v>
+        <v>1.010989010989011</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.9882352941176471</v>
+        <v>0.9791666666666666</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.7</v>
+        <v>1.638888888888889</v>
       </c>
       <c r="AN2" t="n">
-        <v>2.016393442622951</v>
+        <v>1.986111111111111</v>
       </c>
       <c r="AO2" t="n">
-        <v>7.344262295081967</v>
+        <v>7.111111111111111</v>
       </c>
       <c r="AP2" t="n">
-        <v>9.360655737704919</v>
+        <v>9.097222222222221</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>79.76000000000001</v>
+        <v>78.89142857142858</v>
       </c>
       <c r="C3" t="n">
-        <v>80.14666666666666</v>
+        <v>79.35142857142857</v>
       </c>
       <c r="D3" t="n">
-        <v>120.19630677092</v>
+        <v>122.4210564217045</v>
       </c>
       <c r="E3" t="n">
-        <v>110.6305107303278</v>
+        <v>109.2787959529039</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5401785714285714</v>
+        <v>0.5537109375</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1082404712896586</v>
+        <v>0.1110699740836727</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3541666666666666</v>
+        <v>0.3542435424354243</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2098214285714286</v>
+        <v>0.220703125</v>
       </c>
       <c r="J3" t="n">
-        <v>13.66666666666667</v>
+        <v>13.14285714285714</v>
       </c>
       <c r="K3" t="n">
-        <v>14</v>
+        <v>13.42857142857143</v>
       </c>
       <c r="L3" t="n">
-        <v>8.5</v>
+        <v>8.428571428571429</v>
       </c>
       <c r="M3" t="n">
-        <v>10</v>
+        <v>10.14285714285714</v>
       </c>
       <c r="N3" t="n">
-        <v>16.16666666666667</v>
+        <v>16.14285714285714</v>
       </c>
       <c r="O3" t="n">
-        <v>22.83333333333333</v>
+        <v>22.71428571428572</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3058035714285715</v>
+        <v>0.3105468750000001</v>
       </c>
       <c r="Q3" t="n">
         <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>9.5</v>
+        <v>9.714285714285714</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1272321428571429</v>
+        <v>0.1328125</v>
       </c>
       <c r="T3" t="n">
-        <v>3.666666666666667</v>
+        <v>3.857142857142857</v>
       </c>
       <c r="U3" t="n">
-        <v>8.333333333333334</v>
+        <v>8.571428571428571</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1116071428571429</v>
+        <v>0.1171875</v>
       </c>
       <c r="W3" t="n">
-        <v>3.166666666666667</v>
+        <v>3.428571428571428</v>
       </c>
       <c r="X3" t="n">
-        <v>9.333333333333334</v>
+        <v>9.285714285714286</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.125</v>
+        <v>0.126953125</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.833333333333333</v>
+        <v>7.571428571428571</v>
       </c>
       <c r="AA3" t="n">
-        <v>24.66666666666667</v>
+        <v>22.85714285714286</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3303571428571429</v>
+        <v>0.3125</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.7080291970802921</v>
+        <v>0.710691823899371</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.4210526315789473</v>
+        <v>0.411764705882353</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.45</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.3392857142857142</v>
+        <v>0.3692307692307692</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3175675675675675</v>
+        <v>0.33125</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.416058394160584</v>
+        <v>1.421383647798742</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.8799999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.9705882352941176</v>
+        <v>1.026666666666667</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.9879518072289156</v>
+        <v>1.010989010989011</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.9882352941176471</v>
+        <v>0.9791666666666667</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.7</v>
+        <v>1.638888888888889</v>
       </c>
       <c r="AN3" t="n">
-        <v>2.016393442622951</v>
+        <v>1.986111111111111</v>
       </c>
       <c r="AO3" t="n">
-        <v>7.344262295081966</v>
+        <v>7.11111111111111</v>
       </c>
       <c r="AP3" t="n">
-        <v>9.360655737704917</v>
+        <v>9.097222222222221</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>483.2</v>
+        <v>558.6800000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>480.88</v>
+        <v>555.46</v>
       </c>
       <c r="D4" t="n">
-        <v>110.6305107303277</v>
+        <v>109.2787959529039</v>
       </c>
       <c r="E4" t="n">
-        <v>120.19630677092</v>
+        <v>122.4210564217045</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5368171021377672</v>
+        <v>0.5212121212121212</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1508542348237005</v>
+        <v>0.1422586293146574</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2875536480686695</v>
+        <v>0.2913669064748202</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1900237529691211</v>
+        <v>0.1838383838383838</v>
       </c>
       <c r="J4" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="K4" t="n">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="L4" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M4" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="N4" t="n">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="O4" t="n">
-        <v>114</v>
+        <v>145</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2707838479809976</v>
+        <v>0.2929292929292929</v>
       </c>
       <c r="Q4" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="R4" t="n">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="S4" t="n">
-        <v>0.171021377672209</v>
+        <v>0.1797979797979798</v>
       </c>
       <c r="T4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="U4" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="V4" t="n">
-        <v>0.07838479809976247</v>
+        <v>0.07676767676767676</v>
       </c>
       <c r="W4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X4" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1235154394299287</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="Z4" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="AA4" t="n">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3562945368171022</v>
+        <v>0.3393939393939394</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.6842105263157895</v>
+        <v>0.6758620689655173</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.3611111111111111</v>
+        <v>0.3483146067415731</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3157894736842105</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.4230769230769231</v>
+        <v>0.4181818181818182</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3466666666666667</v>
+        <v>0.3273809523809524</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.368421052631579</v>
+        <v>1.351724137931035</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.099009900990099</v>
+        <v>1.04932735426009</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.819672131147541</v>
+        <v>0.8611111111111112</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.059701492537313</v>
+        <v>1.024691358024691</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.470588235294118</v>
+        <v>1.5</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.325301204819277</v>
+        <v>1.373626373626374</v>
       </c>
       <c r="AO4" t="n">
-        <v>5.072289156626506</v>
+        <v>5.43956043956044</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.397590361445783</v>
+        <v>6.813186813186813</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>80.53333333333335</v>
+        <v>79.81142857142858</v>
       </c>
       <c r="C5" t="n">
-        <v>80.14666666666666</v>
+        <v>79.35142857142857</v>
       </c>
       <c r="D5" t="n">
-        <v>110.6305107303278</v>
+        <v>109.2787959529039</v>
       </c>
       <c r="E5" t="n">
-        <v>120.19630677092</v>
+        <v>122.4210564217045</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5368171021377673</v>
+        <v>0.5212121212121213</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1508542348237005</v>
+        <v>0.1422586293146574</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2875536480686695</v>
+        <v>0.2913669064748201</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1900237529691212</v>
+        <v>0.1838383838383839</v>
       </c>
       <c r="J5" t="n">
-        <v>8.333333333333334</v>
+        <v>8.857142857142858</v>
       </c>
       <c r="K5" t="n">
-        <v>11.83333333333333</v>
+        <v>11.85714285714286</v>
       </c>
       <c r="L5" t="n">
-        <v>4.166666666666667</v>
+        <v>4.714285714285714</v>
       </c>
       <c r="M5" t="n">
-        <v>12.66666666666667</v>
+        <v>11.42857142857143</v>
       </c>
       <c r="N5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O5" t="n">
-        <v>19</v>
+        <v>20.71428571428572</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2707838479809976</v>
+        <v>0.292929292929293</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.333333333333333</v>
+        <v>4.428571428571429</v>
       </c>
       <c r="R5" t="n">
-        <v>12</v>
+        <v>12.71428571428571</v>
       </c>
       <c r="S5" t="n">
-        <v>0.171021377672209</v>
+        <v>0.1797979797979798</v>
       </c>
       <c r="T5" t="n">
-        <v>1.833333333333333</v>
+        <v>1.714285714285714</v>
       </c>
       <c r="U5" t="n">
-        <v>5.5</v>
+        <v>5.428571428571429</v>
       </c>
       <c r="V5" t="n">
-        <v>0.07838479809976248</v>
+        <v>0.07676767676767678</v>
       </c>
       <c r="W5" t="n">
-        <v>3.666666666666667</v>
+        <v>3.285714285714286</v>
       </c>
       <c r="X5" t="n">
-        <v>8.666666666666666</v>
+        <v>7.857142857142857</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1235154394299288</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.666666666666666</v>
+        <v>7.857142857142857</v>
       </c>
       <c r="AA5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3562945368171022</v>
+        <v>0.3393939393939394</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.6842105263157895</v>
+        <v>0.6758620689655173</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.3611111111111111</v>
+        <v>0.3483146067415731</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3157894736842105</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.4230769230769231</v>
+        <v>0.4181818181818182</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3466666666666666</v>
+        <v>0.3273809523809524</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.368421052631579</v>
+        <v>1.351724137931035</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.099009900990099</v>
+        <v>1.04932735426009</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.8196721311475411</v>
+        <v>0.861111111111111</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.059701492537314</v>
+        <v>1.024691358024691</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.470588235294118</v>
+        <v>1.5</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.325301204819277</v>
+        <v>1.373626373626374</v>
       </c>
       <c r="AO5" t="n">
-        <v>5.072289156626505</v>
+        <v>5.439560439560439</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.397590361445782</v>
+        <v>6.813186813186813</v>
       </c>
     </row>
     <row r="7">
@@ -1419,34 +1419,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="D8" t="n">
+        <v>18</v>
+      </c>
+      <c r="E8" t="n">
+        <v>29</v>
+      </c>
+      <c r="F8" t="n">
+        <v>11</v>
+      </c>
+      <c r="G8" t="n">
+        <v>36</v>
+      </c>
+      <c r="H8" t="n">
+        <v>14</v>
+      </c>
+      <c r="I8" t="n">
         <v>17</v>
       </c>
-      <c r="E8" t="n">
-        <v>26</v>
-      </c>
-      <c r="F8" t="n">
-        <v>10</v>
-      </c>
-      <c r="G8" t="n">
-        <v>34</v>
-      </c>
-      <c r="H8" t="n">
-        <v>12</v>
-      </c>
-      <c r="I8" t="n">
-        <v>15</v>
-      </c>
       <c r="J8" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L8" t="n">
         <v>3</v>
@@ -1467,16 +1467,16 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
+        <v>15</v>
+      </c>
+      <c r="S8" t="n">
         <v>14</v>
       </c>
-      <c r="S8" t="n">
-        <v>13</v>
-      </c>
       <c r="T8" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="U8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="V8" t="n">
         <v>5</v>
@@ -1488,37 +1488,37 @@
         <v>3</v>
       </c>
       <c r="Y8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.75</v>
+        <v>0.778</v>
       </c>
       <c r="AB8" t="n">
         <v>4</v>
       </c>
       <c r="AC8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.667</v>
+        <v>0.571</v>
       </c>
       <c r="AE8" t="n">
         <v>7</v>
       </c>
       <c r="AF8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI8" t="n">
         <v>12</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0.583</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>10</v>
       </c>
       <c r="AJ8" t="n">
         <v>0.5</v>
@@ -1534,41 +1534,41 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>157:35</t>
+          <t>179:43</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>69.59999999999999</v>
+        <v>75.48</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.533</v>
+        <v>0.531</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.571</v>
+        <v>0.573</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.092</v>
+        <v>1.1</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.043</v>
+        <v>0.04</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.2</v>
+        <v>0.215</v>
       </c>
       <c r="AU8" t="n">
-        <v>5.333</v>
+        <v>6</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.196</v>
+        <v>0.188</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.02</v>
+        <v>0.018</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.048</v>
+        <v>0.052</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.083</v>
       </c>
     </row>
     <row r="9">
@@ -1578,22 +1578,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E9" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G9" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H9" t="n">
         <v>9</v>
@@ -1602,19 +1602,19 @@
         <v>11</v>
       </c>
       <c r="J9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K9" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L9" t="n">
         <v>5</v>
       </c>
       <c r="M9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1629,16 +1629,16 @@
         <v>11</v>
       </c>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T9" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="U9" t="n">
         <v>7</v>
       </c>
       <c r="V9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W9" t="n">
         <v>6</v>
@@ -1659,19 +1659,19 @@
         <v>3</v>
       </c>
       <c r="AC9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.5</v>
+        <v>0.429</v>
       </c>
       <c r="AE9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.533</v>
+        <v>0.529</v>
       </c>
       <c r="AH9" t="n">
         <v>1</v>
@@ -1683,439 +1683,439 @@
         <v>0.143</v>
       </c>
       <c r="AK9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.346</v>
+        <v>0.37</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>159:34</t>
+          <t>182:56</t>
         </is>
       </c>
       <c r="AO9" t="n">
-        <v>75.84</v>
+        <v>79.84</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.547</v>
+        <v>0.551</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.574</v>
+        <v>0.577</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.042</v>
+        <v>1.052</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.092</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.141</v>
+        <v>0.132</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.571</v>
+        <v>1.714</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.211</v>
+        <v>0.195</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.033</v>
+        <v>0.029</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.141</v>
+        <v>0.137</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.061</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>#3 N. REUVERS</t>
+          <t>#2 J. PUERTO</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
         <v>2</v>
       </c>
-      <c r="K10" t="n">
-        <v>6</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
+      <c r="X10" t="n">
         <v>2</v>
       </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>7</v>
-      </c>
-      <c r="S10" t="n">
-        <v>6</v>
-      </c>
-      <c r="T10" t="n">
-        <v>32</v>
-      </c>
-      <c r="U10" t="n">
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>04:01</t>
+        </is>
+      </c>
+      <c r="AO10" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0.532</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0.694</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="AT10" t="n">
         <v>2</v>
       </c>
-      <c r="V10" t="n">
-        <v>6</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>33:56</t>
-        </is>
-      </c>
-      <c r="AO10" t="n">
-        <v>14.08</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0.864</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0.888</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>1.776</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0.545</v>
-      </c>
       <c r="AU10" t="n">
         <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.184</v>
+        <v>0.321</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.031</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.19</v>
+        <v>0.26</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>#4 J. PRADILLA</t>
+          <t>#3 N. REUVERS</t>
         </is>
       </c>
       <c r="B11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" t="n">
+        <v>25</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>7</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4</v>
+      </c>
+      <c r="H11" t="n">
         <v>6</v>
       </c>
-      <c r="C11" t="n">
-        <v>60</v>
-      </c>
-      <c r="D11" t="n">
-        <v>17</v>
-      </c>
-      <c r="E11" t="n">
-        <v>27</v>
-      </c>
-      <c r="F11" t="n">
-        <v>5</v>
-      </c>
-      <c r="G11" t="n">
-        <v>16</v>
-      </c>
-      <c r="H11" t="n">
-        <v>11</v>
-      </c>
       <c r="I11" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="L11" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>7</v>
       </c>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T11" t="n">
-        <v>87</v>
+        <v>32</v>
       </c>
       <c r="U11" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="V11" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="W11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="Z11" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.739</v>
+        <v>1</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF11" t="n">
         <v>3</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AH11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
         <v>3</v>
       </c>
       <c r="AL11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>130:56</t>
+          <t>33:56</t>
         </is>
       </c>
       <c r="AO11" t="n">
-        <v>52.28</v>
+        <v>14.08</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.57</v>
+        <v>0.864</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.621</v>
+        <v>0.888</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.148</v>
+        <v>1.776</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.077</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.256</v>
+        <v>0.545</v>
       </c>
       <c r="AU11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.177</v>
+        <v>0.186</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.032</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.131</v>
+        <v>0.184</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.043</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>#5 S. DE LARREA</t>
+          <t>#4 J. PRADILLA</t>
         </is>
       </c>
       <c r="B12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C12" t="n">
+        <v>70</v>
+      </c>
+      <c r="D12" t="n">
+        <v>18</v>
+      </c>
+      <c r="E12" t="n">
+        <v>30</v>
+      </c>
+      <c r="F12" t="n">
         <v>6</v>
       </c>
-      <c r="C12" t="n">
-        <v>32</v>
-      </c>
-      <c r="D12" t="n">
+      <c r="G12" t="n">
+        <v>18</v>
+      </c>
+      <c r="H12" t="n">
+        <v>16</v>
+      </c>
+      <c r="I12" t="n">
+        <v>19</v>
+      </c>
+      <c r="J12" t="n">
+        <v>11</v>
+      </c>
+      <c r="K12" t="n">
+        <v>21</v>
+      </c>
+      <c r="L12" t="n">
+        <v>13</v>
+      </c>
+      <c r="M12" t="n">
+        <v>7</v>
+      </c>
+      <c r="N12" t="n">
         <v>6</v>
       </c>
-      <c r="E12" t="n">
-        <v>15</v>
-      </c>
-      <c r="F12" t="n">
-        <v>4</v>
-      </c>
-      <c r="G12" t="n">
-        <v>19</v>
-      </c>
-      <c r="H12" t="n">
-        <v>8</v>
-      </c>
-      <c r="I12" t="n">
-        <v>11</v>
-      </c>
-      <c r="J12" t="n">
-        <v>10</v>
-      </c>
-      <c r="K12" t="n">
-        <v>16</v>
-      </c>
-      <c r="L12" t="n">
-        <v>4</v>
-      </c>
-      <c r="M12" t="n">
-        <v>5</v>
-      </c>
-      <c r="N12" t="n">
-        <v>5</v>
-      </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="R12" t="n">
         <v>9</v>
       </c>
       <c r="S12" t="n">
+        <v>18</v>
+      </c>
+      <c r="T12" t="n">
+        <v>103</v>
+      </c>
+      <c r="U12" t="n">
         <v>14</v>
       </c>
-      <c r="T12" t="n">
-        <v>40</v>
-      </c>
-      <c r="U12" t="n">
-        <v>5</v>
-      </c>
       <c r="V12" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="W12" t="n">
         <v>5</v>
@@ -2124,22 +2124,22 @@
         <v>2</v>
       </c>
       <c r="Y12" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="Z12" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.571</v>
+        <v>0.72</v>
       </c>
       <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
         <v>2</v>
       </c>
-      <c r="AC12" t="n">
-        <v>5</v>
-      </c>
       <c r="AD12" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -2151,57 +2151,57 @@
         <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI12" t="n">
         <v>8</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.25</v>
+        <v>0.375</v>
       </c>
       <c r="AK12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.182</v>
+        <v>0.3</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>101:38</t>
+          <t>150:18</t>
         </is>
       </c>
       <c r="AO12" t="n">
-        <v>48.84</v>
+        <v>63.36</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.353</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.412</v>
+        <v>0.621</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.655</v>
+        <v>1.105</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.205</v>
+        <v>0.11</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.235</v>
+        <v>0.333</v>
       </c>
       <c r="AU12" t="n">
-        <v>1</v>
+        <v>1.571</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.213</v>
+        <v>0.189</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.041</v>
+        <v>0.093</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.169</v>
+        <v>0.146</v>
       </c>
       <c r="AY12" t="n">
         <v>0.05</v>
@@ -2210,731 +2210,731 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>#7 B. KEY</t>
+          <t>#5 S. DE LARREA</t>
         </is>
       </c>
       <c r="B13" t="n">
+        <v>7</v>
+      </c>
+      <c r="C13" t="n">
+        <v>42</v>
+      </c>
+      <c r="D13" t="n">
+        <v>7</v>
+      </c>
+      <c r="E13" t="n">
+        <v>18</v>
+      </c>
+      <c r="F13" t="n">
         <v>6</v>
       </c>
-      <c r="C13" t="n">
-        <v>51</v>
-      </c>
-      <c r="D13" t="n">
-        <v>17</v>
-      </c>
-      <c r="E13" t="n">
-        <v>32</v>
-      </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
+        <v>23</v>
+      </c>
+      <c r="H13" t="n">
+        <v>10</v>
+      </c>
+      <c r="I13" t="n">
+        <v>13</v>
+      </c>
+      <c r="J13" t="n">
+        <v>11</v>
+      </c>
+      <c r="K13" t="n">
+        <v>16</v>
+      </c>
+      <c r="L13" t="n">
+        <v>4</v>
+      </c>
+      <c r="M13" t="n">
+        <v>5</v>
+      </c>
+      <c r="N13" t="n">
+        <v>5</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>10</v>
+      </c>
+      <c r="R13" t="n">
+        <v>12</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="n">
+        <v>45</v>
+      </c>
+      <c r="U13" t="n">
+        <v>5</v>
+      </c>
+      <c r="V13" t="n">
+        <v>6</v>
+      </c>
+      <c r="W13" t="n">
+        <v>5</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AH13" t="n">
         <v>3</v>
       </c>
-      <c r="G13" t="n">
-        <v>10</v>
-      </c>
-      <c r="H13" t="n">
-        <v>8</v>
-      </c>
-      <c r="I13" t="n">
-        <v>12</v>
-      </c>
-      <c r="J13" t="n">
-        <v>18</v>
-      </c>
-      <c r="K13" t="n">
-        <v>23</v>
-      </c>
-      <c r="L13" t="n">
-        <v>11</v>
-      </c>
-      <c r="M13" t="n">
-        <v>6</v>
-      </c>
-      <c r="N13" t="n">
-        <v>6</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
+      <c r="AI13" t="n">
         <v>9</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>9</v>
-      </c>
-      <c r="R13" t="n">
-        <v>14</v>
-      </c>
-      <c r="S13" t="n">
-        <v>10</v>
-      </c>
-      <c r="T13" t="n">
-        <v>76</v>
-      </c>
-      <c r="U13" t="n">
-        <v>11</v>
-      </c>
-      <c r="V13" t="n">
-        <v>7</v>
-      </c>
-      <c r="W13" t="n">
-        <v>6</v>
-      </c>
-      <c r="X13" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0.714</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>3</v>
       </c>
       <c r="AJ13" t="n">
         <v>0.333</v>
       </c>
       <c r="AK13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL13" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.286</v>
+        <v>0.214</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>133:54</t>
+          <t>117:52</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>56.28</v>
+        <v>56.72</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.512</v>
+        <v>0.39</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.539</v>
+        <v>0.449</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.906</v>
+        <v>0.74</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.16</v>
+        <v>0.176</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.19</v>
+        <v>0.244</v>
       </c>
       <c r="AU13" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.186</v>
+        <v>0.215</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.036</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.184</v>
+        <v>0.142</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.095</v>
+        <v>0.047</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>#8 J. MONTERO</t>
+          <t>#7 B. KEY</t>
         </is>
       </c>
       <c r="B14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C14" t="n">
+        <v>66</v>
+      </c>
+      <c r="D14" t="n">
+        <v>23</v>
+      </c>
+      <c r="E14" t="n">
+        <v>43</v>
+      </c>
+      <c r="F14" t="n">
+        <v>4</v>
+      </c>
+      <c r="G14" t="n">
+        <v>11</v>
+      </c>
+      <c r="H14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I14" t="n">
+        <v>12</v>
+      </c>
+      <c r="J14" t="n">
+        <v>20</v>
+      </c>
+      <c r="K14" t="n">
+        <v>27</v>
+      </c>
+      <c r="L14" t="n">
+        <v>13</v>
+      </c>
+      <c r="M14" t="n">
         <v>6</v>
       </c>
-      <c r="C14" t="n">
-        <v>112</v>
-      </c>
-      <c r="D14" t="n">
-        <v>22</v>
-      </c>
-      <c r="E14" t="n">
-        <v>38</v>
-      </c>
-      <c r="F14" t="n">
+      <c r="N14" t="n">
+        <v>7</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>10</v>
+      </c>
+      <c r="R14" t="n">
         <v>15</v>
       </c>
-      <c r="G14" t="n">
-        <v>37</v>
-      </c>
-      <c r="H14" t="n">
-        <v>23</v>
-      </c>
-      <c r="I14" t="n">
-        <v>25</v>
-      </c>
-      <c r="J14" t="n">
-        <v>36</v>
-      </c>
-      <c r="K14" t="n">
-        <v>14</v>
-      </c>
-      <c r="L14" t="n">
-        <v>6</v>
-      </c>
-      <c r="M14" t="n">
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="n">
+        <v>93</v>
+      </c>
+      <c r="U14" t="n">
+        <v>11</v>
+      </c>
+      <c r="V14" t="n">
         <v>7</v>
       </c>
-      <c r="N14" t="n">
-        <v>6</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
+      <c r="W14" t="n">
+        <v>8</v>
+      </c>
+      <c r="X14" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC14" t="n">
         <v>11</v>
       </c>
-      <c r="Q14" t="n">
-        <v>11</v>
-      </c>
-      <c r="R14" t="n">
-        <v>8</v>
-      </c>
-      <c r="S14" t="n">
-        <v>30</v>
-      </c>
-      <c r="T14" t="n">
-        <v>152</v>
-      </c>
-      <c r="U14" t="n">
-        <v>20</v>
-      </c>
-      <c r="V14" t="n">
-        <v>15</v>
-      </c>
-      <c r="W14" t="n">
-        <v>9</v>
-      </c>
-      <c r="X14" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0.6840000000000001</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>12</v>
-      </c>
       <c r="AD14" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG14" t="n">
         <v>0.5</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>7</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0.429</v>
       </c>
       <c r="AH14" t="n">
         <v>2</v>
       </c>
       <c r="AI14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="AK14" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="AL14" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.382</v>
+        <v>0.286</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>172:54</t>
+          <t>154:34</t>
         </is>
       </c>
       <c r="AO14" t="n">
-        <v>97</v>
+        <v>69.28</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.593</v>
+        <v>0.537</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.651</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.155</v>
+        <v>0.953</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.113</v>
+        <v>0.144</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.307</v>
+        <v>0.148</v>
       </c>
       <c r="AU14" t="n">
-        <v>3.273</v>
+        <v>2</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.249</v>
+        <v>0.201</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.036</v>
+        <v>0.09</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.182</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.209</v>
+        <v>0.092</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>#10 O. MOORE</t>
+          <t>#8 J. MONTERO</t>
         </is>
       </c>
       <c r="B15" t="n">
+        <v>7</v>
+      </c>
+      <c r="C15" t="n">
+        <v>131</v>
+      </c>
+      <c r="D15" t="n">
+        <v>28</v>
+      </c>
+      <c r="E15" t="n">
+        <v>46</v>
+      </c>
+      <c r="F15" t="n">
+        <v>15</v>
+      </c>
+      <c r="G15" t="n">
+        <v>40</v>
+      </c>
+      <c r="H15" t="n">
+        <v>30</v>
+      </c>
+      <c r="I15" t="n">
+        <v>32</v>
+      </c>
+      <c r="J15" t="n">
+        <v>42</v>
+      </c>
+      <c r="K15" t="n">
+        <v>19</v>
+      </c>
+      <c r="L15" t="n">
         <v>6</v>
       </c>
-      <c r="C15" t="n">
-        <v>26</v>
-      </c>
-      <c r="D15" t="n">
+      <c r="M15" t="n">
+        <v>8</v>
+      </c>
+      <c r="N15" t="n">
+        <v>6</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>13</v>
+      </c>
+      <c r="R15" t="n">
+        <v>9</v>
+      </c>
+      <c r="S15" t="n">
+        <v>34</v>
+      </c>
+      <c r="T15" t="n">
+        <v>179</v>
+      </c>
+      <c r="U15" t="n">
+        <v>22</v>
+      </c>
+      <c r="V15" t="n">
+        <v>15</v>
+      </c>
+      <c r="W15" t="n">
+        <v>13</v>
+      </c>
+      <c r="X15" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.696</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE15" t="n">
         <v>5</v>
       </c>
-      <c r="E15" t="n">
-        <v>11</v>
-      </c>
-      <c r="F15" t="n">
-        <v>4</v>
-      </c>
-      <c r="G15" t="n">
-        <v>17</v>
-      </c>
-      <c r="H15" t="n">
-        <v>4</v>
-      </c>
-      <c r="I15" t="n">
-        <v>6</v>
-      </c>
-      <c r="J15" t="n">
-        <v>4</v>
-      </c>
-      <c r="K15" t="n">
-        <v>11</v>
-      </c>
-      <c r="L15" t="n">
-        <v>5</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" t="n">
+      <c r="AF15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="AH15" t="n">
         <v>2</v>
       </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>9</v>
-      </c>
-      <c r="R15" t="n">
-        <v>5</v>
-      </c>
-      <c r="S15" t="n">
-        <v>6</v>
-      </c>
-      <c r="T15" t="n">
-        <v>20</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1</v>
-      </c>
-      <c r="V15" t="n">
-        <v>5</v>
-      </c>
-      <c r="W15" t="n">
+      <c r="AI15" t="n">
         <v>3</v>
       </c>
-      <c r="X15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>10</v>
-      </c>
       <c r="AJ15" t="n">
-        <v>0.1</v>
+        <v>0.667</v>
       </c>
       <c r="AK15" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="AL15" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.429</v>
+        <v>0.351</v>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>105:57</t>
+          <t>196:19</t>
         </is>
       </c>
       <c r="AO15" t="n">
-        <v>39.64</v>
+        <v>113.08</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.393</v>
+        <v>0.587</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.424</v>
+        <v>0.654</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.656</v>
+        <v>1.158</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.227</v>
+        <v>0.115</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.143</v>
+        <v>0.349</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.444</v>
+        <v>3.231</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.166</v>
+        <v>0.258</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.049</v>
+        <v>0.033</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.111</v>
+        <v>0.101</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.02</v>
+        <v>0.208</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>#12 N. SAKO</t>
+          <t>#10 O. MOORE</t>
         </is>
       </c>
       <c r="B16" t="n">
+        <v>7</v>
+      </c>
+      <c r="C16" t="n">
+        <v>37</v>
+      </c>
+      <c r="D16" t="n">
         <v>6</v>
       </c>
-      <c r="C16" t="n">
-        <v>41</v>
-      </c>
-      <c r="D16" t="n">
-        <v>18</v>
-      </c>
       <c r="E16" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H16" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" t="n">
+        <v>6</v>
+      </c>
+      <c r="J16" t="n">
         <v>5</v>
       </c>
-      <c r="I16" t="n">
-        <v>15</v>
-      </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
+        <v>11</v>
+      </c>
+      <c r="L16" t="n">
+        <v>6</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
         <v>3</v>
       </c>
-      <c r="K16" t="n">
-        <v>17</v>
-      </c>
-      <c r="L16" t="n">
-        <v>15</v>
-      </c>
-      <c r="M16" t="n">
-        <v>2</v>
-      </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>10</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6</v>
+      </c>
+      <c r="S16" t="n">
+        <v>7</v>
+      </c>
+      <c r="T16" t="n">
+        <v>32</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" t="n">
+        <v>5</v>
+      </c>
+      <c r="W16" t="n">
+        <v>3</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" t="n">
         <v>4</v>
       </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2</v>
-      </c>
-      <c r="R16" t="n">
+      <c r="Z16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL16" t="n">
         <v>10</v>
       </c>
-      <c r="S16" t="n">
-        <v>13</v>
-      </c>
-      <c r="T16" t="n">
-        <v>66</v>
-      </c>
-      <c r="U16" t="n">
-        <v>9</v>
-      </c>
-      <c r="V16" t="n">
-        <v>6</v>
-      </c>
-      <c r="W16" t="n">
-        <v>5</v>
-      </c>
-      <c r="X16" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>107:31</t>
+          <t>122:37</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>33.6</v>
+        <v>45.64</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.72</v>
+        <v>0.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.649</v>
+        <v>0.519</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.22</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.06</v>
+        <v>0.219</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.2</v>
+        <v>0.121</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.139</v>
+        <v>0.167</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.145</v>
+        <v>0.052</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.17</v>
+        <v>0.094</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.016</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>#13 D. THOMPSON</t>
+          <t>#12 N. SAKO</t>
         </is>
       </c>
       <c r="B17" t="n">
+        <v>7</v>
+      </c>
+      <c r="C17" t="n">
+        <v>45</v>
+      </c>
+      <c r="D17" t="n">
+        <v>20</v>
+      </c>
+      <c r="E17" t="n">
+        <v>27</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
         <v>5</v>
       </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2965,564 +2965,564 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>123:46</t>
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>37.04</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>0.741</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>0.661</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.215</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>0.081</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>0.185</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>1.333</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>0.134</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>0.147</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>#23 A. CÁRDENAS</t>
+          <t>#13 D. THOMPSON</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.571</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>85:02</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO18" t="n">
-        <v>32.88</v>
+        <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.554</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.571</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.004</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.122</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.07099999999999999</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.172</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.037</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.038</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.046</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>#24 M. COSTELLO</t>
+          <t>#23 A. CÁRDENAS</t>
         </is>
       </c>
       <c r="B19" t="n">
+        <v>7</v>
+      </c>
+      <c r="C19" t="n">
+        <v>35</v>
+      </c>
+      <c r="D19" t="n">
+        <v>6</v>
+      </c>
+      <c r="E19" t="n">
+        <v>16</v>
+      </c>
+      <c r="F19" t="n">
+        <v>7</v>
+      </c>
+      <c r="G19" t="n">
+        <v>14</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2</v>
+      </c>
+      <c r="J19" t="n">
+        <v>12</v>
+      </c>
+      <c r="K19" t="n">
+        <v>5</v>
+      </c>
+      <c r="L19" t="n">
         <v>4</v>
       </c>
-      <c r="C19" t="n">
-        <v>33</v>
-      </c>
-      <c r="D19" t="n">
-        <v>7</v>
-      </c>
-      <c r="E19" t="n">
-        <v>10</v>
-      </c>
-      <c r="F19" t="n">
+      <c r="M19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
         <v>5</v>
       </c>
-      <c r="G19" t="n">
-        <v>19</v>
-      </c>
-      <c r="H19" t="n">
-        <v>4</v>
-      </c>
-      <c r="I19" t="n">
-        <v>6</v>
-      </c>
-      <c r="J19" t="n">
-        <v>6</v>
-      </c>
-      <c r="K19" t="n">
-        <v>13</v>
-      </c>
-      <c r="L19" t="n">
-        <v>6</v>
-      </c>
-      <c r="M19" t="n">
+      <c r="Q19" t="n">
         <v>5</v>
       </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
       <c r="R19" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
       </c>
       <c r="T19" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="U19" t="n">
+        <v>3</v>
+      </c>
+      <c r="V19" t="n">
+        <v>5</v>
+      </c>
+      <c r="W19" t="n">
+        <v>5</v>
+      </c>
+      <c r="X19" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y19" t="n">
         <v>2</v>
       </c>
-      <c r="V19" t="n">
+      <c r="Z19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
         <v>2</v>
       </c>
-      <c r="W19" t="n">
-        <v>2</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y19" t="n">
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI19" t="n">
         <v>5</v>
       </c>
-      <c r="Z19" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI19" t="n">
+      <c r="AJ19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AK19" t="n">
         <v>3</v>
       </c>
-      <c r="AJ19" t="n">
+      <c r="AL19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AM19" t="n">
         <v>0.333</v>
       </c>
-      <c r="AK19" t="n">
-        <v>4</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>16</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>0.25</v>
-      </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>81:16</t>
+          <t>99:18</t>
         </is>
       </c>
       <c r="AO19" t="n">
-        <v>32.64</v>
+        <v>35.88</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.521</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.011</v>
+        <v>0.975</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.031</v>
+        <v>0.139</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.138</v>
+        <v>0.067</v>
       </c>
       <c r="AU19" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.178</v>
+        <v>0.162</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.077</v>
+        <v>0.043</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.172</v>
+        <v>0.053</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.03</v>
+        <v>0.052</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>#32 I. NOGUÉS</t>
+          <t>#24 M. COSTELLO</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>92:52</t>
         </is>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>38.08</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>0.545</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>1.077</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>0.053</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>0.152</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>0.183</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>0.081</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>0.168</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>#77 Y. SIMA</t>
+          <t>#32 I. NOGUÉS</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3534,19 +3534,19 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
@@ -3555,19 +3555,19 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3594,45 +3594,45 @@
         <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
         <v>0</v>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>34:02</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO21" t="n">
-        <v>9.880000000000001</v>
+        <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.444</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.506</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.012</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
         <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>0.222</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
         <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.129</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.092</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.095</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
         <v>0</v>
@@ -3641,71 +3641,71 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>#77 Y. SIMA</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>6</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="L22" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
@@ -3714,22 +3714,22 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3750,48 +3750,48 @@
         <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>46:13</t>
         </is>
       </c>
       <c r="AO22" t="n">
-        <v>0</v>
+        <v>15.88</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>0.598</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.196</v>
       </c>
       <c r="AS22" t="n">
         <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>0.133</v>
       </c>
       <c r="AU22" t="n">
         <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>0.116</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>0.113</v>
       </c>
       <c r="AY22" t="n">
         <v>0</v>
@@ -3800,157 +3800,157 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Equip</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C23" t="n">
-        <v>578</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>244</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>166</v>
+        <v>19</v>
       </c>
       <c r="L23" t="n">
-        <v>85</v>
+        <v>12</v>
       </c>
       <c r="M23" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>726</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.708</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.421</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.339</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.318</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>1250:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO23" t="n">
-        <v>563.5599999999999</v>
+        <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.54</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.575</v>
+        <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.026</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="n">
-        <v>0.108</v>
+        <v>0</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>2.016</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.07099999999999999</v>
+        <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.142</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="n">
         <v>0</v>
@@ -3959,157 +3959,157 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Rival</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C24" t="n">
-        <v>532</v>
+        <v>680</v>
       </c>
       <c r="D24" t="n">
-        <v>115</v>
+        <v>168</v>
       </c>
       <c r="E24" t="n">
-        <v>219</v>
+        <v>287</v>
       </c>
       <c r="F24" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G24" t="n">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="H24" t="n">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="I24" t="n">
-        <v>105</v>
+        <v>146</v>
       </c>
       <c r="J24" t="n">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="K24" t="n">
-        <v>155</v>
+        <v>197</v>
       </c>
       <c r="L24" t="n">
-        <v>67</v>
+        <v>96</v>
       </c>
       <c r="M24" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="N24" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="Q24" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="R24" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="S24" t="n">
-        <v>115</v>
+        <v>147</v>
       </c>
       <c r="T24" t="n">
-        <v>589</v>
+        <v>857</v>
       </c>
       <c r="U24" t="n">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="V24" t="n">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="W24" t="n">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="X24" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="Y24" t="n">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="Z24" t="n">
-        <v>114</v>
+        <v>159</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.711</v>
       </c>
       <c r="AB24" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AC24" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.361</v>
+        <v>0.412</v>
       </c>
       <c r="AE24" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="AF24" t="n">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.333</v>
+        <v>0.45</v>
       </c>
       <c r="AH24" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AI24" t="n">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.423</v>
+        <v>0.369</v>
       </c>
       <c r="AK24" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AL24" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.347</v>
+        <v>0.331</v>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>1250:00</t>
+          <t>1450:00</t>
         </is>
       </c>
       <c r="AO24" t="n">
-        <v>550.2</v>
+        <v>648.24</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.537</v>
+        <v>0.554</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.569</v>
+        <v>0.59</v>
       </c>
       <c r="AR24" t="n">
-        <v>0.967</v>
+        <v>1.049</v>
       </c>
       <c r="AS24" t="n">
-        <v>0.151</v>
+        <v>0.111</v>
       </c>
       <c r="AT24" t="n">
-        <v>0.19</v>
+        <v>0.221</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.325</v>
+        <v>1.986</v>
       </c>
       <c r="AV24" t="n">
         <v>0.2</v>
       </c>
       <c r="AW24" t="n">
-        <v>0.058</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.129</v>
+        <v>0.142</v>
       </c>
       <c r="AY24" t="n">
         <v>0</v>
@@ -4118,626 +4118,626 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>--- PER GAME STATS ---</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
-      <c r="AA25" t="inlineStr"/>
-      <c r="AB25" t="inlineStr"/>
-      <c r="AC25" t="inlineStr"/>
-      <c r="AD25" t="inlineStr"/>
-      <c r="AE25" t="inlineStr"/>
-      <c r="AF25" t="inlineStr"/>
-      <c r="AG25" t="inlineStr"/>
-      <c r="AH25" t="inlineStr"/>
-      <c r="AI25" t="inlineStr"/>
-      <c r="AJ25" t="inlineStr"/>
-      <c r="AK25" t="inlineStr"/>
-      <c r="AL25" t="inlineStr"/>
-      <c r="AM25" t="inlineStr"/>
-      <c r="AN25" t="inlineStr"/>
-      <c r="AO25" t="inlineStr"/>
-      <c r="AP25" t="inlineStr"/>
-      <c r="AQ25" t="inlineStr"/>
-      <c r="AR25" t="inlineStr"/>
-      <c r="AS25" t="inlineStr"/>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AU25" t="inlineStr"/>
-      <c r="AV25" t="inlineStr"/>
-      <c r="AW25" t="inlineStr"/>
-      <c r="AX25" t="inlineStr"/>
-      <c r="AY25" t="inlineStr"/>
+          <t>Rival</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>7</v>
+      </c>
+      <c r="C25" t="n">
+        <v>607</v>
+      </c>
+      <c r="D25" t="n">
+        <v>141</v>
+      </c>
+      <c r="E25" t="n">
+        <v>272</v>
+      </c>
+      <c r="F25" t="n">
+        <v>78</v>
+      </c>
+      <c r="G25" t="n">
+        <v>223</v>
+      </c>
+      <c r="H25" t="n">
+        <v>91</v>
+      </c>
+      <c r="I25" t="n">
+        <v>122</v>
+      </c>
+      <c r="J25" t="n">
+        <v>125</v>
+      </c>
+      <c r="K25" t="n">
+        <v>175</v>
+      </c>
+      <c r="L25" t="n">
+        <v>81</v>
+      </c>
+      <c r="M25" t="n">
+        <v>48</v>
+      </c>
+      <c r="N25" t="n">
+        <v>45</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>91</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>80</v>
+      </c>
+      <c r="R25" t="n">
+        <v>147</v>
+      </c>
+      <c r="S25" t="n">
+        <v>134</v>
+      </c>
+      <c r="T25" t="n">
+        <v>670</v>
+      </c>
+      <c r="U25" t="n">
+        <v>62</v>
+      </c>
+      <c r="V25" t="n">
+        <v>83</v>
+      </c>
+      <c r="W25" t="n">
+        <v>33</v>
+      </c>
+      <c r="X25" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>98</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>145</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>31</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>89</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>38</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>168</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="AN25" t="inlineStr">
+        <is>
+          <t>1450:00</t>
+        </is>
+      </c>
+      <c r="AO25" t="n">
+        <v>639.6799999999999</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0.521</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0.553</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0.949</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>1.374</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>#0 B. BADIO (Per Game)</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>6</v>
-      </c>
-      <c r="C26" t="n">
-        <v>12.667</v>
-      </c>
-      <c r="D26" t="n">
-        <v>2.833</v>
-      </c>
-      <c r="E26" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="F26" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="G26" t="n">
-        <v>5.667</v>
-      </c>
-      <c r="H26" t="n">
-        <v>2</v>
-      </c>
-      <c r="I26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J26" t="n">
-        <v>2.667</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1.167</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R26" t="n">
-        <v>2.333</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.167</v>
-      </c>
-      <c r="T26" t="n">
-        <v>69</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.167</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>0.583</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>4</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>0.208</v>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>26:15</t>
-        </is>
-      </c>
-      <c r="AO26" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>1.092</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>5.333</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>0.196</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>0.08799999999999999</v>
-      </c>
+          <t>--- PER GAME STATS ---</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr"/>
+      <c r="AJ26" t="inlineStr"/>
+      <c r="AK26" t="inlineStr"/>
+      <c r="AL26" t="inlineStr"/>
+      <c r="AM26" t="inlineStr"/>
+      <c r="AN26" t="inlineStr"/>
+      <c r="AO26" t="inlineStr"/>
+      <c r="AP26" t="inlineStr"/>
+      <c r="AQ26" t="inlineStr"/>
+      <c r="AR26" t="inlineStr"/>
+      <c r="AS26" t="inlineStr"/>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AU26" t="inlineStr"/>
+      <c r="AV26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr"/>
+      <c r="AX26" t="inlineStr"/>
+      <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>#1 K. TAYLOR (Per Game)</t>
+          <t>#0 B. BADIO (Per Game)</t>
         </is>
       </c>
       <c r="B27" t="n">
+        <v>7</v>
+      </c>
+      <c r="C27" t="n">
+        <v>11.857</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2.571</v>
+      </c>
+      <c r="E27" t="n">
+        <v>4.143</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.571</v>
+      </c>
+      <c r="G27" t="n">
+        <v>5.143</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2.429</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.571</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1.286</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2.143</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2</v>
+      </c>
+      <c r="T27" t="n">
+        <v>77</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.714</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.286</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.857</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1.714</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>3.429</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0.208</v>
+      </c>
+      <c r="AN27" t="inlineStr">
+        <is>
+          <t>25:40</t>
+        </is>
+      </c>
+      <c r="AO27" t="n">
+        <v>10.783</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="AU27" t="n">
         <v>6</v>
       </c>
-      <c r="C27" t="n">
-        <v>13.167</v>
-      </c>
-      <c r="D27" t="n">
-        <v>3.333</v>
-      </c>
-      <c r="E27" t="n">
-        <v>5.167</v>
-      </c>
-      <c r="F27" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="G27" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I27" t="n">
-        <v>1.833</v>
-      </c>
-      <c r="J27" t="n">
-        <v>1.833</v>
-      </c>
-      <c r="K27" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1.167</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1.167</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.833</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.167</v>
-      </c>
-      <c r="T27" t="n">
-        <v>88</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.167</v>
-      </c>
-      <c r="V27" t="n">
-        <v>2.167</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>1.167</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>0.346</v>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>26:35</t>
-        </is>
-      </c>
-      <c r="AO27" t="n">
-        <v>12.64</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>0.547</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>0.574</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>1.042</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>0.092</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>0.141</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>1.571</v>
-      </c>
       <c r="AV27" t="n">
-        <v>0.211</v>
+        <v>0.188</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.033</v>
+        <v>0.018</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.141</v>
+        <v>0.052</v>
       </c>
       <c r="AY27" t="n">
-        <v>0.061</v>
+        <v>0.083</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>#3 N. REUVERS (Per Game)</t>
+          <t>#1 K. TAYLOR (Per Game)</t>
         </is>
       </c>
       <c r="B28" t="n">
+        <v>7</v>
+      </c>
+      <c r="C28" t="n">
+        <v>12</v>
+      </c>
+      <c r="D28" t="n">
         <v>3</v>
       </c>
-      <c r="C28" t="n">
-        <v>8.333</v>
-      </c>
-      <c r="D28" t="n">
-        <v>1.667</v>
-      </c>
       <c r="E28" t="n">
-        <v>2.333</v>
+        <v>4.857</v>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>1.571</v>
       </c>
       <c r="G28" t="n">
-        <v>1.333</v>
+        <v>4.857</v>
       </c>
       <c r="H28" t="n">
-        <v>2</v>
+        <v>1.286</v>
       </c>
       <c r="I28" t="n">
-        <v>2.333</v>
+        <v>1.571</v>
       </c>
       <c r="J28" t="n">
-        <v>0.667</v>
+        <v>1.714</v>
       </c>
       <c r="K28" t="n">
-        <v>2</v>
+        <v>3.429</v>
       </c>
       <c r="L28" t="n">
-        <v>0.333</v>
+        <v>0.714</v>
       </c>
       <c r="M28" t="n">
-        <v>0.667</v>
+        <v>1.571</v>
       </c>
       <c r="N28" t="n">
-        <v>0.333</v>
+        <v>0.571</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>2.333</v>
+        <v>1.571</v>
       </c>
       <c r="S28" t="n">
         <v>2</v>
       </c>
       <c r="T28" t="n">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="U28" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="V28" t="n">
-        <v>2</v>
+        <v>2.143</v>
       </c>
       <c r="W28" t="n">
-        <v>0.333</v>
+        <v>0.857</v>
       </c>
       <c r="X28" t="n">
-        <v>0.333</v>
+        <v>0.571</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.333</v>
+        <v>1.286</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.333</v>
+        <v>1.429</v>
       </c>
       <c r="AA28" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>0.429</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>0.429</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.333</v>
+        <v>1.286</v>
       </c>
       <c r="AF28" t="n">
-        <v>1</v>
+        <v>2.429</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.333</v>
+        <v>0.529</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="AI28" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="AK28" t="n">
-        <v>1</v>
+        <v>1.429</v>
       </c>
       <c r="AL28" t="n">
-        <v>1</v>
+        <v>3.857</v>
       </c>
       <c r="AM28" t="n">
-        <v>1</v>
+        <v>0.37</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>26:08</t>
         </is>
       </c>
       <c r="AO28" t="n">
-        <v>4.693</v>
+        <v>11.406</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.864</v>
+        <v>0.551</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.888</v>
+        <v>0.577</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.776</v>
+        <v>1.052</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AT28" t="n">
-        <v>0.545</v>
+        <v>0.132</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>1.714</v>
       </c>
       <c r="AV28" t="n">
-        <v>0.184</v>
+        <v>0.195</v>
       </c>
       <c r="AW28" t="n">
-        <v>0.031</v>
+        <v>0.029</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.19</v>
+        <v>0.137</v>
       </c>
       <c r="AY28" t="n">
-        <v>0.021</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>#4 J. PRADILLA (Per Game)</t>
+          <t>#2 J. PUERTO (Per Game)</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>2.833</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>0.833</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>2.667</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.833</v>
+        <v>2</v>
       </c>
       <c r="I29" t="n">
         <v>2</v>
       </c>
       <c r="J29" t="n">
-        <v>1.333</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>2.667</v>
+        <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>1.833</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.167</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>0.833</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>1.167</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.167</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>87</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>2.167</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>0.833</v>
+        <v>2</v>
       </c>
       <c r="X29" t="n">
-        <v>0.333</v>
+        <v>2</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.833</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.833</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.739</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
         <v>0</v>
@@ -4746,1222 +4746,1222 @@
         <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
-        <v>1.667</v>
+        <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>21:49</t>
+          <t>04:01</t>
         </is>
       </c>
       <c r="AO29" t="n">
-        <v>8.712999999999999</v>
+        <v>2.88</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.57</v>
+        <v>0</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.621</v>
+        <v>0.532</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.148</v>
+        <v>0.694</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.077</v>
+        <v>0.347</v>
       </c>
       <c r="AT29" t="n">
-        <v>0.256</v>
+        <v>2</v>
       </c>
       <c r="AU29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV29" t="n">
-        <v>0.177</v>
+        <v>0.321</v>
       </c>
       <c r="AW29" t="n">
-        <v>0.08799999999999999</v>
+        <v>0</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.131</v>
+        <v>0.26</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>#5 S. DE LARREA (Per Game)</t>
+          <t>#3 N. REUVERS (Per Game)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C30" t="n">
-        <v>5.333</v>
+        <v>8.333</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>1.667</v>
       </c>
       <c r="E30" t="n">
-        <v>2.5</v>
+        <v>2.333</v>
       </c>
       <c r="F30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2.333</v>
+      </c>
+      <c r="J30" t="n">
         <v>0.667</v>
       </c>
-      <c r="G30" t="n">
-        <v>3.167</v>
-      </c>
-      <c r="H30" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="I30" t="n">
-        <v>1.833</v>
-      </c>
-      <c r="J30" t="n">
-        <v>1.667</v>
-      </c>
       <c r="K30" t="n">
-        <v>2.667</v>
+        <v>2</v>
       </c>
       <c r="L30" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="M30" t="n">
         <v>0.667</v>
       </c>
-      <c r="M30" t="n">
-        <v>0.833</v>
-      </c>
       <c r="N30" t="n">
-        <v>0.833</v>
+        <v>0.333</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.667</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.667</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.5</v>
+        <v>2.333</v>
       </c>
       <c r="S30" t="n">
-        <v>2.333</v>
+        <v>2</v>
       </c>
       <c r="T30" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="U30" t="n">
-        <v>0.833</v>
+        <v>0.667</v>
       </c>
       <c r="V30" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="W30" t="n">
-        <v>0.833</v>
+        <v>0.333</v>
       </c>
       <c r="X30" t="n">
         <v>0.333</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.667</v>
+        <v>1.333</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.167</v>
+        <v>1.333</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.571</v>
+        <v>1</v>
       </c>
       <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
         <v>0.333</v>
       </c>
-      <c r="AC30" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>0</v>
-      </c>
       <c r="AF30" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
         <v>0.333</v>
       </c>
-      <c r="AI30" t="n">
-        <v>1.333</v>
-      </c>
       <c r="AJ30" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.833</v>
+        <v>1</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.182</v>
+        <v>1</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>8.140000000000001</v>
+        <v>4.693</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.353</v>
+        <v>0.864</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.412</v>
+        <v>0.888</v>
       </c>
       <c r="AR30" t="n">
-        <v>0.655</v>
+        <v>1.776</v>
       </c>
       <c r="AS30" t="n">
-        <v>0.205</v>
+        <v>0</v>
       </c>
       <c r="AT30" t="n">
-        <v>0.235</v>
+        <v>0.545</v>
       </c>
       <c r="AU30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.213</v>
+        <v>0.186</v>
       </c>
       <c r="AW30" t="n">
-        <v>0.041</v>
+        <v>0.032</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.169</v>
+        <v>0.184</v>
       </c>
       <c r="AY30" t="n">
-        <v>0.05</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>#7 B. KEY (Per Game)</t>
+          <t>#4 J. PRADILLA (Per Game)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C31" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="D31" t="n">
-        <v>2.833</v>
+        <v>2.571</v>
       </c>
       <c r="E31" t="n">
-        <v>5.333</v>
+        <v>4.286</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5</v>
+        <v>0.857</v>
       </c>
       <c r="G31" t="n">
-        <v>1.667</v>
+        <v>2.571</v>
       </c>
       <c r="H31" t="n">
-        <v>1.333</v>
+        <v>2.286</v>
       </c>
       <c r="I31" t="n">
+        <v>2.714</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.571</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.857</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.286</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.571</v>
+      </c>
+      <c r="T31" t="n">
+        <v>103</v>
+      </c>
+      <c r="U31" t="n">
         <v>2</v>
       </c>
-      <c r="J31" t="n">
-        <v>3</v>
-      </c>
-      <c r="K31" t="n">
-        <v>3.833</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1.833</v>
-      </c>
-      <c r="M31" t="n">
-        <v>1</v>
-      </c>
-      <c r="N31" t="n">
-        <v>1</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R31" t="n">
-        <v>2.333</v>
-      </c>
-      <c r="S31" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="T31" t="n">
-        <v>76</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.833</v>
-      </c>
       <c r="V31" t="n">
-        <v>1.167</v>
+        <v>1.857</v>
       </c>
       <c r="W31" t="n">
-        <v>1</v>
+        <v>0.714</v>
       </c>
       <c r="X31" t="n">
-        <v>0.5</v>
+        <v>0.286</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.5</v>
+        <v>2.571</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.5</v>
+        <v>3.571</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.714</v>
+        <v>0.72</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.5</v>
+        <v>0.286</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.111</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1.143</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1.429</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AN31" t="inlineStr">
+        <is>
+          <t>21:28</t>
+        </is>
+      </c>
+      <c r="AO31" t="n">
+        <v>9.051</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0.621</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1.105</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AT31" t="n">
         <v>0.333</v>
       </c>
-      <c r="AG31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>1.167</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>22:19</t>
-        </is>
-      </c>
-      <c r="AO31" t="n">
-        <v>9.380000000000001</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>0.512</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>0.539</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>0.906</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>0.19</v>
-      </c>
       <c r="AU31" t="n">
-        <v>2</v>
+        <v>1.571</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.186</v>
+        <v>0.189</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.093</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.184</v>
+        <v>0.146</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.095</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>#8 J. MONTERO (Per Game)</t>
+          <t>#5 S. DE LARREA (Per Game)</t>
         </is>
       </c>
       <c r="B32" t="n">
+        <v>7</v>
+      </c>
+      <c r="C32" t="n">
         <v>6</v>
       </c>
-      <c r="C32" t="n">
-        <v>18.667</v>
-      </c>
       <c r="D32" t="n">
-        <v>3.667</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>6.333</v>
+        <v>2.571</v>
       </c>
       <c r="F32" t="n">
-        <v>2.5</v>
+        <v>0.857</v>
       </c>
       <c r="G32" t="n">
-        <v>6.167</v>
+        <v>3.286</v>
       </c>
       <c r="H32" t="n">
-        <v>3.833</v>
+        <v>1.429</v>
       </c>
       <c r="I32" t="n">
-        <v>4.167</v>
+        <v>1.857</v>
       </c>
       <c r="J32" t="n">
-        <v>6</v>
+        <v>1.571</v>
       </c>
       <c r="K32" t="n">
-        <v>2.333</v>
+        <v>2.286</v>
       </c>
       <c r="L32" t="n">
-        <v>1</v>
+        <v>0.571</v>
       </c>
       <c r="M32" t="n">
-        <v>1.167</v>
+        <v>0.714</v>
       </c>
       <c r="N32" t="n">
-        <v>1</v>
+        <v>0.714</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.833</v>
+        <v>1.429</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.833</v>
+        <v>1.429</v>
       </c>
       <c r="R32" t="n">
-        <v>1.333</v>
+        <v>1.714</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>2.143</v>
       </c>
       <c r="T32" t="n">
-        <v>152</v>
+        <v>45</v>
       </c>
       <c r="U32" t="n">
-        <v>3.333</v>
+        <v>0.714</v>
       </c>
       <c r="V32" t="n">
-        <v>2.5</v>
+        <v>0.857</v>
       </c>
       <c r="W32" t="n">
-        <v>1.5</v>
+        <v>0.714</v>
       </c>
       <c r="X32" t="n">
-        <v>1</v>
+        <v>0.286</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.167</v>
+        <v>0.571</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.167</v>
+        <v>1</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.571</v>
       </c>
       <c r="AB32" t="n">
-        <v>1</v>
+        <v>0.286</v>
       </c>
       <c r="AC32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>1.286</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="AL32" t="n">
         <v>2</v>
       </c>
-      <c r="AD32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.167</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>2.167</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>5.667</v>
-      </c>
       <c r="AM32" t="n">
-        <v>0.382</v>
+        <v>0.214</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>28:49</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>16.167</v>
+        <v>8.103</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.593</v>
+        <v>0.39</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.651</v>
+        <v>0.449</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.155</v>
+        <v>0.74</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.113</v>
+        <v>0.176</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.307</v>
+        <v>0.244</v>
       </c>
       <c r="AU32" t="n">
-        <v>3.273</v>
+        <v>1.1</v>
       </c>
       <c r="AV32" t="n">
-        <v>0.249</v>
+        <v>0.215</v>
       </c>
       <c r="AW32" t="n">
         <v>0.036</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.142</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.209</v>
+        <v>0.047</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>#10 O. MOORE (Per Game)</t>
+          <t>#7 B. KEY (Per Game)</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C33" t="n">
-        <v>4.333</v>
+        <v>9.429</v>
       </c>
       <c r="D33" t="n">
-        <v>0.833</v>
+        <v>3.286</v>
       </c>
       <c r="E33" t="n">
-        <v>1.833</v>
+        <v>6.143</v>
       </c>
       <c r="F33" t="n">
-        <v>0.667</v>
+        <v>0.571</v>
       </c>
       <c r="G33" t="n">
-        <v>2.833</v>
+        <v>1.571</v>
       </c>
       <c r="H33" t="n">
-        <v>0.667</v>
+        <v>1.143</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>1.714</v>
       </c>
       <c r="J33" t="n">
-        <v>0.667</v>
+        <v>2.857</v>
       </c>
       <c r="K33" t="n">
-        <v>1.833</v>
+        <v>3.857</v>
       </c>
       <c r="L33" t="n">
-        <v>0.833</v>
+        <v>1.857</v>
       </c>
       <c r="M33" t="n">
-        <v>0.167</v>
+        <v>0.857</v>
       </c>
       <c r="N33" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.5</v>
+        <v>1.429</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.5</v>
+        <v>1.429</v>
       </c>
       <c r="R33" t="n">
-        <v>0.833</v>
+        <v>2.143</v>
       </c>
       <c r="S33" t="n">
-        <v>1</v>
+        <v>1.429</v>
       </c>
       <c r="T33" t="n">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="U33" t="n">
-        <v>0.167</v>
+        <v>1.571</v>
       </c>
       <c r="V33" t="n">
-        <v>0.833</v>
+        <v>1</v>
       </c>
       <c r="W33" t="n">
+        <v>1.143</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>2.714</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.571</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="AG33" t="n">
         <v>0.5</v>
       </c>
-      <c r="X33" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="Y33" t="n">
+      <c r="AH33" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="AJ33" t="n">
         <v>0.5</v>
       </c>
-      <c r="Z33" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>0.1</v>
-      </c>
       <c r="AK33" t="n">
-        <v>0.5</v>
+        <v>0.286</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.167</v>
+        <v>1</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.429</v>
+        <v>0.286</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>22:04</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>6.607</v>
+        <v>9.897</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.393</v>
+        <v>0.537</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.424</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="AR33" t="n">
-        <v>0.656</v>
+        <v>0.953</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.227</v>
+        <v>0.144</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.143</v>
+        <v>0.148</v>
       </c>
       <c r="AU33" t="n">
-        <v>0.444</v>
+        <v>2</v>
       </c>
       <c r="AV33" t="n">
-        <v>0.166</v>
+        <v>0.201</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.049</v>
+        <v>0.09</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.111</v>
+        <v>0.182</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.02</v>
+        <v>0.092</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>#12 N. SAKO (Per Game)</t>
+          <t>#8 J. MONTERO (Per Game)</t>
         </is>
       </c>
       <c r="B34" t="n">
+        <v>7</v>
+      </c>
+      <c r="C34" t="n">
+        <v>18.714</v>
+      </c>
+      <c r="D34" t="n">
+        <v>4</v>
+      </c>
+      <c r="E34" t="n">
+        <v>6.571</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.143</v>
+      </c>
+      <c r="G34" t="n">
+        <v>5.714</v>
+      </c>
+      <c r="H34" t="n">
+        <v>4.286</v>
+      </c>
+      <c r="I34" t="n">
+        <v>4.571</v>
+      </c>
+      <c r="J34" t="n">
         <v>6</v>
       </c>
-      <c r="C34" t="n">
-        <v>6.833</v>
-      </c>
-      <c r="D34" t="n">
-        <v>3</v>
-      </c>
-      <c r="E34" t="n">
-        <v>4.167</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="I34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J34" t="n">
+      <c r="K34" t="n">
+        <v>2.714</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.143</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.857</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1.857</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.286</v>
+      </c>
+      <c r="S34" t="n">
+        <v>4.857</v>
+      </c>
+      <c r="T34" t="n">
+        <v>179</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3.143</v>
+      </c>
+      <c r="V34" t="n">
+        <v>2.143</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.857</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.286</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>2.286</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>3.286</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0.696</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD34" t="n">
         <v>0.5</v>
       </c>
-      <c r="K34" t="n">
-        <v>2.833</v>
-      </c>
-      <c r="L34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="N34" t="n">
+      <c r="AE34" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.286</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="AJ34" t="n">
         <v>0.667</v>
       </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2.167</v>
-      </c>
-      <c r="T34" t="n">
-        <v>66</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>2.667</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>3.333</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>0</v>
-      </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1.857</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>5.286</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>0.351</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>28:02</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>5.6</v>
+        <v>16.154</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.72</v>
+        <v>0.587</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.649</v>
+        <v>0.654</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.22</v>
+        <v>1.158</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.06</v>
+        <v>0.115</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.2</v>
+        <v>0.349</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.5</v>
+        <v>3.231</v>
       </c>
       <c r="AV34" t="n">
-        <v>0.139</v>
+        <v>0.258</v>
       </c>
       <c r="AW34" t="n">
-        <v>0.145</v>
+        <v>0.033</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.17</v>
+        <v>0.101</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.016</v>
+        <v>0.208</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>#13 D. THOMPSON (Per Game)</t>
+          <t>#10 O. MOORE (Per Game)</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>5.286</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>0.857</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>1.714</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>0.571</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>0.857</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>0.714</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>1.571</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>0.857</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>0.429</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.429</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>1.429</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>0.857</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>0.714</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>0.429</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>0.571</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>0.857</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>0.429</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>0.429</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>1.571</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>0.091</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>0.857</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>1.429</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>0</v>
+        <v>6.52</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>0.519</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>0.219</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>0.121</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>0.052</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>0.094</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>#23 A. CÁRDENAS (Per Game)</t>
+          <t>#12 N. SAKO (Per Game)</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C36" t="n">
-        <v>5.5</v>
+        <v>6.429</v>
       </c>
       <c r="D36" t="n">
-        <v>0.833</v>
+        <v>2.857</v>
       </c>
       <c r="E36" t="n">
-        <v>2.333</v>
+        <v>3.857</v>
       </c>
       <c r="F36" t="n">
-        <v>1.167</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>2.333</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.333</v>
+        <v>0.714</v>
       </c>
       <c r="I36" t="n">
-        <v>0.333</v>
+        <v>2.286</v>
       </c>
       <c r="J36" t="n">
-        <v>1.5</v>
+        <v>0.571</v>
       </c>
       <c r="K36" t="n">
+        <v>2.714</v>
+      </c>
+      <c r="L36" t="n">
+        <v>2.429</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.571</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.429</v>
+      </c>
+      <c r="T36" t="n">
+        <v>77</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.286</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>2.429</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="AD36" t="n">
         <v>0.5</v>
       </c>
-      <c r="L36" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="R36" t="n">
-        <v>3</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="T36" t="n">
-        <v>19</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="X36" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.167</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>0.571</v>
-      </c>
       <c r="AE36" t="n">
         <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.833</v>
+        <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>5.48</v>
+        <v>5.291</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.554</v>
+        <v>0.741</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.571</v>
+        <v>0.661</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.004</v>
+        <v>1.215</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.122</v>
+        <v>0.081</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.185</v>
       </c>
       <c r="AU36" t="n">
-        <v>2.25</v>
+        <v>1.333</v>
       </c>
       <c r="AV36" t="n">
-        <v>0.172</v>
+        <v>0.134</v>
       </c>
       <c r="AW36" t="n">
-        <v>0.037</v>
+        <v>0.147</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.038</v>
+        <v>0.16</v>
       </c>
       <c r="AY36" t="n">
-        <v>0.046</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>#24 M. COSTELLO (Per Game)</t>
+          <t>#13 D. THOMPSON (Per Game)</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C37" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -5970,442 +5970,442 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.625</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AM37" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>8.16</v>
+        <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.521</v>
+        <v>0</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.011</v>
+        <v>0</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.031</v>
+        <v>0</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.138</v>
+        <v>0</v>
       </c>
       <c r="AU37" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.178</v>
+        <v>0</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.077</v>
+        <v>0</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.172</v>
+        <v>0</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.047</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>#32 I. NOGUÉS (Per Game)</t>
+          <t>#23 A. CÁRDENAS (Per Game)</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>0.857</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>2.286</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>0.286</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>0.286</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1.714</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>0.714</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>0.571</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>0.286</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>0.286</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>0.714</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>0.714</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>0.714</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>0.429</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>0.714</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>0.714</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>0.429</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>0.286</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>0.286</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>0.571</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>0.571</v>
       </c>
       <c r="AE38" t="n">
         <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>0.286</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>0.571</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>0.714</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>0.429</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>1.286</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AO38" t="n">
-        <v>0</v>
+        <v>5.126</v>
       </c>
       <c r="AP38" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="AR38" t="n">
-        <v>0</v>
+        <v>0.975</v>
       </c>
       <c r="AS38" t="n">
-        <v>0</v>
+        <v>0.139</v>
       </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>0.067</v>
       </c>
       <c r="AU38" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AV38" t="n">
-        <v>0</v>
+        <v>0.162</v>
       </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>0.043</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>0.053</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>0.052</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>#77 Y. SIMA (Per Game)</t>
+          <t>#24 M. COSTELLO (Per Game)</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>5</v>
       </c>
       <c r="C39" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E39" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G39" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K39" t="n">
+        <v>3</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T39" t="n">
+        <v>48</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z39" t="n">
         <v>2</v>
       </c>
-      <c r="D39" t="n">
+      <c r="AA39" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AK39" t="n">
         <v>0.8</v>
       </c>
-      <c r="E39" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="T39" t="n">
-        <v>10</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>0</v>
-      </c>
       <c r="AL39" t="n">
-        <v>0.2</v>
+        <v>3.2</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>06:48</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>1.976</v>
+        <v>7.616</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.444</v>
+        <v>0.545</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.506</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.012</v>
+        <v>1.077</v>
       </c>
       <c r="AS39" t="n">
-        <v>0</v>
+        <v>0.053</v>
       </c>
       <c r="AT39" t="n">
-        <v>0.222</v>
+        <v>0.152</v>
       </c>
       <c r="AU39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV39" t="n">
-        <v>0.129</v>
+        <v>0.183</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.092</v>
+        <v>0.081</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.095</v>
+        <v>0.168</v>
       </c>
       <c r="AY39" t="n">
-        <v>0</v>
+        <v>0.038</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>#32 I. NOGUÉS (Per Game)</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
@@ -6432,10 +6432,10 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>2.667</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -6447,7 +6447,7 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6560,157 +6560,157 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>TOTAL (Per Game)</t>
+          <t>#77 Y. SIMA (Per Game)</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>6</v>
       </c>
       <c r="C41" t="n">
-        <v>96.333</v>
+        <v>3.167</v>
       </c>
       <c r="D41" t="n">
-        <v>23.833</v>
+        <v>1.167</v>
       </c>
       <c r="E41" t="n">
-        <v>40.667</v>
+        <v>2</v>
       </c>
       <c r="F41" t="n">
-        <v>11</v>
+        <v>0.167</v>
       </c>
       <c r="G41" t="n">
-        <v>34</v>
+        <v>0.5</v>
       </c>
       <c r="H41" t="n">
-        <v>15.667</v>
+        <v>0.333</v>
       </c>
       <c r="I41" t="n">
-        <v>20.667</v>
+        <v>0.333</v>
       </c>
       <c r="J41" t="n">
-        <v>20.5</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>27.667</v>
+        <v>0.833</v>
       </c>
       <c r="L41" t="n">
-        <v>14.167</v>
+        <v>0.833</v>
       </c>
       <c r="M41" t="n">
-        <v>8.667</v>
+        <v>0.167</v>
       </c>
       <c r="N41" t="n">
-        <v>6.5</v>
+        <v>0.667</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>10.167</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>19.333</v>
+        <v>1.333</v>
       </c>
       <c r="S41" t="n">
-        <v>21.5</v>
+        <v>0.167</v>
       </c>
       <c r="T41" t="n">
-        <v>726</v>
+        <v>20</v>
       </c>
       <c r="U41" t="n">
-        <v>13.667</v>
+        <v>0.667</v>
       </c>
       <c r="V41" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="W41" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>16.167</v>
+        <v>1</v>
       </c>
       <c r="Z41" t="n">
-        <v>22.833</v>
+        <v>1.5</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.708</v>
+        <v>0.667</v>
       </c>
       <c r="AB41" t="n">
-        <v>4</v>
+        <v>0.167</v>
       </c>
       <c r="AC41" t="n">
-        <v>9.5</v>
+        <v>0.5</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.421</v>
+        <v>0.333</v>
       </c>
       <c r="AE41" t="n">
-        <v>3.667</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>8.333</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>3.167</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
-        <v>9.333</v>
+        <v>0</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.339</v>
+        <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>7.833</v>
+        <v>0.167</v>
       </c>
       <c r="AL41" t="n">
-        <v>24.667</v>
+        <v>0.5</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.318</v>
+        <v>0.333</v>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>208:20</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="AO41" t="n">
-        <v>93.92700000000001</v>
+        <v>2.647</v>
       </c>
       <c r="AP41" t="n">
-        <v>0.54</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.575</v>
+        <v>0.598</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.026</v>
+        <v>1.196</v>
       </c>
       <c r="AS41" t="n">
-        <v>0.108</v>
+        <v>0</v>
       </c>
       <c r="AT41" t="n">
-        <v>0.21</v>
+        <v>0.133</v>
       </c>
       <c r="AU41" t="n">
-        <v>2.016</v>
+        <v>0</v>
       </c>
       <c r="AV41" t="n">
-        <v>0.2</v>
+        <v>0.154</v>
       </c>
       <c r="AW41" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.116</v>
       </c>
       <c r="AX41" t="n">
-        <v>0.142</v>
+        <v>0.113</v>
       </c>
       <c r="AY41" t="n">
         <v>0</v>
@@ -6719,159 +6719,477 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
+          <t>Equip (Per Game)</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>7</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.714</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1.714</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN42" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AO42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL (Per Game)</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>7</v>
+      </c>
+      <c r="C43" t="n">
+        <v>97.143</v>
+      </c>
+      <c r="D43" t="n">
+        <v>24</v>
+      </c>
+      <c r="E43" t="n">
+        <v>41</v>
+      </c>
+      <c r="F43" t="n">
+        <v>11</v>
+      </c>
+      <c r="G43" t="n">
+        <v>32.143</v>
+      </c>
+      <c r="H43" t="n">
+        <v>16.143</v>
+      </c>
+      <c r="I43" t="n">
+        <v>20.857</v>
+      </c>
+      <c r="J43" t="n">
+        <v>20.429</v>
+      </c>
+      <c r="K43" t="n">
+        <v>28.143</v>
+      </c>
+      <c r="L43" t="n">
+        <v>13.714</v>
+      </c>
+      <c r="M43" t="n">
+        <v>7.857</v>
+      </c>
+      <c r="N43" t="n">
+        <v>6.571</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>10.286</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>10.143</v>
+      </c>
+      <c r="R43" t="n">
+        <v>19.286</v>
+      </c>
+      <c r="S43" t="n">
+        <v>21</v>
+      </c>
+      <c r="T43" t="n">
+        <v>857</v>
+      </c>
+      <c r="U43" t="n">
+        <v>13.143</v>
+      </c>
+      <c r="V43" t="n">
+        <v>13.429</v>
+      </c>
+      <c r="W43" t="n">
+        <v>8.429</v>
+      </c>
+      <c r="X43" t="n">
+        <v>5.143</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>16.143</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>22.714</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0.711</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>9.714</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>3.857</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>8.571</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>3.429</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>9.286</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>7.571</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>22.857</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="AN43" t="inlineStr">
+        <is>
+          <t>207:08</t>
+        </is>
+      </c>
+      <c r="AO43" t="n">
+        <v>92.60599999999999</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>0.554</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>1.049</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>0.221</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>1.986</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
           <t>Rival (Per Game)</t>
         </is>
       </c>
-      <c r="B42" t="n">
-        <v>6</v>
-      </c>
-      <c r="C42" t="n">
-        <v>88.667</v>
-      </c>
-      <c r="D42" t="n">
-        <v>19.167</v>
-      </c>
-      <c r="E42" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="F42" t="n">
-        <v>12.333</v>
-      </c>
-      <c r="G42" t="n">
-        <v>33.667</v>
-      </c>
-      <c r="H42" t="n">
-        <v>13.333</v>
-      </c>
-      <c r="I42" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="J42" t="n">
-        <v>18.333</v>
-      </c>
-      <c r="K42" t="n">
-        <v>25.833</v>
-      </c>
-      <c r="L42" t="n">
-        <v>11.167</v>
-      </c>
-      <c r="M42" t="n">
+      <c r="B44" t="n">
         <v>7</v>
       </c>
-      <c r="N42" t="n">
-        <v>6.333</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>13.833</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>12.667</v>
-      </c>
-      <c r="R42" t="n">
-        <v>21.667</v>
-      </c>
-      <c r="S42" t="n">
-        <v>19.167</v>
-      </c>
-      <c r="T42" t="n">
-        <v>589</v>
-      </c>
-      <c r="U42" t="n">
-        <v>8.333</v>
-      </c>
-      <c r="V42" t="n">
-        <v>11.833</v>
-      </c>
-      <c r="W42" t="n">
-        <v>4.167</v>
-      </c>
-      <c r="X42" t="n">
-        <v>2.833</v>
-      </c>
-      <c r="Y42" t="n">
+      <c r="C44" t="n">
+        <v>86.714</v>
+      </c>
+      <c r="D44" t="n">
+        <v>20.143</v>
+      </c>
+      <c r="E44" t="n">
+        <v>38.857</v>
+      </c>
+      <c r="F44" t="n">
+        <v>11.143</v>
+      </c>
+      <c r="G44" t="n">
+        <v>31.857</v>
+      </c>
+      <c r="H44" t="n">
         <v>13</v>
       </c>
-      <c r="Z42" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>0.6840000000000001</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>0.361</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>1.833</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>3.667</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>8.667</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>0.423</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>8.667</v>
-      </c>
-      <c r="AL42" t="n">
+      <c r="I44" t="n">
+        <v>17.429</v>
+      </c>
+      <c r="J44" t="n">
+        <v>17.857</v>
+      </c>
+      <c r="K44" t="n">
         <v>25</v>
       </c>
-      <c r="AM42" t="n">
-        <v>0.347</v>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>208:20</t>
-        </is>
-      </c>
-      <c r="AO42" t="n">
-        <v>91.7</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>0.537</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>0.569</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>0.967</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>0.151</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>1.325</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>0.195</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="AY42" t="n">
+      <c r="L44" t="n">
+        <v>11.571</v>
+      </c>
+      <c r="M44" t="n">
+        <v>6.857</v>
+      </c>
+      <c r="N44" t="n">
+        <v>6.429</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>11.429</v>
+      </c>
+      <c r="R44" t="n">
+        <v>21</v>
+      </c>
+      <c r="S44" t="n">
+        <v>19.143</v>
+      </c>
+      <c r="T44" t="n">
+        <v>670</v>
+      </c>
+      <c r="U44" t="n">
+        <v>8.856999999999999</v>
+      </c>
+      <c r="V44" t="n">
+        <v>11.857</v>
+      </c>
+      <c r="W44" t="n">
+        <v>4.714</v>
+      </c>
+      <c r="X44" t="n">
+        <v>3.143</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>20.714</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>4.429</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>12.714</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>1.714</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>5.429</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>3.286</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>7.857</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>7.857</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>24</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="AN44" t="inlineStr">
+        <is>
+          <t>207:08</t>
+        </is>
+      </c>
+      <c r="AO44" t="n">
+        <v>91.383</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>0.521</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>0.553</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>0.949</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>1.374</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="AY44" t="n">
         <v>0</v>
       </c>
     </row>

--- a/informes_data/ACB/2025-26/playoffs/aggregate/AGGREGATE_Valencia Basket.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate/AGGREGATE_Valencia Basket.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,212 +417,212 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Team</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>POSSind</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>POSSest</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>OER</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>DER</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>eFG%</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>TOV%</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>ORB%</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>FTR</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>TOpts</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>2CPts</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>FastBPts</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>TOunf</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Rim FGM</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Rim FGA</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Rim_vol</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Paint FGM</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Paint FGA</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Paint_vol</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>MR FGM</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>MR FGA</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>MR_vol</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Cor3 FGM</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Cor3 FGA</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Cor3_vol</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>ATB3 FGM</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>ATB3 FGA</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>ATB3_vol</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Rim %</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Paint %</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>MR %</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Cor3 %</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>ATB3 %</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Rim PPS</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>MR PPS</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>3P PPS</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>TOptsPPO</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>2CPtsPPO</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>FastBPtsPPO</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Ass/TO</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Sh/TO</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Gen/TO</t>
         </is>
@@ -647,127 +635,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>552.24</v>
+        <v>704.52</v>
       </c>
       <c r="C2" t="n">
-        <v>555.46</v>
+        <v>709.2400000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>122.4210564217045</v>
+        <v>123.5124922452202</v>
       </c>
       <c r="E2" t="n">
-        <v>109.2787959529039</v>
+        <v>108.7079126952794</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5537109375</v>
+        <v>0.5587786259541985</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1110699740836727</v>
+        <v>0.1111755607115236</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3542435424354243</v>
+        <v>0.358600583090379</v>
       </c>
       <c r="I2" t="n">
-        <v>0.220703125</v>
+        <v>0.2198473282442748</v>
       </c>
       <c r="J2" t="n">
+        <v>112</v>
+      </c>
+      <c r="K2" t="n">
+        <v>116</v>
+      </c>
+      <c r="L2" t="n">
+        <v>71</v>
+      </c>
+      <c r="M2" t="n">
+        <v>90</v>
+      </c>
+      <c r="N2" t="n">
+        <v>142</v>
+      </c>
+      <c r="O2" t="n">
+        <v>203</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.3099236641221374</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>41</v>
+      </c>
+      <c r="R2" t="n">
         <v>92</v>
       </c>
-      <c r="K2" t="n">
-        <v>94</v>
-      </c>
-      <c r="L2" t="n">
-        <v>59</v>
-      </c>
-      <c r="M2" t="n">
-        <v>71</v>
-      </c>
-      <c r="N2" t="n">
-        <v>113</v>
-      </c>
-      <c r="O2" t="n">
-        <v>159</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.310546875</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>28</v>
-      </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
+        <v>0.1404580152671756</v>
+      </c>
+      <c r="T2" t="n">
+        <v>33</v>
+      </c>
+      <c r="U2" t="n">
+        <v>78</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.1190839694656489</v>
+      </c>
+      <c r="W2" t="n">
+        <v>32</v>
+      </c>
+      <c r="X2" t="n">
+        <v>82</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.1251908396946565</v>
+      </c>
+      <c r="Z2" t="n">
         <v>68</v>
       </c>
-      <c r="S2" t="n">
-        <v>0.1328125</v>
-      </c>
-      <c r="T2" t="n">
-        <v>27</v>
-      </c>
-      <c r="U2" t="n">
-        <v>60</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.1171875</v>
-      </c>
-      <c r="W2" t="n">
-        <v>24</v>
-      </c>
-      <c r="X2" t="n">
-        <v>65</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.126953125</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>53</v>
-      </c>
       <c r="AA2" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3125</v>
+        <v>0.3053435114503817</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.710691823899371</v>
+        <v>0.6995073891625616</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.4117647058823529</v>
+        <v>0.4456521739130435</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.45</v>
+        <v>0.4230769230769231</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.3692307692307693</v>
+        <v>0.3902439024390244</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.33125</v>
+        <v>0.34</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.421383647798742</v>
+        <v>1.399014778325123</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.9</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.026666666666667</v>
+        <v>1.063829787234043</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.010989010989011</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.9791666666666666</v>
+        <v>0.943089430894309</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.638888888888889</v>
+        <v>1.651162790697674</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.986111111111111</v>
+        <v>1.923913043478261</v>
       </c>
       <c r="AO2" t="n">
-        <v>7.111111111111111</v>
+        <v>7.119565217391305</v>
       </c>
       <c r="AP2" t="n">
-        <v>9.097222222222221</v>
+        <v>9.043478260869565</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +765,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>78.89142857142858</v>
+        <v>78.28</v>
       </c>
       <c r="C3" t="n">
-        <v>79.35142857142857</v>
+        <v>78.80444444444446</v>
       </c>
       <c r="D3" t="n">
-        <v>122.4210564217045</v>
+        <v>123.5124922452202</v>
       </c>
       <c r="E3" t="n">
-        <v>109.2787959529039</v>
+        <v>108.7079126952794</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5537109375</v>
+        <v>0.5587786259541985</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1110699740836727</v>
+        <v>0.1111755607115236</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3542435424354243</v>
+        <v>0.358600583090379</v>
       </c>
       <c r="I3" t="n">
-        <v>0.220703125</v>
+        <v>0.2198473282442748</v>
       </c>
       <c r="J3" t="n">
-        <v>13.14285714285714</v>
+        <v>12.44444444444444</v>
       </c>
       <c r="K3" t="n">
-        <v>13.42857142857143</v>
+        <v>12.88888888888889</v>
       </c>
       <c r="L3" t="n">
-        <v>8.428571428571429</v>
+        <v>7.888888888888889</v>
       </c>
       <c r="M3" t="n">
-        <v>10.14285714285714</v>
+        <v>10</v>
       </c>
       <c r="N3" t="n">
-        <v>16.14285714285714</v>
+        <v>15.77777777777778</v>
       </c>
       <c r="O3" t="n">
-        <v>22.71428571428572</v>
+        <v>22.55555555555556</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3105468750000001</v>
+        <v>0.3099236641221375</v>
       </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>4.555555555555555</v>
       </c>
       <c r="R3" t="n">
-        <v>9.714285714285714</v>
+        <v>10.22222222222222</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1328125</v>
+        <v>0.1404580152671756</v>
       </c>
       <c r="T3" t="n">
-        <v>3.857142857142857</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="U3" t="n">
-        <v>8.571428571428571</v>
+        <v>8.666666666666666</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1171875</v>
+        <v>0.1190839694656489</v>
       </c>
       <c r="W3" t="n">
-        <v>3.428571428571428</v>
+        <v>3.555555555555555</v>
       </c>
       <c r="X3" t="n">
-        <v>9.285714285714286</v>
+        <v>9.111111111111111</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.126953125</v>
+        <v>0.1251908396946565</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.571428571428571</v>
+        <v>7.555555555555555</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.85714285714286</v>
+        <v>22.22222222222222</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3125</v>
+        <v>0.3053435114503817</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.710691823899371</v>
+        <v>0.6995073891625616</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.411764705882353</v>
+        <v>0.4456521739130435</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.45</v>
+        <v>0.4230769230769231</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.3692307692307692</v>
+        <v>0.3902439024390244</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.33125</v>
+        <v>0.34</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.421383647798742</v>
+        <v>1.399014778325123</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.9</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.026666666666667</v>
+        <v>1.063829787234043</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.010989010989011</v>
+        <v>0.9411764705882354</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.9791666666666667</v>
+        <v>0.943089430894309</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.638888888888889</v>
+        <v>1.651162790697674</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.986111111111111</v>
+        <v>1.923913043478261</v>
       </c>
       <c r="AO3" t="n">
-        <v>7.11111111111111</v>
+        <v>7.119565217391305</v>
       </c>
       <c r="AP3" t="n">
-        <v>9.097222222222221</v>
+        <v>9.043478260869566</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +895,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>558.6800000000001</v>
+        <v>713.96</v>
       </c>
       <c r="C4" t="n">
-        <v>555.46</v>
+        <v>709.2400000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>109.2787959529039</v>
+        <v>108.7079126952794</v>
       </c>
       <c r="E4" t="n">
-        <v>122.4210564217045</v>
+        <v>123.5124922452202</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5212121212121212</v>
+        <v>0.5265273311897106</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1422586293146574</v>
+        <v>0.1467396665680182</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2913669064748202</v>
+        <v>0.2779369627507163</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1838383838383838</v>
+        <v>0.1864951768488746</v>
       </c>
       <c r="J4" t="n">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="K4" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="L4" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="M4" t="n">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="N4" t="n">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="O4" t="n">
-        <v>145</v>
+        <v>181</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2929292929292929</v>
+        <v>0.2909967845659164</v>
       </c>
       <c r="Q4" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="R4" t="n">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1797979797979798</v>
+        <v>0.1672025723472669</v>
       </c>
       <c r="T4" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="U4" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="V4" t="n">
-        <v>0.07676767676767676</v>
+        <v>0.08360128617363344</v>
       </c>
       <c r="W4" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="X4" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1109324758842444</v>
       </c>
       <c r="Z4" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AA4" t="n">
-        <v>168</v>
+        <v>216</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3393939393939394</v>
+        <v>0.3472668810289389</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.6758620689655173</v>
+        <v>0.6685082872928176</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.3483146067415731</v>
+        <v>0.3846153846153846</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.3157894736842105</v>
+        <v>0.3461538461538461</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.4181818181818182</v>
+        <v>0.4202898550724637</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3273809523809524</v>
+        <v>0.3240740740740741</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.351724137931035</v>
+        <v>1.337016574585635</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.631578947368421</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.04932735426009</v>
+        <v>1.042105263157895</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.8611111111111112</v>
+        <v>0.8369565217391305</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.024691358024691</v>
+        <v>0.9484536082474226</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.373626373626374</v>
+        <v>1.26890756302521</v>
       </c>
       <c r="AO4" t="n">
-        <v>5.43956043956044</v>
+        <v>5.226890756302521</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.813186813186813</v>
+        <v>6.495798319327731</v>
       </c>
     </row>
     <row r="5">
@@ -1037,422 +1025,422 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>79.81142857142858</v>
+        <v>79.3288888888889</v>
       </c>
       <c r="C5" t="n">
-        <v>79.35142857142857</v>
+        <v>78.80444444444446</v>
       </c>
       <c r="D5" t="n">
-        <v>109.2787959529039</v>
+        <v>108.7079126952794</v>
       </c>
       <c r="E5" t="n">
-        <v>122.4210564217045</v>
+        <v>123.5124922452202</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5212121212121213</v>
+        <v>0.5265273311897105</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1422586293146574</v>
+        <v>0.1467396665680181</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2913669064748201</v>
+        <v>0.2779369627507163</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1838383838383839</v>
+        <v>0.1864951768488746</v>
       </c>
       <c r="J5" t="n">
-        <v>8.857142857142858</v>
+        <v>8.555555555555555</v>
       </c>
       <c r="K5" t="n">
-        <v>11.85714285714286</v>
+        <v>10.22222222222222</v>
       </c>
       <c r="L5" t="n">
-        <v>4.714285714285714</v>
+        <v>4.555555555555555</v>
       </c>
       <c r="M5" t="n">
-        <v>11.42857142857143</v>
+        <v>11.77777777777778</v>
       </c>
       <c r="N5" t="n">
-        <v>14</v>
+        <v>13.44444444444444</v>
       </c>
       <c r="O5" t="n">
-        <v>20.71428571428572</v>
+        <v>20.11111111111111</v>
       </c>
       <c r="P5" t="n">
-        <v>0.292929292929293</v>
+        <v>0.2909967845659164</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.428571428571429</v>
+        <v>4.444444444444445</v>
       </c>
       <c r="R5" t="n">
-        <v>12.71428571428571</v>
+        <v>11.55555555555556</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1797979797979798</v>
+        <v>0.1672025723472669</v>
       </c>
       <c r="T5" t="n">
-        <v>1.714285714285714</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>5.428571428571429</v>
+        <v>5.777777777777778</v>
       </c>
       <c r="V5" t="n">
-        <v>0.07676767676767678</v>
+        <v>0.08360128617363344</v>
       </c>
       <c r="W5" t="n">
-        <v>3.285714285714286</v>
+        <v>3.222222222222222</v>
       </c>
       <c r="X5" t="n">
-        <v>7.857142857142857</v>
+        <v>7.666666666666667</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1109324758842444</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.857142857142857</v>
+        <v>7.777777777777778</v>
       </c>
       <c r="AA5" t="n">
         <v>24</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3393939393939394</v>
+        <v>0.3472668810289389</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.6758620689655173</v>
+        <v>0.6685082872928177</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.3483146067415731</v>
+        <v>0.3846153846153846</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.3157894736842105</v>
+        <v>0.3461538461538461</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.4181818181818182</v>
+        <v>0.4202898550724637</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3273809523809524</v>
+        <v>0.3240740740740741</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.351724137931035</v>
+        <v>1.337016574585635</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.631578947368421</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.04932735426009</v>
+        <v>1.042105263157895</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.861111111111111</v>
+        <v>0.8369565217391305</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.024691358024691</v>
+        <v>0.9484536082474225</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.373626373626374</v>
+        <v>1.26890756302521</v>
       </c>
       <c r="AO5" t="n">
-        <v>5.439560439560439</v>
+        <v>5.226890756302522</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.813186813186813</v>
+        <v>6.495798319327731</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="1" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Games</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>PTS</t>
         </is>
       </c>
-      <c r="D7" s="1" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>2PM</t>
         </is>
       </c>
-      <c r="E7" s="1" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>2PA</t>
         </is>
       </c>
-      <c r="F7" s="1" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>3PM</t>
         </is>
       </c>
-      <c r="G7" s="1" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>3PA</t>
         </is>
       </c>
-      <c r="H7" s="1" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>FTM</t>
         </is>
       </c>
-      <c r="I7" s="1" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>FTA</t>
         </is>
       </c>
-      <c r="J7" s="1" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>AS</t>
         </is>
       </c>
-      <c r="K7" s="1" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>DRB</t>
         </is>
       </c>
-      <c r="L7" s="1" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>ORB</t>
         </is>
       </c>
-      <c r="M7" s="1" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>STL</t>
         </is>
       </c>
-      <c r="N7" s="1" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>BLK</t>
         </is>
       </c>
-      <c r="O7" s="1" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>BLK A.</t>
         </is>
       </c>
-      <c r="P7" s="1" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>TO</t>
         </is>
       </c>
-      <c r="Q7" s="1" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>TOunf</t>
         </is>
       </c>
-      <c r="R7" s="1" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="S7" s="1" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>F+</t>
         </is>
       </c>
-      <c r="T7" s="1" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>EFI</t>
         </is>
       </c>
-      <c r="U7" s="1" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>TOpts</t>
         </is>
       </c>
-      <c r="V7" s="1" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>2CPts</t>
         </is>
       </c>
-      <c r="W7" s="1" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>FastBPts</t>
         </is>
       </c>
-      <c r="X7" s="1" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>FastB Opp</t>
         </is>
       </c>
-      <c r="Y7" s="1" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Rim FGM</t>
         </is>
       </c>
-      <c r="Z7" s="1" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>Rim FGA</t>
         </is>
       </c>
-      <c r="AA7" s="1" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Rim %</t>
         </is>
       </c>
-      <c r="AB7" s="1" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>Paint FGM</t>
         </is>
       </c>
-      <c r="AC7" s="1" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>Paint FGA</t>
         </is>
       </c>
-      <c r="AD7" s="1" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>Paint %</t>
         </is>
       </c>
-      <c r="AE7" s="1" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>MR FGM</t>
         </is>
       </c>
-      <c r="AF7" s="1" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>MR FGA</t>
         </is>
       </c>
-      <c r="AG7" s="1" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>MR %</t>
         </is>
       </c>
-      <c r="AH7" s="1" t="inlineStr">
+      <c r="AH7" t="inlineStr">
         <is>
           <t>Cor3 FGM</t>
         </is>
       </c>
-      <c r="AI7" s="1" t="inlineStr">
+      <c r="AI7" t="inlineStr">
         <is>
           <t>Cor3 FGA</t>
         </is>
       </c>
-      <c r="AJ7" s="1" t="inlineStr">
+      <c r="AJ7" t="inlineStr">
         <is>
           <t>Cor3 %</t>
         </is>
       </c>
-      <c r="AK7" s="1" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>ATB3 FGM</t>
         </is>
       </c>
-      <c r="AL7" s="1" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>ATB3 FGA</t>
         </is>
       </c>
-      <c r="AM7" s="1" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>ATB3 %</t>
         </is>
       </c>
-      <c r="AN7" s="1" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>TIME</t>
         </is>
       </c>
-      <c r="AO7" s="1" t="inlineStr">
+      <c r="AO7" t="inlineStr">
         <is>
           <t>PLAYS</t>
         </is>
       </c>
-      <c r="AP7" s="1" t="inlineStr">
+      <c r="AP7" t="inlineStr">
         <is>
           <t>eFG%</t>
         </is>
       </c>
-      <c r="AQ7" s="1" t="inlineStr">
+      <c r="AQ7" t="inlineStr">
         <is>
           <t>TS%</t>
         </is>
       </c>
-      <c r="AR7" s="1" t="inlineStr">
+      <c r="AR7" t="inlineStr">
         <is>
           <t>PTS/PLAY</t>
         </is>
       </c>
-      <c r="AS7" s="1" t="inlineStr">
+      <c r="AS7" t="inlineStr">
         <is>
           <t>TO%</t>
         </is>
       </c>
-      <c r="AT7" s="1" t="inlineStr">
+      <c r="AT7" t="inlineStr">
         <is>
           <t>FTR</t>
         </is>
       </c>
-      <c r="AU7" s="1" t="inlineStr">
+      <c r="AU7" t="inlineStr">
         <is>
           <t>Ass/TO</t>
         </is>
       </c>
-      <c r="AV7" s="1" t="inlineStr">
+      <c r="AV7" t="inlineStr">
         <is>
           <t>USG%</t>
         </is>
       </c>
-      <c r="AW7" s="1" t="inlineStr">
+      <c r="AW7" t="inlineStr">
         <is>
           <t>OR%</t>
         </is>
       </c>
-      <c r="AX7" s="1" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>DR%</t>
         </is>
       </c>
-      <c r="AY7" s="1" t="inlineStr">
+      <c r="AY7" t="inlineStr">
         <is>
           <t>pAST%</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>#0 B. BADIO</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C8" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="D8" t="n">
+        <v>19</v>
+      </c>
+      <c r="E8" t="n">
+        <v>35</v>
+      </c>
+      <c r="F8" t="n">
+        <v>13</v>
+      </c>
+      <c r="G8" t="n">
+        <v>43</v>
+      </c>
+      <c r="H8" t="n">
+        <v>15</v>
+      </c>
+      <c r="I8" t="n">
         <v>18</v>
       </c>
-      <c r="E8" t="n">
-        <v>29</v>
-      </c>
-      <c r="F8" t="n">
-        <v>11</v>
-      </c>
-      <c r="G8" t="n">
-        <v>36</v>
-      </c>
-      <c r="H8" t="n">
-        <v>14</v>
-      </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
+        <v>22</v>
+      </c>
+      <c r="K8" t="n">
         <v>17</v>
-      </c>
-      <c r="J8" t="n">
-        <v>18</v>
-      </c>
-      <c r="K8" t="n">
-        <v>9</v>
       </c>
       <c r="L8" t="n">
         <v>3</v>
       </c>
       <c r="M8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N8" t="n">
         <v>3</v>
@@ -1461,19 +1449,19 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R8" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="S8" t="n">
         <v>14</v>
       </c>
       <c r="T8" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="U8" t="n">
         <v>12</v>
@@ -1491,154 +1479,154 @@
         <v>7</v>
       </c>
       <c r="Z8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.778</v>
+        <v>0.636</v>
       </c>
       <c r="AB8" t="n">
         <v>4</v>
       </c>
       <c r="AC8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH8" t="n">
         <v>7</v>
       </c>
-      <c r="AD8" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0.538</v>
-      </c>
-      <c r="AH8" t="n">
+      <c r="AI8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="AK8" t="n">
         <v>6</v>
       </c>
-      <c r="AI8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>5</v>
-      </c>
       <c r="AL8" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.208</v>
+        <v>0.214</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>179:43</t>
+          <t>226:51</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>75.48</v>
+        <v>91.92</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.531</v>
+        <v>0.494</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.573</v>
+        <v>0.535</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.1</v>
+        <v>1.001</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.04</v>
+        <v>0.065</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.215</v>
+        <v>0.192</v>
       </c>
       <c r="AU8" t="n">
-        <v>6</v>
+        <v>3.667</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.188</v>
+        <v>0.181</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.018</v>
+        <v>0.014</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.052</v>
+        <v>0.079</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.083</v>
+        <v>0.077</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>#1 K. TAYLOR</t>
         </is>
       </c>
       <c r="B9" t="n">
+        <v>9</v>
+      </c>
+      <c r="C9" t="n">
+        <v>118</v>
+      </c>
+      <c r="D9" t="n">
+        <v>32</v>
+      </c>
+      <c r="E9" t="n">
+        <v>55</v>
+      </c>
+      <c r="F9" t="n">
+        <v>14</v>
+      </c>
+      <c r="G9" t="n">
+        <v>40</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="n">
+        <v>14</v>
+      </c>
+      <c r="J9" t="n">
+        <v>13</v>
+      </c>
+      <c r="K9" t="n">
+        <v>31</v>
+      </c>
+      <c r="L9" t="n">
         <v>7</v>
       </c>
-      <c r="C9" t="n">
-        <v>84</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="M9" t="n">
+        <v>15</v>
+      </c>
+      <c r="N9" t="n">
+        <v>5</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>8</v>
+      </c>
+      <c r="R9" t="n">
+        <v>16</v>
+      </c>
+      <c r="S9" t="n">
         <v>21</v>
       </c>
-      <c r="E9" t="n">
-        <v>34</v>
-      </c>
-      <c r="F9" t="n">
-        <v>11</v>
-      </c>
-      <c r="G9" t="n">
-        <v>34</v>
-      </c>
-      <c r="H9" t="n">
-        <v>9</v>
-      </c>
-      <c r="I9" t="n">
-        <v>11</v>
-      </c>
-      <c r="J9" t="n">
+      <c r="T9" t="n">
+        <v>135</v>
+      </c>
+      <c r="U9" t="n">
         <v>12</v>
       </c>
-      <c r="K9" t="n">
-        <v>24</v>
-      </c>
-      <c r="L9" t="n">
-        <v>5</v>
-      </c>
-      <c r="M9" t="n">
-        <v>11</v>
-      </c>
-      <c r="N9" t="n">
-        <v>4</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>7</v>
-      </c>
-      <c r="R9" t="n">
-        <v>11</v>
-      </c>
-      <c r="S9" t="n">
-        <v>14</v>
-      </c>
-      <c r="T9" t="n">
-        <v>98</v>
-      </c>
-      <c r="U9" t="n">
-        <v>7</v>
-      </c>
       <c r="V9" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="W9" t="n">
         <v>6</v>
@@ -1647,97 +1635,97 @@
         <v>4</v>
       </c>
       <c r="Y9" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.706</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI9" t="n">
         <v>9</v>
       </c>
-      <c r="Z9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0.529</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>7</v>
-      </c>
       <c r="AJ9" t="n">
-        <v>0.143</v>
+        <v>0.333</v>
       </c>
       <c r="AK9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL9" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.37</v>
+        <v>0.355</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>182:56</t>
+          <t>232:13</t>
         </is>
       </c>
       <c r="AO9" t="n">
-        <v>79.84</v>
+        <v>109.16</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.551</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.577</v>
+        <v>0.583</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.052</v>
+        <v>1.081</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.073</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.132</v>
+        <v>0.126</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.714</v>
+        <v>1.625</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.195</v>
+        <v>0.21</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.029</v>
+        <v>0.033</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.137</v>
+        <v>0.142</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.056</v>
+        <v>0.048</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>#2 J. PUERTO</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
         <v>2</v>
@@ -1883,35 +1871,35 @@
         <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.26</v>
+        <v>0.264</v>
       </c>
       <c r="AY10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>#3 N. REUVERS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F11" t="n">
         <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H11" t="n">
         <v>6</v>
@@ -1923,17 +1911,17 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M11" t="n">
+        <v>3</v>
+      </c>
+      <c r="N11" t="n">
         <v>2</v>
       </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
@@ -1944,19 +1932,19 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="S11" t="n">
         <v>6</v>
       </c>
       <c r="T11" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="U11" t="n">
         <v>2</v>
       </c>
       <c r="V11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W11" t="n">
         <v>1</v>
@@ -1965,19 +1953,19 @@
         <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z11" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA11" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
         <v>1</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -1995,7 +1983,7 @@
         <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
@@ -2004,88 +1992,88 @@
         <v>3</v>
       </c>
       <c r="AL11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM11" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>33:56</t>
+          <t>49:58</t>
         </is>
       </c>
       <c r="AO11" t="n">
-        <v>14.08</v>
+        <v>20.08</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.864</v>
+        <v>0.676</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.888</v>
+        <v>0.722</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.776</v>
+        <v>1.444</v>
       </c>
       <c r="AS11" t="n">
         <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.545</v>
+        <v>0.353</v>
       </c>
       <c r="AU11" t="n">
         <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.186</v>
+        <v>0.18</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.032</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.184</v>
+        <v>0.149</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>#4 J. PRADILLA</t>
         </is>
       </c>
       <c r="B12" t="n">
+        <v>9</v>
+      </c>
+      <c r="C12" t="n">
+        <v>85</v>
+      </c>
+      <c r="D12" t="n">
+        <v>23</v>
+      </c>
+      <c r="E12" t="n">
+        <v>39</v>
+      </c>
+      <c r="F12" t="n">
         <v>7</v>
       </c>
-      <c r="C12" t="n">
-        <v>70</v>
-      </c>
-      <c r="D12" t="n">
+      <c r="G12" t="n">
+        <v>21</v>
+      </c>
+      <c r="H12" t="n">
         <v>18</v>
       </c>
-      <c r="E12" t="n">
-        <v>30</v>
-      </c>
-      <c r="F12" t="n">
-        <v>6</v>
-      </c>
-      <c r="G12" t="n">
-        <v>18</v>
-      </c>
-      <c r="H12" t="n">
-        <v>16</v>
-      </c>
       <c r="I12" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K12" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="L12" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M12" t="n">
         <v>7</v>
@@ -2097,25 +2085,25 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Q12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="R12" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="S12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="T12" t="n">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="U12" t="n">
         <v>14</v>
       </c>
       <c r="V12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W12" t="n">
         <v>5</v>
@@ -2124,22 +2112,22 @@
         <v>2</v>
       </c>
       <c r="Y12" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="Z12" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.72</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -2154,97 +2142,97 @@
         <v>3</v>
       </c>
       <c r="AI12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.375</v>
+        <v>0.333</v>
       </c>
       <c r="AK12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AM12" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>190:06</t>
+        </is>
+      </c>
+      <c r="AO12" t="n">
+        <v>82.12</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0.5580000000000001</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0.606</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.035</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="AT12" t="n">
         <v>0.3</v>
       </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>150:18</t>
-        </is>
-      </c>
-      <c r="AO12" t="n">
-        <v>63.36</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0.5620000000000001</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0.621</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>1.105</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0.333</v>
-      </c>
       <c r="AU12" t="n">
-        <v>1.571</v>
+        <v>1.167</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.189</v>
+        <v>0.193</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.093</v>
+        <v>0.096</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.146</v>
+        <v>0.151</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.05</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>#5 S. DE LARREA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G13" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I13" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J13" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L13" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M13" t="n">
         <v>5</v>
@@ -2256,208 +2244,208 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q13" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="R13" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T13" t="n">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="U13" t="n">
         <v>5</v>
       </c>
       <c r="V13" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="W13" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y13" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Z13" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.571</v>
+        <v>0.727</v>
       </c>
       <c r="AB13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.286</v>
+        <v>0.333</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
       </c>
       <c r="AF13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AH13" t="n">
         <v>3</v>
       </c>
       <c r="AI13" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.333</v>
+        <v>0.273</v>
       </c>
       <c r="AK13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AL13" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.214</v>
+        <v>0.263</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>117:52</t>
+          <t>150:38</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>56.72</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.39</v>
+        <v>0.436</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.449</v>
+        <v>0.479</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.74</v>
+        <v>0.791</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.176</v>
+        <v>0.174</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.244</v>
+        <v>0.2</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.1</v>
+        <v>1.154</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.215</v>
+        <v>0.221</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.036</v>
+        <v>0.057</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.142</v>
+        <v>0.12</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.047</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>#7 B. KEY</t>
         </is>
       </c>
       <c r="B14" t="n">
+        <v>9</v>
+      </c>
+      <c r="C14" t="n">
+        <v>90</v>
+      </c>
+      <c r="D14" t="n">
+        <v>28</v>
+      </c>
+      <c r="E14" t="n">
+        <v>51</v>
+      </c>
+      <c r="F14" t="n">
+        <v>5</v>
+      </c>
+      <c r="G14" t="n">
+        <v>14</v>
+      </c>
+      <c r="H14" t="n">
+        <v>19</v>
+      </c>
+      <c r="I14" t="n">
+        <v>23</v>
+      </c>
+      <c r="J14" t="n">
+        <v>22</v>
+      </c>
+      <c r="K14" t="n">
+        <v>39</v>
+      </c>
+      <c r="L14" t="n">
+        <v>15</v>
+      </c>
+      <c r="M14" t="n">
         <v>7</v>
       </c>
-      <c r="C14" t="n">
-        <v>66</v>
-      </c>
-      <c r="D14" t="n">
-        <v>23</v>
-      </c>
-      <c r="E14" t="n">
-        <v>43</v>
-      </c>
-      <c r="F14" t="n">
-        <v>4</v>
-      </c>
-      <c r="G14" t="n">
+      <c r="N14" t="n">
+        <v>8</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
         <v>11</v>
       </c>
-      <c r="H14" t="n">
-        <v>8</v>
-      </c>
-      <c r="I14" t="n">
-        <v>12</v>
-      </c>
-      <c r="J14" t="n">
+      <c r="Q14" t="n">
+        <v>11</v>
+      </c>
+      <c r="R14" t="n">
         <v>20</v>
       </c>
-      <c r="K14" t="n">
-        <v>27</v>
-      </c>
-      <c r="L14" t="n">
+      <c r="S14" t="n">
+        <v>17</v>
+      </c>
+      <c r="T14" t="n">
+        <v>131</v>
+      </c>
+      <c r="U14" t="n">
         <v>13</v>
-      </c>
-      <c r="M14" t="n">
-        <v>6</v>
-      </c>
-      <c r="N14" t="n">
-        <v>7</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>10</v>
-      </c>
-      <c r="R14" t="n">
-        <v>15</v>
-      </c>
-      <c r="S14" t="n">
-        <v>10</v>
-      </c>
-      <c r="T14" t="n">
-        <v>93</v>
-      </c>
-      <c r="U14" t="n">
-        <v>11</v>
       </c>
       <c r="V14" t="n">
         <v>7</v>
       </c>
       <c r="W14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y14" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="Z14" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.679</v>
+        <v>0.697</v>
       </c>
       <c r="AB14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.182</v>
+        <v>0.214</v>
       </c>
       <c r="AE14" t="n">
         <v>2</v>
@@ -2469,256 +2457,256 @@
         <v>0.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AK14" t="n">
         <v>2</v>
       </c>
       <c r="AL14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.286</v>
+        <v>0.222</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>154:34</t>
+          <t>197:11</t>
         </is>
       </c>
       <c r="AO14" t="n">
-        <v>69.28</v>
+        <v>86.12</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.537</v>
+        <v>0.546</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.599</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.953</v>
+        <v>1.045</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.144</v>
+        <v>0.128</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.148</v>
+        <v>0.292</v>
       </c>
       <c r="AU14" t="n">
         <v>2</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.201</v>
+        <v>0.195</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.09</v>
+        <v>0.082</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.182</v>
+        <v>0.21</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.092</v>
+        <v>0.078</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>#8 J. MONTERO</t>
         </is>
       </c>
       <c r="B15" t="n">
+        <v>9</v>
+      </c>
+      <c r="C15" t="n">
+        <v>183</v>
+      </c>
+      <c r="D15" t="n">
+        <v>37</v>
+      </c>
+      <c r="E15" t="n">
+        <v>61</v>
+      </c>
+      <c r="F15" t="n">
+        <v>23</v>
+      </c>
+      <c r="G15" t="n">
+        <v>54</v>
+      </c>
+      <c r="H15" t="n">
+        <v>40</v>
+      </c>
+      <c r="I15" t="n">
+        <v>42</v>
+      </c>
+      <c r="J15" t="n">
+        <v>51</v>
+      </c>
+      <c r="K15" t="n">
+        <v>26</v>
+      </c>
+      <c r="L15" t="n">
         <v>7</v>
       </c>
-      <c r="C15" t="n">
-        <v>131</v>
-      </c>
-      <c r="D15" t="n">
-        <v>28</v>
-      </c>
-      <c r="E15" t="n">
-        <v>46</v>
-      </c>
-      <c r="F15" t="n">
-        <v>15</v>
-      </c>
-      <c r="G15" t="n">
-        <v>40</v>
-      </c>
-      <c r="H15" t="n">
-        <v>30</v>
-      </c>
-      <c r="I15" t="n">
+      <c r="M15" t="n">
+        <v>13</v>
+      </c>
+      <c r="N15" t="n">
+        <v>7</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>16</v>
+      </c>
+      <c r="R15" t="n">
+        <v>11</v>
+      </c>
+      <c r="S15" t="n">
+        <v>43</v>
+      </c>
+      <c r="T15" t="n">
+        <v>246</v>
+      </c>
+      <c r="U15" t="n">
+        <v>33</v>
+      </c>
+      <c r="V15" t="n">
+        <v>21</v>
+      </c>
+      <c r="W15" t="n">
+        <v>17</v>
+      </c>
+      <c r="X15" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z15" t="n">
         <v>32</v>
       </c>
-      <c r="J15" t="n">
-        <v>42</v>
-      </c>
-      <c r="K15" t="n">
-        <v>19</v>
-      </c>
-      <c r="L15" t="n">
-        <v>6</v>
-      </c>
-      <c r="M15" t="n">
-        <v>8</v>
-      </c>
-      <c r="N15" t="n">
-        <v>6</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>13</v>
-      </c>
-      <c r="R15" t="n">
-        <v>9</v>
-      </c>
-      <c r="S15" t="n">
-        <v>34</v>
-      </c>
-      <c r="T15" t="n">
-        <v>179</v>
-      </c>
-      <c r="U15" t="n">
-        <v>22</v>
-      </c>
-      <c r="V15" t="n">
-        <v>15</v>
-      </c>
-      <c r="W15" t="n">
-        <v>13</v>
-      </c>
-      <c r="X15" t="n">
-        <v>9</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>23</v>
-      </c>
       <c r="AA15" t="n">
-        <v>0.696</v>
+        <v>0.719</v>
       </c>
       <c r="AB15" t="n">
         <v>7</v>
       </c>
       <c r="AC15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF15" t="n">
         <v>14</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="AG15" t="n">
         <v>0.5</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>5</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>9</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>0.556</v>
       </c>
       <c r="AH15" t="n">
         <v>2</v>
       </c>
       <c r="AI15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="AK15" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AL15" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.351</v>
+        <v>0.42</v>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>196:19</t>
+          <t>250:14</t>
         </is>
       </c>
       <c r="AO15" t="n">
-        <v>113.08</v>
+        <v>149.48</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.587</v>
+        <v>0.622</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.654</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.158</v>
+        <v>1.224</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.115</v>
+        <v>0.107</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.349</v>
+        <v>0.348</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.231</v>
+        <v>3.188</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.258</v>
+        <v>0.267</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.033</v>
+        <v>0.03</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.101</v>
+        <v>0.11</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.208</v>
+        <v>0.199</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>#10 O. MOORE</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
+        <v>9</v>
+      </c>
+      <c r="E16" t="n">
+        <v>16</v>
+      </c>
+      <c r="F16" t="n">
+        <v>11</v>
+      </c>
+      <c r="G16" t="n">
+        <v>28</v>
+      </c>
+      <c r="H16" t="n">
         <v>6</v>
       </c>
-      <c r="E16" t="n">
-        <v>12</v>
-      </c>
-      <c r="F16" t="n">
-        <v>7</v>
-      </c>
-      <c r="G16" t="n">
-        <v>21</v>
-      </c>
-      <c r="H16" t="n">
-        <v>4</v>
-      </c>
       <c r="I16" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J16" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K16" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L16" t="n">
         <v>6</v>
@@ -2733,19 +2721,19 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T16" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="U16" t="n">
         <v>1</v>
@@ -2760,22 +2748,22 @@
         <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.667</v>
+        <v>0.75</v>
       </c>
       <c r="AB16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.333</v>
+        <v>0.4</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -2787,79 +2775,79 @@
         <v>0.333</v>
       </c>
       <c r="AH16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AI16" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.091</v>
+        <v>0.267</v>
       </c>
       <c r="AK16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL16" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.6</v>
+        <v>0.538</v>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>122:37</t>
+          <t>153:52</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>45.64</v>
+        <v>59.96</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.5</v>
+        <v>0.58</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.519</v>
+        <v>0.594</v>
       </c>
       <c r="AR16" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.951</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.219</v>
+        <v>0.2</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.121</v>
+        <v>0.136</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.167</v>
+        <v>0.174</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.052</v>
+        <v>0.042</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.094</v>
+        <v>0.103</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.022</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>#12 N. SAKO</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E17" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -2868,22 +2856,22 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I17" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J17" t="n">
+        <v>6</v>
+      </c>
+      <c r="K17" t="n">
+        <v>23</v>
+      </c>
+      <c r="L17" t="n">
+        <v>22</v>
+      </c>
+      <c r="M17" t="n">
         <v>4</v>
-      </c>
-      <c r="K17" t="n">
-        <v>19</v>
-      </c>
-      <c r="L17" t="n">
-        <v>17</v>
-      </c>
-      <c r="M17" t="n">
-        <v>3</v>
       </c>
       <c r="N17" t="n">
         <v>4</v>
@@ -2892,19 +2880,19 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="S17" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="T17" t="n">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="U17" t="n">
         <v>9</v>
@@ -2919,13 +2907,13 @@
         <v>4</v>
       </c>
       <c r="Y17" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="Z17" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AB17" t="n">
         <v>3</v>
@@ -2940,7 +2928,7 @@
         <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -2965,45 +2953,45 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>123:46</t>
+          <t>155:22</t>
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>37.04</v>
+        <v>44.36</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.741</v>
+        <v>0.719</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.661</v>
+        <v>0.644</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.215</v>
+        <v>1.172</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.081</v>
+        <v>0.09</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.185</v>
+        <v>0.188</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.333</v>
+        <v>1.5</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.134</v>
+        <v>0.128</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.147</v>
+        <v>0.153</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.16</v>
+        <v>0.157</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.018</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>#13 D. THOMPSON</t>
         </is>
@@ -3162,28 +3150,28 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>#23 A. CÁRDENAS</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G19" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H19" t="n">
         <v>2</v>
@@ -3192,16 +3180,16 @@
         <v>2</v>
       </c>
       <c r="J19" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L19" t="n">
         <v>4</v>
       </c>
       <c r="M19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N19" t="n">
         <v>2</v>
@@ -3216,13 +3204,13 @@
         <v>5</v>
       </c>
       <c r="R19" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T19" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="U19" t="n">
         <v>3</v>
@@ -3231,10 +3219,10 @@
         <v>5</v>
       </c>
       <c r="W19" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y19" t="n">
         <v>2</v>
@@ -3246,103 +3234,103 @@
         <v>0.286</v>
       </c>
       <c r="AB19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF19" t="n">
         <v>4</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AG19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI19" t="n">
         <v>7</v>
       </c>
-      <c r="AD19" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>5</v>
-      </c>
       <c r="AJ19" t="n">
-        <v>0.8</v>
+        <v>0.714</v>
       </c>
       <c r="AK19" t="n">
         <v>3</v>
       </c>
       <c r="AL19" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>99:18</t>
+          <t>125:18</t>
         </is>
       </c>
       <c r="AO19" t="n">
-        <v>35.88</v>
+        <v>44.88</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.55</v>
+        <v>0.513</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.527</v>
       </c>
       <c r="AR19" t="n">
-        <v>0.975</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.139</v>
+        <v>0.111</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.067</v>
+        <v>0.051</v>
       </c>
       <c r="AU19" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.162</v>
+        <v>0.16</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.043</v>
+        <v>0.034</v>
       </c>
       <c r="AX19" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="AY19" t="n">
         <v>0.053</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>0.052</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>#24 M. COSTELLO</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E20" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G20" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H20" t="n">
         <v>5</v>
@@ -3351,19 +3339,19 @@
         <v>7</v>
       </c>
       <c r="J20" t="n">
+        <v>8</v>
+      </c>
+      <c r="K20" t="n">
+        <v>19</v>
+      </c>
+      <c r="L20" t="n">
+        <v>10</v>
+      </c>
+      <c r="M20" t="n">
         <v>6</v>
       </c>
-      <c r="K20" t="n">
-        <v>15</v>
-      </c>
-      <c r="L20" t="n">
-        <v>7</v>
-      </c>
-      <c r="M20" t="n">
-        <v>5</v>
-      </c>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3375,19 +3363,19 @@
         <v>2</v>
       </c>
       <c r="R20" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T20" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="U20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W20" t="n">
         <v>2</v>
@@ -3399,25 +3387,25 @@
         <v>7</v>
       </c>
       <c r="Z20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.7</v>
+        <v>0.636</v>
       </c>
       <c r="AB20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD20" t="n">
         <v>1</v>
       </c>
       <c r="AE20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG20" t="n">
         <v>1</v>
@@ -3432,55 +3420,55 @@
         <v>0.4</v>
       </c>
       <c r="AK20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>19</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>123:03</t>
+        </is>
+      </c>
+      <c r="AO20" t="n">
+        <v>44.08</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0.551</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1.089</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="AU20" t="n">
         <v>4</v>
       </c>
-      <c r="AL20" t="n">
-        <v>16</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>92:52</t>
-        </is>
-      </c>
-      <c r="AO20" t="n">
-        <v>38.08</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0.5679999999999999</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>1.077</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0.152</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>3</v>
-      </c>
       <c r="AV20" t="n">
-        <v>0.183</v>
+        <v>0.16</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.081</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.168</v>
+        <v>0.164</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.026</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>#32 I. NOGUÉS</t>
         </is>
@@ -3639,7 +3627,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>#77 Y. SIMA</t>
         </is>
@@ -3788,23 +3776,23 @@
         <v>0.154</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.116</v>
+        <v>0.117</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.113</v>
+        <v>0.115</v>
       </c>
       <c r="AY22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Equip</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -3834,7 +3822,7 @@
         <v>19</v>
       </c>
       <c r="L23" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -3846,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -3957,325 +3945,325 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C24" t="n">
-        <v>680</v>
+        <v>876</v>
       </c>
       <c r="D24" t="n">
-        <v>168</v>
+        <v>216</v>
       </c>
       <c r="E24" t="n">
-        <v>287</v>
+        <v>373</v>
       </c>
       <c r="F24" t="n">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="G24" t="n">
-        <v>225</v>
+        <v>282</v>
       </c>
       <c r="H24" t="n">
-        <v>113</v>
+        <v>144</v>
       </c>
       <c r="I24" t="n">
-        <v>146</v>
+        <v>183</v>
       </c>
       <c r="J24" t="n">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="K24" t="n">
-        <v>197</v>
+        <v>252</v>
       </c>
       <c r="L24" t="n">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="M24" t="n">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="N24" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="Q24" t="n">
+        <v>90</v>
+      </c>
+      <c r="R24" t="n">
+        <v>175</v>
+      </c>
+      <c r="S24" t="n">
+        <v>182</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1087</v>
+      </c>
+      <c r="U24" t="n">
+        <v>112</v>
+      </c>
+      <c r="V24" t="n">
+        <v>116</v>
+      </c>
+      <c r="W24" t="n">
         <v>71</v>
       </c>
-      <c r="R24" t="n">
-        <v>135</v>
-      </c>
-      <c r="S24" t="n">
-        <v>147</v>
-      </c>
-      <c r="T24" t="n">
-        <v>857</v>
-      </c>
-      <c r="U24" t="n">
+      <c r="X24" t="n">
+        <v>43</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>142</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>203</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>41</v>
+      </c>
+      <c r="AC24" t="n">
         <v>92</v>
       </c>
-      <c r="V24" t="n">
-        <v>94</v>
-      </c>
-      <c r="W24" t="n">
-        <v>59</v>
-      </c>
-      <c r="X24" t="n">
-        <v>36</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>113</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>159</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0.711</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>28</v>
-      </c>
-      <c r="AC24" t="n">
+      <c r="AD24" t="n">
+        <v>0.446</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>33</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>78</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0.423</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>82</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AK24" t="n">
         <v>68</v>
       </c>
-      <c r="AD24" t="n">
-        <v>0.412</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>27</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>60</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>0.369</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>53</v>
-      </c>
       <c r="AL24" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.331</v>
+        <v>0.34</v>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>1450:00</t>
+          <t>1850:00</t>
         </is>
       </c>
       <c r="AO24" t="n">
-        <v>648.24</v>
+        <v>827.52</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.554</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.59</v>
+        <v>0.595</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.049</v>
+        <v>1.059</v>
       </c>
       <c r="AS24" t="n">
         <v>0.111</v>
       </c>
       <c r="AT24" t="n">
-        <v>0.221</v>
+        <v>0.22</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.986</v>
+        <v>1.924</v>
       </c>
       <c r="AV24" t="n">
         <v>0.2</v>
       </c>
       <c r="AW24" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.142</v>
+        <v>0.144</v>
       </c>
       <c r="AY24" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Rival</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C25" t="n">
-        <v>607</v>
+        <v>771</v>
       </c>
       <c r="D25" t="n">
-        <v>141</v>
+        <v>179</v>
       </c>
       <c r="E25" t="n">
-        <v>272</v>
+        <v>337</v>
       </c>
       <c r="F25" t="n">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="G25" t="n">
-        <v>223</v>
+        <v>285</v>
       </c>
       <c r="H25" t="n">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="I25" t="n">
-        <v>122</v>
+        <v>159</v>
       </c>
       <c r="J25" t="n">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c r="K25" t="n">
-        <v>175</v>
+        <v>220</v>
       </c>
       <c r="L25" t="n">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="M25" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="N25" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="Q25" t="n">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="R25" t="n">
-        <v>147</v>
+        <v>183</v>
       </c>
       <c r="S25" t="n">
-        <v>134</v>
+        <v>174</v>
       </c>
       <c r="T25" t="n">
-        <v>670</v>
+        <v>834</v>
       </c>
       <c r="U25" t="n">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="V25" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="W25" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="X25" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="Y25" t="n">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="Z25" t="n">
-        <v>145</v>
+        <v>181</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.676</v>
+        <v>0.669</v>
       </c>
       <c r="AB25" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="AC25" t="n">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.348</v>
+        <v>0.385</v>
       </c>
       <c r="AE25" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AF25" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.316</v>
+        <v>0.346</v>
       </c>
       <c r="AH25" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="AI25" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.418</v>
+        <v>0.42</v>
       </c>
       <c r="AK25" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AL25" t="n">
-        <v>168</v>
+        <v>216</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.327</v>
+        <v>0.324</v>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>1450:00</t>
+          <t>1850:00</t>
         </is>
       </c>
       <c r="AO25" t="n">
-        <v>639.6799999999999</v>
+        <v>810.96</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.521</v>
+        <v>0.527</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.553</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="AR25" t="n">
-        <v>0.949</v>
+        <v>0.951</v>
       </c>
       <c r="AS25" t="n">
-        <v>0.142</v>
+        <v>0.147</v>
       </c>
       <c r="AT25" t="n">
-        <v>0.184</v>
+        <v>0.186</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.374</v>
+        <v>1.269</v>
       </c>
       <c r="AV25" t="n">
         <v>0.2</v>
       </c>
       <c r="AW25" t="n">
-        <v>0.058</v>
+        <v>0.056</v>
       </c>
       <c r="AX25" t="n">
-        <v>0.129</v>
+        <v>0.128</v>
       </c>
       <c r="AY25" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>--- PER GAME STATS ---</t>
         </is>
@@ -4332,340 +4320,340 @@
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>#0 B. BADIO (Per Game)</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C27" t="n">
-        <v>11.857</v>
+        <v>10.222</v>
       </c>
       <c r="D27" t="n">
-        <v>2.571</v>
+        <v>2.111</v>
       </c>
       <c r="E27" t="n">
-        <v>4.143</v>
+        <v>3.889</v>
       </c>
       <c r="F27" t="n">
-        <v>1.571</v>
+        <v>1.444</v>
       </c>
       <c r="G27" t="n">
-        <v>5.143</v>
+        <v>4.778</v>
       </c>
       <c r="H27" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="I27" t="n">
         <v>2</v>
       </c>
-      <c r="I27" t="n">
-        <v>2.429</v>
-      </c>
       <c r="J27" t="n">
-        <v>2.571</v>
+        <v>2.444</v>
       </c>
       <c r="K27" t="n">
-        <v>1.286</v>
+        <v>1.889</v>
       </c>
       <c r="L27" t="n">
-        <v>0.429</v>
+        <v>0.333</v>
       </c>
       <c r="M27" t="n">
-        <v>0.571</v>
+        <v>0.667</v>
       </c>
       <c r="N27" t="n">
-        <v>0.429</v>
+        <v>0.333</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>0.429</v>
+        <v>0.667</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.429</v>
+        <v>0.667</v>
       </c>
       <c r="R27" t="n">
-        <v>2.143</v>
+        <v>1.889</v>
       </c>
       <c r="S27" t="n">
-        <v>2</v>
+        <v>1.556</v>
       </c>
       <c r="T27" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="U27" t="n">
-        <v>1.714</v>
+        <v>1.333</v>
       </c>
       <c r="V27" t="n">
-        <v>0.714</v>
+        <v>0.556</v>
       </c>
       <c r="W27" t="n">
-        <v>0.571</v>
+        <v>0.444</v>
       </c>
       <c r="X27" t="n">
-        <v>0.429</v>
+        <v>0.333</v>
       </c>
       <c r="Y27" t="n">
-        <v>1</v>
+        <v>0.778</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.286</v>
+        <v>1.222</v>
       </c>
       <c r="AA27" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.778</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH27" t="n">
         <v>0.778</v>
       </c>
-      <c r="AB27" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.857</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0.538</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0.857</v>
-      </c>
       <c r="AI27" t="n">
-        <v>1.714</v>
+        <v>1.667</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.5</v>
+        <v>0.467</v>
       </c>
       <c r="AK27" t="n">
-        <v>0.714</v>
+        <v>0.667</v>
       </c>
       <c r="AL27" t="n">
-        <v>3.429</v>
+        <v>3.111</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.208</v>
+        <v>0.214</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>25:40</t>
+          <t>25:12</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>10.783</v>
+        <v>10.213</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.531</v>
+        <v>0.494</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.573</v>
+        <v>0.535</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.1</v>
+        <v>1.001</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.04</v>
+        <v>0.065</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.215</v>
+        <v>0.192</v>
       </c>
       <c r="AU27" t="n">
-        <v>6</v>
+        <v>3.667</v>
       </c>
       <c r="AV27" t="n">
-        <v>0.188</v>
+        <v>0.181</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.018</v>
+        <v>0.014</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.052</v>
+        <v>0.079</v>
       </c>
       <c r="AY27" t="n">
-        <v>0.083</v>
+        <v>0.077</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>#1 K. TAYLOR (Per Game)</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C28" t="n">
-        <v>12</v>
+        <v>13.111</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>3.556</v>
       </c>
       <c r="E28" t="n">
-        <v>4.857</v>
+        <v>6.111</v>
       </c>
       <c r="F28" t="n">
-        <v>1.571</v>
+        <v>1.556</v>
       </c>
       <c r="G28" t="n">
-        <v>4.857</v>
+        <v>4.444</v>
       </c>
       <c r="H28" t="n">
-        <v>1.286</v>
+        <v>1.333</v>
       </c>
       <c r="I28" t="n">
-        <v>1.571</v>
+        <v>1.556</v>
       </c>
       <c r="J28" t="n">
-        <v>1.714</v>
+        <v>1.444</v>
       </c>
       <c r="K28" t="n">
-        <v>3.429</v>
+        <v>3.444</v>
       </c>
       <c r="L28" t="n">
-        <v>0.714</v>
+        <v>0.778</v>
       </c>
       <c r="M28" t="n">
-        <v>1.571</v>
+        <v>1.667</v>
       </c>
       <c r="N28" t="n">
-        <v>0.571</v>
+        <v>0.556</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1</v>
+        <v>0.889</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0.889</v>
       </c>
       <c r="R28" t="n">
-        <v>1.571</v>
+        <v>1.778</v>
       </c>
       <c r="S28" t="n">
+        <v>2.333</v>
+      </c>
+      <c r="T28" t="n">
+        <v>135</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="V28" t="n">
         <v>2</v>
       </c>
-      <c r="T28" t="n">
-        <v>98</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1</v>
-      </c>
-      <c r="V28" t="n">
-        <v>2.143</v>
-      </c>
       <c r="W28" t="n">
-        <v>0.857</v>
+        <v>0.667</v>
       </c>
       <c r="X28" t="n">
-        <v>0.571</v>
+        <v>0.444</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.286</v>
+        <v>1.333</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.429</v>
+        <v>1.889</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.9</v>
+        <v>0.706</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.429</v>
+        <v>1.111</v>
       </c>
       <c r="AC28" t="n">
-        <v>1</v>
+        <v>1.778</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.429</v>
+        <v>0.625</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.286</v>
+        <v>1.111</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.429</v>
+        <v>2.444</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.529</v>
+        <v>0.455</v>
       </c>
       <c r="AH28" t="n">
-        <v>0.143</v>
+        <v>0.333</v>
       </c>
       <c r="AI28" t="n">
         <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.143</v>
+        <v>0.333</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.429</v>
+        <v>1.222</v>
       </c>
       <c r="AL28" t="n">
-        <v>3.857</v>
+        <v>3.444</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.37</v>
+        <v>0.355</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>26:08</t>
+          <t>25:48</t>
         </is>
       </c>
       <c r="AO28" t="n">
-        <v>11.406</v>
+        <v>12.129</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.551</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.577</v>
+        <v>0.583</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.052</v>
+        <v>1.081</v>
       </c>
       <c r="AS28" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.073</v>
       </c>
       <c r="AT28" t="n">
-        <v>0.132</v>
+        <v>0.126</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.714</v>
+        <v>1.625</v>
       </c>
       <c r="AV28" t="n">
-        <v>0.195</v>
+        <v>0.21</v>
       </c>
       <c r="AW28" t="n">
-        <v>0.029</v>
+        <v>0.033</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.137</v>
+        <v>0.142</v>
       </c>
       <c r="AY28" t="n">
-        <v>0.056</v>
+        <v>0.048</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>#2 J. PUERTO (Per Game)</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>0.667</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4674,16 +4662,16 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>2</v>
+        <v>0.667</v>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>0.667</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -4698,10 +4686,10 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -4719,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>2</v>
+        <v>0.667</v>
       </c>
       <c r="X29" t="n">
-        <v>2</v>
+        <v>0.667</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
@@ -4746,7 +4734,7 @@
         <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>
@@ -4771,11 +4759,11 @@
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>04:01</t>
+          <t>01:20</t>
         </is>
       </c>
       <c r="AO29" t="n">
-        <v>2.88</v>
+        <v>0.96</v>
       </c>
       <c r="AP29" t="n">
         <v>0</v>
@@ -4802,56 +4790,56 @@
         <v>0</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.26</v>
+        <v>0.264</v>
       </c>
       <c r="AY29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>#3 N. REUVERS (Per Game)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>8.333</v>
+        <v>5.8</v>
       </c>
       <c r="D30" t="n">
-        <v>1.667</v>
+        <v>1.4</v>
       </c>
       <c r="E30" t="n">
-        <v>2.333</v>
+        <v>2.2</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="G30" t="n">
-        <v>1.333</v>
+        <v>1.2</v>
       </c>
       <c r="H30" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="I30" t="n">
-        <v>2.333</v>
+        <v>1.4</v>
       </c>
       <c r="J30" t="n">
-        <v>0.667</v>
+        <v>0.4</v>
       </c>
       <c r="K30" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="L30" t="n">
-        <v>0.333</v>
+        <v>0.8</v>
       </c>
       <c r="M30" t="n">
-        <v>0.667</v>
+        <v>0.6</v>
       </c>
       <c r="N30" t="n">
-        <v>0.333</v>
+        <v>0.4</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4863,49 +4851,49 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.333</v>
+        <v>2.4</v>
       </c>
       <c r="S30" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="T30" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="U30" t="n">
-        <v>0.667</v>
+        <v>0.4</v>
       </c>
       <c r="V30" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="W30" t="n">
-        <v>0.333</v>
+        <v>0.2</v>
       </c>
       <c r="X30" t="n">
-        <v>0.333</v>
+        <v>0.2</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.333</v>
+        <v>1.2</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.333</v>
+        <v>1.4</v>
       </c>
       <c r="AA30" t="n">
-        <v>1</v>
+        <v>0.857</v>
       </c>
       <c r="AB30" t="n">
         <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.333</v>
+        <v>0.2</v>
       </c>
       <c r="AF30" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="AG30" t="n">
         <v>0.333</v>
@@ -4914,871 +4902,871 @@
         <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.333</v>
+        <v>0.4</v>
       </c>
       <c r="AJ30" t="n">
         <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="AL30" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AM30" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>4.693</v>
+        <v>4.016</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.864</v>
+        <v>0.676</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.888</v>
+        <v>0.722</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.776</v>
+        <v>1.444</v>
       </c>
       <c r="AS30" t="n">
         <v>0</v>
       </c>
       <c r="AT30" t="n">
-        <v>0.545</v>
+        <v>0.353</v>
       </c>
       <c r="AU30" t="n">
         <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.186</v>
+        <v>0.18</v>
       </c>
       <c r="AW30" t="n">
-        <v>0.032</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.184</v>
+        <v>0.149</v>
       </c>
       <c r="AY30" t="n">
-        <v>0.021</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>#4 J. PRADILLA (Per Game)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C31" t="n">
-        <v>10</v>
+        <v>9.444000000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>2.571</v>
+        <v>2.556</v>
       </c>
       <c r="E31" t="n">
-        <v>4.286</v>
+        <v>4.333</v>
       </c>
       <c r="F31" t="n">
-        <v>0.857</v>
+        <v>0.778</v>
       </c>
       <c r="G31" t="n">
-        <v>2.571</v>
+        <v>2.333</v>
       </c>
       <c r="H31" t="n">
-        <v>2.286</v>
+        <v>2</v>
       </c>
       <c r="I31" t="n">
-        <v>2.714</v>
+        <v>2.556</v>
       </c>
       <c r="J31" t="n">
-        <v>1.571</v>
+        <v>1.556</v>
       </c>
       <c r="K31" t="n">
         <v>3</v>
       </c>
       <c r="L31" t="n">
-        <v>1.857</v>
+        <v>1.889</v>
       </c>
       <c r="M31" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.556</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.222</v>
+      </c>
+      <c r="T31" t="n">
+        <v>115</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.556</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>2.444</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>3.556</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AI31" t="n">
         <v>1</v>
       </c>
-      <c r="N31" t="n">
-        <v>0.857</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>1</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.286</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.571</v>
-      </c>
-      <c r="T31" t="n">
-        <v>103</v>
-      </c>
-      <c r="U31" t="n">
-        <v>2</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.857</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0.714</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>2.571</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>3.571</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>1.143</v>
-      </c>
       <c r="AJ31" t="n">
-        <v>0.375</v>
+        <v>0.333</v>
       </c>
       <c r="AK31" t="n">
-        <v>0.429</v>
+        <v>0.444</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.429</v>
+        <v>1.333</v>
       </c>
       <c r="AM31" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AN31" t="inlineStr">
+        <is>
+          <t>21:07</t>
+        </is>
+      </c>
+      <c r="AO31" t="n">
+        <v>9.124000000000001</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0.5580000000000001</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0.606</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1.035</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="AT31" t="n">
         <v>0.3</v>
       </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>21:28</t>
-        </is>
-      </c>
-      <c r="AO31" t="n">
-        <v>9.051</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>0.5620000000000001</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>0.621</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>1.105</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>0.333</v>
-      </c>
       <c r="AU31" t="n">
-        <v>1.571</v>
+        <v>1.167</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.189</v>
+        <v>0.193</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.093</v>
+        <v>0.096</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.146</v>
+        <v>0.151</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.05</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>#5 S. DE LARREA (Per Game)</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C32" t="n">
-        <v>6</v>
+        <v>6.556</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>1.333</v>
       </c>
       <c r="E32" t="n">
-        <v>2.571</v>
+        <v>2.778</v>
       </c>
       <c r="F32" t="n">
-        <v>0.857</v>
+        <v>0.889</v>
       </c>
       <c r="G32" t="n">
-        <v>3.286</v>
+        <v>3.333</v>
       </c>
       <c r="H32" t="n">
-        <v>1.429</v>
+        <v>1.222</v>
       </c>
       <c r="I32" t="n">
-        <v>1.857</v>
+        <v>1.667</v>
       </c>
       <c r="J32" t="n">
-        <v>1.571</v>
+        <v>1.667</v>
       </c>
       <c r="K32" t="n">
-        <v>2.286</v>
+        <v>1.889</v>
       </c>
       <c r="L32" t="n">
-        <v>0.571</v>
+        <v>0.889</v>
       </c>
       <c r="M32" t="n">
-        <v>0.714</v>
+        <v>0.556</v>
       </c>
       <c r="N32" t="n">
-        <v>0.714</v>
+        <v>0.556</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.429</v>
+        <v>1.444</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.429</v>
+        <v>1.444</v>
       </c>
       <c r="R32" t="n">
-        <v>1.714</v>
+        <v>1.667</v>
       </c>
       <c r="S32" t="n">
-        <v>2.143</v>
+        <v>1.778</v>
       </c>
       <c r="T32" t="n">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="U32" t="n">
-        <v>0.714</v>
+        <v>0.556</v>
       </c>
       <c r="V32" t="n">
-        <v>0.857</v>
+        <v>1.444</v>
       </c>
       <c r="W32" t="n">
-        <v>0.714</v>
+        <v>0.889</v>
       </c>
       <c r="X32" t="n">
-        <v>0.286</v>
+        <v>0.333</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.571</v>
+        <v>0.889</v>
       </c>
       <c r="Z32" t="n">
-        <v>1</v>
+        <v>1.222</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.571</v>
+        <v>0.727</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.286</v>
+        <v>0.333</v>
       </c>
       <c r="AC32" t="n">
         <v>1</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.286</v>
+        <v>0.333</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.143</v>
+        <v>0.111</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.571</v>
+        <v>0.556</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.429</v>
+        <v>0.333</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.286</v>
+        <v>1.222</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.333</v>
+        <v>0.273</v>
       </c>
       <c r="AK32" t="n">
-        <v>0.429</v>
+        <v>0.556</v>
       </c>
       <c r="AL32" t="n">
-        <v>2</v>
+        <v>2.111</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.214</v>
+        <v>0.263</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>8.103</v>
+        <v>8.289</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.39</v>
+        <v>0.436</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.449</v>
+        <v>0.479</v>
       </c>
       <c r="AR32" t="n">
-        <v>0.74</v>
+        <v>0.791</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.176</v>
+        <v>0.174</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.244</v>
+        <v>0.2</v>
       </c>
       <c r="AU32" t="n">
-        <v>1.1</v>
+        <v>1.154</v>
       </c>
       <c r="AV32" t="n">
-        <v>0.215</v>
+        <v>0.221</v>
       </c>
       <c r="AW32" t="n">
-        <v>0.036</v>
+        <v>0.057</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.142</v>
+        <v>0.12</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.047</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>#7 B. KEY (Per Game)</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C33" t="n">
-        <v>9.429</v>
+        <v>10</v>
       </c>
       <c r="D33" t="n">
-        <v>3.286</v>
+        <v>3.111</v>
       </c>
       <c r="E33" t="n">
-        <v>6.143</v>
+        <v>5.667</v>
       </c>
       <c r="F33" t="n">
-        <v>0.571</v>
+        <v>0.556</v>
       </c>
       <c r="G33" t="n">
-        <v>1.571</v>
+        <v>1.556</v>
       </c>
       <c r="H33" t="n">
-        <v>1.143</v>
+        <v>2.111</v>
       </c>
       <c r="I33" t="n">
-        <v>1.714</v>
+        <v>2.556</v>
       </c>
       <c r="J33" t="n">
-        <v>2.857</v>
+        <v>2.444</v>
       </c>
       <c r="K33" t="n">
-        <v>3.857</v>
+        <v>4.333</v>
       </c>
       <c r="L33" t="n">
-        <v>1.857</v>
+        <v>1.667</v>
       </c>
       <c r="M33" t="n">
-        <v>0.857</v>
+        <v>0.778</v>
       </c>
       <c r="N33" t="n">
-        <v>1</v>
+        <v>0.889</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.429</v>
+        <v>1.222</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.429</v>
+        <v>1.222</v>
       </c>
       <c r="R33" t="n">
-        <v>2.143</v>
+        <v>2.222</v>
       </c>
       <c r="S33" t="n">
-        <v>1.429</v>
+        <v>1.889</v>
       </c>
       <c r="T33" t="n">
-        <v>93</v>
+        <v>131</v>
       </c>
       <c r="U33" t="n">
-        <v>1.571</v>
+        <v>1.444</v>
       </c>
       <c r="V33" t="n">
-        <v>1</v>
+        <v>0.778</v>
       </c>
       <c r="W33" t="n">
-        <v>1.143</v>
+        <v>1.111</v>
       </c>
       <c r="X33" t="n">
-        <v>0.571</v>
+        <v>0.667</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.714</v>
+        <v>2.556</v>
       </c>
       <c r="Z33" t="n">
-        <v>4</v>
+        <v>3.667</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.679</v>
+        <v>0.697</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.286</v>
+        <v>0.333</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.571</v>
+        <v>1.556</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.182</v>
+        <v>0.214</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.286</v>
+        <v>0.222</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.571</v>
+        <v>0.444</v>
       </c>
       <c r="AG33" t="n">
         <v>0.5</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.286</v>
+        <v>0.333</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.571</v>
+        <v>0.556</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AK33" t="n">
-        <v>0.286</v>
+        <v>0.222</v>
       </c>
       <c r="AL33" t="n">
         <v>1</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.286</v>
+        <v>0.222</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>22:04</t>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>9.897</v>
+        <v>9.569000000000001</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.537</v>
+        <v>0.546</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.599</v>
       </c>
       <c r="AR33" t="n">
-        <v>0.953</v>
+        <v>1.045</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.144</v>
+        <v>0.128</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.148</v>
+        <v>0.292</v>
       </c>
       <c r="AU33" t="n">
         <v>2</v>
       </c>
       <c r="AV33" t="n">
-        <v>0.201</v>
+        <v>0.195</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.09</v>
+        <v>0.082</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.182</v>
+        <v>0.21</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.092</v>
+        <v>0.078</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>#8 J. MONTERO (Per Game)</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C34" t="n">
-        <v>18.714</v>
+        <v>20.333</v>
       </c>
       <c r="D34" t="n">
-        <v>4</v>
+        <v>4.111</v>
       </c>
       <c r="E34" t="n">
-        <v>6.571</v>
+        <v>6.778</v>
       </c>
       <c r="F34" t="n">
-        <v>2.143</v>
+        <v>2.556</v>
       </c>
       <c r="G34" t="n">
-        <v>5.714</v>
+        <v>6</v>
       </c>
       <c r="H34" t="n">
-        <v>4.286</v>
+        <v>4.444</v>
       </c>
       <c r="I34" t="n">
-        <v>4.571</v>
+        <v>4.667</v>
       </c>
       <c r="J34" t="n">
-        <v>6</v>
+        <v>5.667</v>
       </c>
       <c r="K34" t="n">
-        <v>2.714</v>
+        <v>2.889</v>
       </c>
       <c r="L34" t="n">
-        <v>0.857</v>
+        <v>0.778</v>
       </c>
       <c r="M34" t="n">
-        <v>1.143</v>
+        <v>1.444</v>
       </c>
       <c r="N34" t="n">
-        <v>0.857</v>
+        <v>0.778</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.857</v>
+        <v>1.778</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.857</v>
+        <v>1.778</v>
       </c>
       <c r="R34" t="n">
-        <v>1.286</v>
+        <v>1.222</v>
       </c>
       <c r="S34" t="n">
-        <v>4.857</v>
+        <v>4.778</v>
       </c>
       <c r="T34" t="n">
-        <v>179</v>
+        <v>246</v>
       </c>
       <c r="U34" t="n">
-        <v>3.143</v>
+        <v>3.667</v>
       </c>
       <c r="V34" t="n">
-        <v>2.143</v>
+        <v>2.333</v>
       </c>
       <c r="W34" t="n">
-        <v>1.857</v>
+        <v>1.889</v>
       </c>
       <c r="X34" t="n">
-        <v>1.286</v>
+        <v>1.333</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.286</v>
+        <v>2.556</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.286</v>
+        <v>3.556</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.696</v>
+        <v>0.719</v>
       </c>
       <c r="AB34" t="n">
-        <v>1</v>
+        <v>0.778</v>
       </c>
       <c r="AC34" t="n">
-        <v>2</v>
+        <v>1.667</v>
       </c>
       <c r="AD34" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.556</v>
+      </c>
+      <c r="AG34" t="n">
         <v>0.5</v>
       </c>
-      <c r="AE34" t="n">
-        <v>0.714</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.286</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>0.556</v>
-      </c>
       <c r="AH34" t="n">
-        <v>0.286</v>
+        <v>0.222</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.429</v>
+        <v>0.444</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.857</v>
+        <v>2.333</v>
       </c>
       <c r="AL34" t="n">
-        <v>5.286</v>
+        <v>5.556</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.351</v>
+        <v>0.42</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>28:02</t>
+          <t>27:48</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>16.154</v>
+        <v>16.609</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.587</v>
+        <v>0.622</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.654</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.158</v>
+        <v>1.224</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.115</v>
+        <v>0.107</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.349</v>
+        <v>0.348</v>
       </c>
       <c r="AU34" t="n">
-        <v>3.231</v>
+        <v>3.188</v>
       </c>
       <c r="AV34" t="n">
-        <v>0.258</v>
+        <v>0.267</v>
       </c>
       <c r="AW34" t="n">
-        <v>0.033</v>
+        <v>0.03</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.101</v>
+        <v>0.11</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.208</v>
+        <v>0.199</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>#10 O. MOORE (Per Game)</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C35" t="n">
-        <v>5.286</v>
+        <v>6.333</v>
       </c>
       <c r="D35" t="n">
-        <v>0.857</v>
+        <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>1.714</v>
+        <v>1.778</v>
       </c>
       <c r="F35" t="n">
+        <v>1.222</v>
+      </c>
+      <c r="G35" t="n">
+        <v>3.111</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="I35" t="n">
         <v>1</v>
       </c>
-      <c r="G35" t="n">
-        <v>3</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0.857</v>
-      </c>
       <c r="J35" t="n">
-        <v>0.714</v>
+        <v>0.889</v>
       </c>
       <c r="K35" t="n">
-        <v>1.571</v>
+        <v>1.667</v>
       </c>
       <c r="L35" t="n">
-        <v>0.857</v>
+        <v>0.667</v>
       </c>
       <c r="M35" t="n">
-        <v>0.143</v>
+        <v>0.111</v>
       </c>
       <c r="N35" t="n">
-        <v>0.429</v>
+        <v>0.333</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1.429</v>
+        <v>1.333</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.429</v>
+        <v>1.333</v>
       </c>
       <c r="R35" t="n">
-        <v>0.857</v>
+        <v>0.778</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
       </c>
       <c r="T35" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="U35" t="n">
-        <v>0.143</v>
+        <v>0.111</v>
       </c>
       <c r="V35" t="n">
-        <v>0.714</v>
+        <v>0.556</v>
       </c>
       <c r="W35" t="n">
-        <v>0.429</v>
+        <v>0.333</v>
       </c>
       <c r="X35" t="n">
-        <v>0.143</v>
+        <v>0.111</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.571</v>
+        <v>0.667</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.857</v>
+        <v>0.889</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.667</v>
+        <v>0.75</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.143</v>
+        <v>0.222</v>
       </c>
       <c r="AC35" t="n">
-        <v>0.429</v>
+        <v>0.556</v>
       </c>
       <c r="AD35" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="AF35" t="n">
         <v>0.333</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>0.429</v>
       </c>
       <c r="AG35" t="n">
         <v>0.333</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.143</v>
+        <v>0.444</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.571</v>
+        <v>1.667</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.091</v>
+        <v>0.267</v>
       </c>
       <c r="AK35" t="n">
-        <v>0.857</v>
+        <v>0.778</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.429</v>
+        <v>1.444</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.6</v>
+        <v>0.538</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>6.52</v>
+        <v>6.662</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.5</v>
+        <v>0.58</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.519</v>
+        <v>0.594</v>
       </c>
       <c r="AR35" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.951</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.219</v>
+        <v>0.2</v>
       </c>
       <c r="AT35" t="n">
-        <v>0.121</v>
+        <v>0.136</v>
       </c>
       <c r="AU35" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
       </c>
       <c r="AV35" t="n">
-        <v>0.167</v>
+        <v>0.174</v>
       </c>
       <c r="AW35" t="n">
-        <v>0.052</v>
+        <v>0.042</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.094</v>
+        <v>0.103</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.022</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>#12 N. SAKO (Per Game)</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C36" t="n">
-        <v>6.429</v>
+        <v>5.778</v>
       </c>
       <c r="D36" t="n">
-        <v>2.857</v>
+        <v>2.556</v>
       </c>
       <c r="E36" t="n">
-        <v>3.857</v>
+        <v>3.556</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -5787,70 +5775,70 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.714</v>
+        <v>0.667</v>
       </c>
       <c r="I36" t="n">
-        <v>2.286</v>
+        <v>2.111</v>
       </c>
       <c r="J36" t="n">
-        <v>0.571</v>
+        <v>0.667</v>
       </c>
       <c r="K36" t="n">
-        <v>2.714</v>
+        <v>2.556</v>
       </c>
       <c r="L36" t="n">
-        <v>2.429</v>
+        <v>2.444</v>
       </c>
       <c r="M36" t="n">
-        <v>0.429</v>
+        <v>0.444</v>
       </c>
       <c r="N36" t="n">
-        <v>0.571</v>
+        <v>0.444</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0.429</v>
+        <v>0.444</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.429</v>
+        <v>0.444</v>
       </c>
       <c r="R36" t="n">
-        <v>1.571</v>
+        <v>1.778</v>
       </c>
       <c r="S36" t="n">
-        <v>2.429</v>
+        <v>2.222</v>
       </c>
       <c r="T36" t="n">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="U36" t="n">
-        <v>1.286</v>
+        <v>1</v>
       </c>
       <c r="V36" t="n">
-        <v>0.857</v>
+        <v>0.667</v>
       </c>
       <c r="W36" t="n">
-        <v>0.714</v>
+        <v>0.556</v>
       </c>
       <c r="X36" t="n">
-        <v>0.571</v>
+        <v>0.444</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.429</v>
+        <v>2.222</v>
       </c>
       <c r="Z36" t="n">
-        <v>3</v>
+        <v>2.778</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.429</v>
+        <v>0.333</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.857</v>
+        <v>0.667</v>
       </c>
       <c r="AD36" t="n">
         <v>0.5</v>
@@ -5859,7 +5847,7 @@
         <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -5884,45 +5872,45 @@
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>5.291</v>
+        <v>4.929</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.741</v>
+        <v>0.719</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.661</v>
+        <v>0.644</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.215</v>
+        <v>1.172</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.081</v>
+        <v>0.09</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.185</v>
+        <v>0.188</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.333</v>
+        <v>1.5</v>
       </c>
       <c r="AV36" t="n">
-        <v>0.134</v>
+        <v>0.128</v>
       </c>
       <c r="AW36" t="n">
-        <v>0.147</v>
+        <v>0.153</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.16</v>
+        <v>0.157</v>
       </c>
       <c r="AY36" t="n">
-        <v>0.018</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>#13 D. THOMPSON (Per Game)</t>
         </is>
@@ -6081,325 +6069,325 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>#23 A. CÁRDENAS (Per Game)</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C38" t="n">
-        <v>5</v>
+        <v>4.667</v>
       </c>
       <c r="D38" t="n">
-        <v>0.857</v>
+        <v>0.889</v>
       </c>
       <c r="E38" t="n">
-        <v>2.286</v>
+        <v>2.222</v>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>0.889</v>
       </c>
       <c r="G38" t="n">
-        <v>2</v>
+        <v>2.111</v>
       </c>
       <c r="H38" t="n">
-        <v>0.286</v>
+        <v>0.222</v>
       </c>
       <c r="I38" t="n">
-        <v>0.286</v>
+        <v>0.222</v>
       </c>
       <c r="J38" t="n">
-        <v>1.714</v>
+        <v>1.778</v>
       </c>
       <c r="K38" t="n">
-        <v>0.714</v>
+        <v>0.667</v>
       </c>
       <c r="L38" t="n">
-        <v>0.571</v>
+        <v>0.444</v>
       </c>
       <c r="M38" t="n">
-        <v>0.286</v>
+        <v>0.333</v>
       </c>
       <c r="N38" t="n">
-        <v>0.286</v>
+        <v>0.222</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>0.714</v>
+        <v>0.556</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.714</v>
+        <v>0.556</v>
       </c>
       <c r="R38" t="n">
-        <v>3</v>
+        <v>2.667</v>
       </c>
       <c r="S38" t="n">
-        <v>0.714</v>
+        <v>0.889</v>
       </c>
       <c r="T38" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="U38" t="n">
-        <v>0.429</v>
+        <v>0.333</v>
       </c>
       <c r="V38" t="n">
-        <v>0.714</v>
+        <v>0.556</v>
       </c>
       <c r="W38" t="n">
-        <v>0.714</v>
+        <v>0.889</v>
       </c>
       <c r="X38" t="n">
-        <v>0.429</v>
+        <v>0.444</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.286</v>
+        <v>0.222</v>
       </c>
       <c r="Z38" t="n">
-        <v>1</v>
+        <v>0.778</v>
       </c>
       <c r="AA38" t="n">
         <v>0.286</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.571</v>
+        <v>0.556</v>
       </c>
       <c r="AC38" t="n">
         <v>1</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.571</v>
+        <v>0.556</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.286</v>
+        <v>0.444</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AH38" t="n">
-        <v>0.571</v>
+        <v>0.556</v>
       </c>
       <c r="AI38" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="AJ38" t="n">
         <v>0.714</v>
       </c>
-      <c r="AJ38" t="n">
-        <v>0.8</v>
-      </c>
       <c r="AK38" t="n">
-        <v>0.429</v>
+        <v>0.333</v>
       </c>
       <c r="AL38" t="n">
-        <v>1.286</v>
+        <v>1.333</v>
       </c>
       <c r="AM38" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AO38" t="n">
-        <v>5.126</v>
+        <v>4.987</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.55</v>
+        <v>0.513</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.527</v>
       </c>
       <c r="AR38" t="n">
-        <v>0.975</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="AS38" t="n">
-        <v>0.139</v>
+        <v>0.111</v>
       </c>
       <c r="AT38" t="n">
-        <v>0.067</v>
+        <v>0.051</v>
       </c>
       <c r="AU38" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="AV38" t="n">
-        <v>0.162</v>
+        <v>0.16</v>
       </c>
       <c r="AW38" t="n">
-        <v>0.043</v>
+        <v>0.034</v>
       </c>
       <c r="AX38" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="AY38" t="n">
         <v>0.053</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>0.052</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>#24 M. COSTELLO (Per Game)</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C39" t="n">
-        <v>8.199999999999999</v>
+        <v>6.857</v>
       </c>
       <c r="D39" t="n">
-        <v>1.8</v>
+        <v>1.571</v>
       </c>
       <c r="E39" t="n">
-        <v>2.4</v>
+        <v>2.143</v>
       </c>
       <c r="F39" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>4.2</v>
+        <v>3.429</v>
       </c>
       <c r="H39" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="I39" t="n">
         <v>1</v>
       </c>
-      <c r="I39" t="n">
-        <v>1.4</v>
-      </c>
       <c r="J39" t="n">
-        <v>1.2</v>
+        <v>1.143</v>
       </c>
       <c r="K39" t="n">
-        <v>3</v>
+        <v>2.714</v>
       </c>
       <c r="L39" t="n">
-        <v>1.4</v>
+        <v>1.429</v>
       </c>
       <c r="M39" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="R39" t="n">
+        <v>2.143</v>
+      </c>
+      <c r="S39" t="n">
         <v>1</v>
       </c>
-      <c r="N39" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="R39" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S39" t="n">
-        <v>1.2</v>
-      </c>
       <c r="T39" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="U39" t="n">
-        <v>0.4</v>
+        <v>0.571</v>
       </c>
       <c r="V39" t="n">
         <v>1</v>
       </c>
       <c r="W39" t="n">
-        <v>0.4</v>
+        <v>0.286</v>
       </c>
       <c r="X39" t="n">
-        <v>0.2</v>
+        <v>0.143</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="Z39" t="n">
-        <v>2</v>
+        <v>1.571</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.7</v>
+        <v>0.636</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.2</v>
+        <v>0.286</v>
       </c>
       <c r="AC39" t="n">
-        <v>0.2</v>
+        <v>0.286</v>
       </c>
       <c r="AD39" t="n">
         <v>1</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.2</v>
+        <v>0.286</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.2</v>
+        <v>0.286</v>
       </c>
       <c r="AG39" t="n">
         <v>1</v>
       </c>
       <c r="AH39" t="n">
-        <v>0.4</v>
+        <v>0.286</v>
       </c>
       <c r="AI39" t="n">
-        <v>1</v>
+        <v>0.714</v>
       </c>
       <c r="AJ39" t="n">
         <v>0.4</v>
       </c>
       <c r="AK39" t="n">
-        <v>0.8</v>
+        <v>0.714</v>
       </c>
       <c r="AL39" t="n">
-        <v>3.2</v>
+        <v>2.714</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.25</v>
+        <v>0.263</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>7.616</v>
+        <v>6.297</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.545</v>
+        <v>0.551</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.57</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.077</v>
+        <v>1.089</v>
       </c>
       <c r="AS39" t="n">
-        <v>0.053</v>
+        <v>0.045</v>
       </c>
       <c r="AT39" t="n">
-        <v>0.152</v>
+        <v>0.128</v>
       </c>
       <c r="AU39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV39" t="n">
-        <v>0.183</v>
+        <v>0.16</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.081</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.168</v>
+        <v>0.164</v>
       </c>
       <c r="AY39" t="n">
-        <v>0.038</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>#32 I. NOGUÉS (Per Game)</t>
         </is>
@@ -6558,7 +6546,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>#77 Y. SIMA (Per Game)</t>
         </is>
@@ -6707,23 +6695,23 @@
         <v>0.154</v>
       </c>
       <c r="AW41" t="n">
-        <v>0.116</v>
+        <v>0.117</v>
       </c>
       <c r="AX41" t="n">
-        <v>0.113</v>
+        <v>0.115</v>
       </c>
       <c r="AY41" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="inlineStr">
+      <c r="A42" t="inlineStr">
         <is>
           <t>Equip (Per Game)</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -6750,10 +6738,10 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>2.714</v>
+        <v>2.111</v>
       </c>
       <c r="L42" t="n">
-        <v>1.714</v>
+        <v>1.667</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -6765,7 +6753,7 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>0.143</v>
+        <v>0.222</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -6876,315 +6864,315 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="inlineStr">
+      <c r="A43" t="inlineStr">
         <is>
           <t>TOTAL (Per Game)</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C43" t="n">
-        <v>97.143</v>
+        <v>97.333</v>
       </c>
       <c r="D43" t="n">
         <v>24</v>
       </c>
       <c r="E43" t="n">
-        <v>41</v>
+        <v>41.444</v>
       </c>
       <c r="F43" t="n">
-        <v>11</v>
+        <v>11.111</v>
       </c>
       <c r="G43" t="n">
-        <v>32.143</v>
+        <v>31.333</v>
       </c>
       <c r="H43" t="n">
-        <v>16.143</v>
+        <v>16</v>
       </c>
       <c r="I43" t="n">
-        <v>20.857</v>
+        <v>20.333</v>
       </c>
       <c r="J43" t="n">
-        <v>20.429</v>
+        <v>19.667</v>
       </c>
       <c r="K43" t="n">
-        <v>28.143</v>
+        <v>28</v>
       </c>
       <c r="L43" t="n">
-        <v>13.714</v>
+        <v>13.667</v>
       </c>
       <c r="M43" t="n">
-        <v>7.857</v>
+        <v>7.889</v>
       </c>
       <c r="N43" t="n">
-        <v>6.571</v>
+        <v>5.667</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>10.286</v>
+        <v>10.222</v>
       </c>
       <c r="Q43" t="n">
-        <v>10.143</v>
+        <v>10</v>
       </c>
       <c r="R43" t="n">
-        <v>19.286</v>
+        <v>19.444</v>
       </c>
       <c r="S43" t="n">
-        <v>21</v>
+        <v>20.222</v>
       </c>
       <c r="T43" t="n">
-        <v>857</v>
+        <v>1087</v>
       </c>
       <c r="U43" t="n">
-        <v>13.143</v>
+        <v>12.444</v>
       </c>
       <c r="V43" t="n">
-        <v>13.429</v>
+        <v>12.889</v>
       </c>
       <c r="W43" t="n">
-        <v>8.429</v>
+        <v>7.889</v>
       </c>
       <c r="X43" t="n">
-        <v>5.143</v>
+        <v>4.778</v>
       </c>
       <c r="Y43" t="n">
-        <v>16.143</v>
+        <v>15.778</v>
       </c>
       <c r="Z43" t="n">
-        <v>22.714</v>
+        <v>22.556</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.711</v>
+        <v>0.7</v>
       </c>
       <c r="AB43" t="n">
-        <v>4</v>
+        <v>4.556</v>
       </c>
       <c r="AC43" t="n">
-        <v>9.714</v>
+        <v>10.222</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.412</v>
+        <v>0.446</v>
       </c>
       <c r="AE43" t="n">
-        <v>3.857</v>
+        <v>3.667</v>
       </c>
       <c r="AF43" t="n">
-        <v>8.571</v>
+        <v>8.667</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.45</v>
+        <v>0.423</v>
       </c>
       <c r="AH43" t="n">
-        <v>3.429</v>
+        <v>3.556</v>
       </c>
       <c r="AI43" t="n">
-        <v>9.286</v>
+        <v>9.111000000000001</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.369</v>
+        <v>0.39</v>
       </c>
       <c r="AK43" t="n">
-        <v>7.571</v>
+        <v>7.556</v>
       </c>
       <c r="AL43" t="n">
-        <v>22.857</v>
+        <v>22.222</v>
       </c>
       <c r="AM43" t="n">
-        <v>0.331</v>
+        <v>0.34</v>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>207:08</t>
+          <t>205:33</t>
         </is>
       </c>
       <c r="AO43" t="n">
-        <v>92.60599999999999</v>
+        <v>91.947</v>
       </c>
       <c r="AP43" t="n">
-        <v>0.554</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0.59</v>
+        <v>0.595</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.049</v>
+        <v>1.059</v>
       </c>
       <c r="AS43" t="n">
         <v>0.111</v>
       </c>
       <c r="AT43" t="n">
-        <v>0.221</v>
+        <v>0.22</v>
       </c>
       <c r="AU43" t="n">
-        <v>1.986</v>
+        <v>1.924</v>
       </c>
       <c r="AV43" t="n">
         <v>0.2</v>
       </c>
       <c r="AW43" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AX43" t="n">
-        <v>0.142</v>
+        <v>0.144</v>
       </c>
       <c r="AY43" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="inlineStr">
+      <c r="A44" t="inlineStr">
         <is>
           <t>Rival (Per Game)</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C44" t="n">
-        <v>86.714</v>
+        <v>85.667</v>
       </c>
       <c r="D44" t="n">
-        <v>20.143</v>
+        <v>19.889</v>
       </c>
       <c r="E44" t="n">
-        <v>38.857</v>
+        <v>37.444</v>
       </c>
       <c r="F44" t="n">
-        <v>11.143</v>
+        <v>11</v>
       </c>
       <c r="G44" t="n">
-        <v>31.857</v>
+        <v>31.667</v>
       </c>
       <c r="H44" t="n">
-        <v>13</v>
+        <v>12.889</v>
       </c>
       <c r="I44" t="n">
-        <v>17.429</v>
+        <v>17.667</v>
       </c>
       <c r="J44" t="n">
-        <v>17.857</v>
+        <v>16.778</v>
       </c>
       <c r="K44" t="n">
-        <v>25</v>
+        <v>24.444</v>
       </c>
       <c r="L44" t="n">
-        <v>11.571</v>
+        <v>10.778</v>
       </c>
       <c r="M44" t="n">
-        <v>6.857</v>
+        <v>6.667</v>
       </c>
       <c r="N44" t="n">
-        <v>6.429</v>
+        <v>5.556</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>13</v>
+        <v>13.222</v>
       </c>
       <c r="Q44" t="n">
-        <v>11.429</v>
+        <v>11.778</v>
       </c>
       <c r="R44" t="n">
-        <v>21</v>
+        <v>20.333</v>
       </c>
       <c r="S44" t="n">
-        <v>19.143</v>
+        <v>19.333</v>
       </c>
       <c r="T44" t="n">
-        <v>670</v>
+        <v>834</v>
       </c>
       <c r="U44" t="n">
-        <v>8.856999999999999</v>
+        <v>8.555999999999999</v>
       </c>
       <c r="V44" t="n">
-        <v>11.857</v>
+        <v>10.222</v>
       </c>
       <c r="W44" t="n">
-        <v>4.714</v>
+        <v>4.556</v>
       </c>
       <c r="X44" t="n">
-        <v>3.143</v>
+        <v>2.778</v>
       </c>
       <c r="Y44" t="n">
-        <v>14</v>
+        <v>13.444</v>
       </c>
       <c r="Z44" t="n">
-        <v>20.714</v>
+        <v>20.111</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.676</v>
+        <v>0.669</v>
       </c>
       <c r="AB44" t="n">
-        <v>4.429</v>
+        <v>4.444</v>
       </c>
       <c r="AC44" t="n">
-        <v>12.714</v>
+        <v>11.556</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.348</v>
+        <v>0.385</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.714</v>
+        <v>2</v>
       </c>
       <c r="AF44" t="n">
-        <v>5.429</v>
+        <v>5.778</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.316</v>
+        <v>0.346</v>
       </c>
       <c r="AH44" t="n">
-        <v>3.286</v>
+        <v>3.222</v>
       </c>
       <c r="AI44" t="n">
-        <v>7.857</v>
+        <v>7.667</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0.418</v>
+        <v>0.42</v>
       </c>
       <c r="AK44" t="n">
-        <v>7.857</v>
+        <v>7.778</v>
       </c>
       <c r="AL44" t="n">
         <v>24</v>
       </c>
       <c r="AM44" t="n">
-        <v>0.327</v>
+        <v>0.324</v>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>207:08</t>
+          <t>205:33</t>
         </is>
       </c>
       <c r="AO44" t="n">
-        <v>91.383</v>
+        <v>90.107</v>
       </c>
       <c r="AP44" t="n">
-        <v>0.521</v>
+        <v>0.527</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.553</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="AR44" t="n">
-        <v>0.949</v>
+        <v>0.951</v>
       </c>
       <c r="AS44" t="n">
-        <v>0.142</v>
+        <v>0.147</v>
       </c>
       <c r="AT44" t="n">
-        <v>0.184</v>
+        <v>0.186</v>
       </c>
       <c r="AU44" t="n">
-        <v>1.374</v>
+        <v>1.269</v>
       </c>
       <c r="AV44" t="n">
-        <v>0.197</v>
+        <v>0.196</v>
       </c>
       <c r="AW44" t="n">
-        <v>0.06</v>
+        <v>0.057</v>
       </c>
       <c r="AX44" t="n">
         <v>0.126</v>
